--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -2277,7 +2277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A2:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="27" min="1" max="1"/>
@@ -2288,7 +2288,6 @@
     <col width="9" customWidth="1" style="27" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2372,7 @@
       <c r="K5" s="77" t="n"/>
       <c r="L5" s="59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
@@ -2402,7 +2401,7 @@
       <c r="K6" s="79" t="n"/>
       <c r="L6" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
@@ -2431,7 +2430,7 @@
       <c r="K7" s="79" t="n"/>
       <c r="L7" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
@@ -2448,7 +2447,7 @@
       </c>
       <c r="D8" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Level per Required/Needed EXP </t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="E8" s="78" t="n"/>
@@ -2460,7 +2459,7 @@
       <c r="K8" s="79" t="n"/>
       <c r="L8" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
@@ -2489,7 +2488,7 @@
       <c r="K9" s="79" t="n"/>
       <c r="L9" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
@@ -2518,7 +2517,7 @@
       <c r="K10" s="79" t="n"/>
       <c r="L10" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
@@ -2547,7 +2546,7 @@
       <c r="K11" s="79" t="n"/>
       <c r="L11" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
@@ -2576,7 +2575,7 @@
       <c r="K12" s="79" t="n"/>
       <c r="L12" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
@@ -2605,7 +2604,7 @@
       <c r="K13" s="79" t="n"/>
       <c r="L13" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
@@ -2634,7 +2633,7 @@
       <c r="K14" s="79" t="n"/>
       <c r="L14" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -2663,7 +2662,7 @@
       <c r="K15" s="79" t="n"/>
       <c r="L15" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
@@ -2692,7 +2691,7 @@
       <c r="K16" s="79" t="n"/>
       <c r="L16" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
@@ -2721,7 +2720,7 @@
       <c r="K17" s="79" t="n"/>
       <c r="L17" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
@@ -2750,7 +2749,7 @@
       <c r="K18" s="79" t="n"/>
       <c r="L18" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M18" s="6" t="n"/>
@@ -2779,7 +2778,7 @@
       <c r="K19" s="79" t="n"/>
       <c r="L19" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M19" s="6" t="n"/>
@@ -3090,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F360"/>
+  <dimension ref="A2:F360"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="2.625" customWidth="1" style="9" min="1" max="1"/>
@@ -3109,7 +3108,6 @@
     <col width="2.625" customWidth="1" style="9" min="55" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16.5" customHeight="1" s="72">
       <c r="B2" s="9" t="n"/>
       <c r="C2" s="9" t="n"/>
@@ -3628,7 +3626,7 @@
       <c r="D108" s="88" t="n"/>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week Reset being applied Timing DDDay HHTime to Display</t>
+          <t>one week reset DD HH displayed</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3873,7 @@
       <c r="D153" s="86" t="n"/>
       <c r="E153" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Number of Times doing case (Achieve Number of Times/Required/Needed Number of Times) Display</t>
+          <t>(achieve / ) displayed</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3955,12 @@
       </c>
       <c r="D160" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> time(s) Week Obtain Possible EXP Display</t>
+          <t>this week obtain possible EXP displayed</t>
         </is>
       </c>
       <c r="E160" s="19" t="inlineStr">
         <is>
-          <t>(Achieve EXP / time(s) Week Maximum to can present EXP) number Display</t>
+          <t>(achieve EXP / this week EXP) displayed</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3978,7 @@
       <c r="D162" s="86" t="n"/>
       <c r="E162" s="20" t="inlineStr">
         <is>
-          <t>Week Mission Tab in only Display</t>
+          <t>Weekly Mission Tab in only Display</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4094,7 @@
       </c>
       <c r="E190" s="25" t="inlineStr">
         <is>
-          <t>Week Mission Tab Remove
+          <t>Weekly Mission Tab Remove
 season Mission, Mission Tab Click when Each Mission All Deactivate state to DisplayDone/Applied</t>
         </is>
       </c>
@@ -4235,7 +4233,7 @@
       <c r="B213" s="9" t="n"/>
       <c r="C213" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - being applied season without case, Corresponding Area </t>
+          <t>- , area</t>
         </is>
       </c>
       <c r="D213" s="23" t="n"/>
@@ -4366,7 +4364,7 @@
     <row r="226" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>- designed Content according to Mission Cumulative or Quest Progress when Count Type to CategorizeDone/Applied</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4380,14 +4378,14 @@
     <row r="228" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C228" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> when) Below and as follows Composition when, 300Shard useDid, Mission when, 300/1,000 to Count Done/Applied</t>
+          <t>) composition , 300 , Challenge Mission , 300/1,000</t>
         </is>
       </c>
     </row>
     <row r="229" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week Mission : Shard 10 use</t>
+          <t xml:space="preserve"> Weekly Mission : Shard 10 use</t>
         </is>
       </c>
     </row>
@@ -4415,14 +4413,14 @@
     <row r="233" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> when) Below and as follows Composition when, Week Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
+          <t xml:space="preserve"> when) Below and as follows Composition when, Weekly Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
         </is>
       </c>
     </row>
     <row r="234" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week Mission : Monster 10creatures Defeat</t>
+          <t xml:space="preserve"> Weekly Mission : Monster 10creatures Defeat</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4727,7 @@
     <row r="267" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C267" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Date, Season Reward Content, Week, season, Mission Correspondingdoing Quest ID input</t>
+          <t xml:space="preserve"> → Date, Season Reward Content, Weekly, season, Mission Correspondingdoing Quest ID input</t>
         </is>
       </c>
     </row>
@@ -4940,16 +4938,16 @@
       </c>
       <c r="E305" s="13" t="inlineStr">
         <is>
-          <t>Week, season Mission's Above And EXP My/The. connectapplied Quest ID input
+          <t>Repeat range and EXP cap for Weekly, Seasonal, and Challenge missions. Enter the linked Quest ID.
 - PassMission
- → Weekly : Week Mission
- → Season : season Mission
- → Challenge : Mission
-- ScheduleID : Corresponding Mission's Day Schedule.xml's ID and matching when Day 
-- EXPLimit : Corresponding Mission's RepeatCycleUnit Standard EXP Obtain My/The
- → 1000 : 1000 to My/The Done/Applied
- → None/N/A : My/The None/N/A
-- Quest : Corresponding Mission's Quest ID</t>
+  → Weekly: Weekly Mission
+  → Season: Seasonal Mission
+  → Challenge: Challenge Mission
+- ScheduleID: Match the mission's schedule to a Schedule.xml ID to control timing
+- EXPLimit: EXP gain cap per RepeatCycleUnit for the mission
+  → 1000: Capped at 1,000 points
+  → Empty: No cap
+- Quest: Quest ID for the mission</t>
         </is>
       </c>
       <c r="F305" s="9" t="n"/>
@@ -5022,7 +5020,7 @@
       <c r="B311" s="9" t="n"/>
       <c r="C311" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Corresponding Data in ID Pass.xml Day when Corresponding Quest's Week, season, Categorize</t>
+          <t xml:space="preserve">  → Match the ID value in this data to Pass.xml to determine whether the quest is Weekly, Seasonal, or Challenge.</t>
         </is>
       </c>
       <c r="D311" s="9" t="n"/>
@@ -5264,7 +5262,7 @@
     <row r="349" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C349" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Each Level also Above Required/Needed Pass EXP input</t>
+          <t>EXP enter</t>
         </is>
       </c>
       <c r="E349" s="18" t="n"/>
@@ -5340,7 +5338,7 @@
       </c>
       <c r="E360" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corresponding Level also Above Required/Needed Cumulative EXP's </t>
+          <t>EXP</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="B2:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -5426,15 +5424,13 @@
     <col width="9" customWidth="1" style="8" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16.5" customHeight="1" s="72">
       <c r="B2" s="37" t="inlineStr">
         <is>
-          <t>Week Mission List</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Weekly Mission List</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="16.5" customHeight="1" s="72">
       <c r="B4" s="38" t="inlineStr">
         <is>
@@ -5972,7 +5968,7 @@
     <row r="37" ht="16.5" customHeight="1" s="72">
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>※ Week EXP My/The 2500, Star's Apostle Summon 1times until if done 1500 Obtain Possible</t>
+          <t>※ Weekly EXP My/The 2500, Star's Apostle Summon 1times until if done 1500 Obtain Possible</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -5985,7 +5981,6 @@
         <v>320</v>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="16.5" customHeight="1" s="72">
       <c r="B39" s="37" t="inlineStr">
         <is>
@@ -5993,7 +5988,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="16.5" customHeight="1" s="72">
       <c r="B41" s="38" t="inlineStr">
         <is>
@@ -6352,8 +6346,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64"/>
     <row r="65" ht="16.5" customHeight="1" s="72">
       <c r="B65" s="37" t="inlineStr">
         <is>
@@ -6361,7 +6353,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="16.5" customHeight="1" s="72">
       <c r="B67" s="38" t="inlineStr">
         <is>
@@ -6800,40 +6791,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128" ht="16.5" customHeight="1" s="72">
       <c r="B128" s="8" t="inlineStr">
         <is>
@@ -6852,24 +6809,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="B2:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="40" min="1" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16.5" customHeight="1" s="72">
       <c r="B2" s="37" t="inlineStr">
         <is>
-          <t>Each season Level per Required/Needed EXP</t>
+          <t>EXP</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" s="72">
       <c r="B3" s="40" t="inlineStr">
         <is>
-          <t>※ Required/Needed Corresponding Level also Behind/After Required/Needed EXP</t>
+          <t>※ EXP</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6842,7 @@
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
-          <t>Required/Needed EXP</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
@@ -7626,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="B2:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="44" min="1" max="3"/>
@@ -7634,7 +7590,6 @@
     <col width="9" customWidth="1" style="44" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="37" t="inlineStr">
         <is>
@@ -7642,7 +7597,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="45" t="inlineStr">
         <is>

--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -110,6 +110,15 @@
       <color theme="0"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -702,7 +711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -940,6 +949,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2277,19 +2325,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="27" min="1" max="1"/>
-    <col width="9" customWidth="1" style="27" min="2" max="2"/>
-    <col width="11" customWidth="1" style="27" min="3" max="3"/>
-    <col width="9" customWidth="1" style="27" min="4" max="15"/>
+    <col width="8" customWidth="1" style="27" min="2" max="2"/>
+    <col width="12" customWidth="1" style="27" min="3" max="3"/>
+    <col width="75" customWidth="1" style="27" min="4" max="15"/>
+    <col width="18" customWidth="1" style="72" min="12" max="12"/>
     <col width="11.375" bestFit="1" customWidth="1" style="27" min="16" max="16"/>
     <col width="9" customWidth="1" style="27" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="22" customHeight="1" s="72">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>Document History : Season Pass</t>
         </is>
@@ -2305,10 +2355,22 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
     </row>
-    <row r="3">
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+    <row r="3" ht="18" customHeight="1" s="72">
+      <c r="B3" s="92" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="C3" s="92" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D3" s="92" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -2316,767 +2378,441 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" s="72">
+      <c r="L3" s="92" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="72">
       <c r="A4" s="5" t="n"/>
-      <c r="B4" s="50" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="C4" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Date</t>
-        </is>
-      </c>
-      <c r="D4" s="52" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E4" s="73" t="n"/>
-      <c r="F4" s="73" t="n"/>
-      <c r="G4" s="73" t="n"/>
-      <c r="H4" s="73" t="n"/>
-      <c r="I4" s="73" t="n"/>
-      <c r="J4" s="73" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t>24.04.22</t>
+        </is>
+      </c>
+      <c r="D4" s="94" t="inlineStr">
+        <is>
+          <t>Initial draft</t>
+        </is>
+      </c>
+      <c r="L4" s="95" t="inlineStr">
+        <is>
+          <t>Juwon Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="72">
       <c r="A5" s="5" t="n"/>
-      <c r="B5" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="55" t="inlineStr">
-        <is>
-          <t>24.04.22</t>
-        </is>
-      </c>
-      <c r="D5" s="75" t="inlineStr">
-        <is>
-          <t>Initial Draft</t>
-        </is>
-      </c>
-      <c r="E5" s="76" t="n"/>
-      <c r="F5" s="76" t="n"/>
-      <c r="G5" s="76" t="n"/>
-      <c r="H5" s="76" t="n"/>
-      <c r="I5" s="76" t="n"/>
-      <c r="J5" s="76" t="n"/>
-      <c r="K5" s="77" t="n"/>
-      <c r="L5" s="59" t="inlineStr">
+      <c r="B5" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="97" t="inlineStr">
+        <is>
+          <t>24.05.27</t>
+        </is>
+      </c>
+      <c r="D5" s="98" t="inlineStr">
+        <is>
+          <t>Package reward removed</t>
+        </is>
+      </c>
+      <c r="L5" s="99" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M5" s="6" t="n"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="72">
+    <row r="6" ht="18" customHeight="1" s="72">
       <c r="A6" s="5" t="n"/>
-      <c r="B6" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="47" t="inlineStr">
-        <is>
-          <t>24.05.27</t>
-        </is>
-      </c>
-      <c r="D6" s="48" t="inlineStr">
-        <is>
-          <t>Package Reward Remove</t>
-        </is>
-      </c>
-      <c r="E6" s="78" t="n"/>
-      <c r="F6" s="78" t="n"/>
-      <c r="G6" s="78" t="n"/>
-      <c r="H6" s="78" t="n"/>
-      <c r="I6" s="78" t="n"/>
-      <c r="J6" s="78" t="n"/>
-      <c r="K6" s="79" t="n"/>
-      <c r="L6" s="61" t="inlineStr">
+      <c r="B6" s="100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="101" t="inlineStr">
+        <is>
+          <t>24.05.28</t>
+        </is>
+      </c>
+      <c r="D6" s="102" t="inlineStr">
+        <is>
+          <t>Past season UI — detailed description added</t>
+        </is>
+      </c>
+      <c r="L6" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M6" s="6" t="n"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="72">
+    <row r="7" ht="18" customHeight="1" s="72">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>24.05.28</t>
-        </is>
-      </c>
-      <c r="D7" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> season UI Detailed Description Add</t>
-        </is>
-      </c>
-      <c r="E7" s="78" t="n"/>
-      <c r="F7" s="78" t="n"/>
-      <c r="G7" s="78" t="n"/>
-      <c r="H7" s="78" t="n"/>
-      <c r="I7" s="78" t="n"/>
-      <c r="J7" s="78" t="n"/>
-      <c r="K7" s="79" t="n"/>
-      <c r="L7" s="61" t="inlineStr">
+      <c r="B7" s="100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="101" t="inlineStr">
+        <is>
+          <t>24.05.29</t>
+        </is>
+      </c>
+      <c r="D7" s="102" t="inlineStr">
+        <is>
+          <t>Required XP per level specified</t>
+        </is>
+      </c>
+      <c r="L7" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M7" s="6" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="72">
+    <row r="8" ht="18" customHeight="1" s="72">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="60" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="B8" s="100" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="101" t="inlineStr">
         <is>
           <t>24.05.29</t>
         </is>
       </c>
-      <c r="D8" s="48" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="E8" s="78" t="n"/>
-      <c r="F8" s="78" t="n"/>
-      <c r="G8" s="78" t="n"/>
-      <c r="H8" s="78" t="n"/>
-      <c r="I8" s="78" t="n"/>
-      <c r="J8" s="78" t="n"/>
-      <c r="K8" s="79" t="n"/>
-      <c r="L8" s="61" t="inlineStr">
+      <c r="D8" s="102" t="inlineStr">
+        <is>
+          <t>All mission types set to cumulative count</t>
+        </is>
+      </c>
+      <c r="L8" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M8" s="6" t="n"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="72">
+    <row r="9" ht="18" customHeight="1" s="72">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="60" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>24.05.29</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="inlineStr">
-        <is>
-          <t>All Type's Mission Cumulative to Count</t>
-        </is>
-      </c>
-      <c r="E9" s="78" t="n"/>
-      <c r="F9" s="78" t="n"/>
-      <c r="G9" s="78" t="n"/>
-      <c r="H9" s="78" t="n"/>
-      <c r="I9" s="78" t="n"/>
-      <c r="J9" s="78" t="n"/>
-      <c r="K9" s="79" t="n"/>
-      <c r="L9" s="61" t="inlineStr">
+      <c r="B9" s="100" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="101" t="inlineStr">
+        <is>
+          <t>24.06.24</t>
+        </is>
+      </c>
+      <c r="D9" s="102" t="inlineStr">
+        <is>
+          <t>Missions split into cumulative vs. quest-progress types</t>
+        </is>
+      </c>
+      <c r="L9" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M9" s="6" t="n"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="72">
+    <row r="10" ht="18" customHeight="1" s="72">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="60" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="B10" s="100" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="101" t="inlineStr">
         <is>
           <t>24.06.24</t>
         </is>
       </c>
-      <c r="D10" s="48" t="inlineStr">
-        <is>
-          <t>Mission designed Content according to Cumulative, Quest Progress when to Categorize Possible</t>
-        </is>
-      </c>
-      <c r="E10" s="78" t="n"/>
-      <c r="F10" s="78" t="n"/>
-      <c r="G10" s="78" t="n"/>
-      <c r="H10" s="78" t="n"/>
-      <c r="I10" s="78" t="n"/>
-      <c r="J10" s="78" t="n"/>
-      <c r="K10" s="79" t="n"/>
-      <c r="L10" s="61" t="inlineStr">
+      <c r="D10" s="102" t="inlineStr">
+        <is>
+          <t>Bilibili ranking system content applied</t>
+        </is>
+      </c>
+      <c r="L10" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M10" s="6" t="n"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="72">
+    <row r="11" ht="18" customHeight="1" s="72">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="60" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
+      <c r="B11" s="100" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>24.06.24</t>
         </is>
       </c>
-      <c r="D11" s="48" t="inlineStr">
-        <is>
-          <t>Current Bilibili's Ranking when 's Content Apply</t>
-        </is>
-      </c>
-      <c r="E11" s="78" t="n"/>
-      <c r="F11" s="78" t="n"/>
-      <c r="G11" s="78" t="n"/>
-      <c r="H11" s="78" t="n"/>
-      <c r="I11" s="78" t="n"/>
-      <c r="J11" s="78" t="n"/>
-      <c r="K11" s="79" t="n"/>
-      <c r="L11" s="61" t="inlineStr">
+      <c r="D11" s="102" t="inlineStr">
+        <is>
+          <t>Cosmetic rewards (name tags, titles, profile skins) added to reward pool</t>
+        </is>
+      </c>
+      <c r="L11" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M11" s="6" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="72">
+    <row r="12" ht="18" customHeight="1" s="72">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="60" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="47" t="inlineStr">
-        <is>
-          <t>24.06.24</t>
-        </is>
-      </c>
-      <c r="D12" s="48" t="inlineStr">
-        <is>
-          <t>Reward Content Name Tag, Title, Profile Skin Etc.'s Cosmetic Item Provide can Yes/Available</t>
-        </is>
-      </c>
-      <c r="E12" s="78" t="n"/>
-      <c r="F12" s="78" t="n"/>
-      <c r="G12" s="78" t="n"/>
-      <c r="H12" s="78" t="n"/>
-      <c r="I12" s="78" t="n"/>
-      <c r="J12" s="78" t="n"/>
-      <c r="K12" s="79" t="n"/>
-      <c r="L12" s="61" t="inlineStr">
+      <c r="B12" s="100" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="101" t="inlineStr">
+        <is>
+          <t>24.07.11</t>
+        </is>
+      </c>
+      <c r="D12" s="102" t="inlineStr">
+        <is>
+          <t>Access button changed</t>
+        </is>
+      </c>
+      <c r="L12" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M12" s="6" t="n"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="72">
+    <row r="13" ht="18" customHeight="1" s="72">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="60" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>24.07.11</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>Access Button Change</t>
-        </is>
-      </c>
-      <c r="E13" s="78" t="n"/>
-      <c r="F13" s="78" t="n"/>
-      <c r="G13" s="78" t="n"/>
-      <c r="H13" s="78" t="n"/>
-      <c r="I13" s="78" t="n"/>
-      <c r="J13" s="78" t="n"/>
-      <c r="K13" s="79" t="n"/>
-      <c r="L13" s="61" t="inlineStr">
+      <c r="B13" s="100" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="101" t="inlineStr">
+        <is>
+          <t>24.07.15</t>
+        </is>
+      </c>
+      <c r="D13" s="102" t="inlineStr">
+        <is>
+          <t>HUD rank indicator feature added</t>
+        </is>
+      </c>
+      <c r="L13" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M13" s="6" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="72">
+    <row r="14" ht="18" customHeight="1" s="72">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>24.07.15</t>
-        </is>
-      </c>
-      <c r="D14" s="48" t="inlineStr">
-        <is>
-          <t>HUD Rank check can present Function Add</t>
-        </is>
-      </c>
-      <c r="E14" s="78" t="n"/>
-      <c r="F14" s="78" t="n"/>
-      <c r="G14" s="78" t="n"/>
-      <c r="H14" s="78" t="n"/>
-      <c r="I14" s="78" t="n"/>
-      <c r="J14" s="78" t="n"/>
-      <c r="K14" s="79" t="n"/>
-      <c r="L14" s="61" t="inlineStr">
+      <c r="B14" s="100" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="101" t="inlineStr">
+        <is>
+          <t>24.07.22</t>
+        </is>
+      </c>
+      <c r="D14" s="102" t="inlineStr">
+        <is>
+          <t>Unlock timing specified</t>
+        </is>
+      </c>
+      <c r="L14" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="72">
+    <row r="15" ht="18" customHeight="1" s="72">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="60" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="47" t="inlineStr">
-        <is>
-          <t>24.07.22</t>
-        </is>
-      </c>
-      <c r="D15" s="48" t="inlineStr">
-        <is>
-          <t>Unlock Timing Add</t>
-        </is>
-      </c>
-      <c r="E15" s="78" t="n"/>
-      <c r="F15" s="78" t="n"/>
-      <c r="G15" s="78" t="n"/>
-      <c r="H15" s="78" t="n"/>
-      <c r="I15" s="78" t="n"/>
-      <c r="J15" s="78" t="n"/>
-      <c r="K15" s="79" t="n"/>
-      <c r="L15" s="61" t="inlineStr">
+      <c r="B15" s="100" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="101" t="inlineStr">
+        <is>
+          <t>24.08.26</t>
+        </is>
+      </c>
+      <c r="D15" s="102" t="inlineStr">
+        <is>
+          <t>List updated; levels changed to 45 tiers; Pass XP halved</t>
+        </is>
+      </c>
+      <c r="L15" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M15" s="6" t="n"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="72">
+    <row r="16" ht="18" customHeight="1" s="72">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="60" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="47" t="inlineStr">
-        <is>
-          <t>24.08.26</t>
-        </is>
-      </c>
-      <c r="D16" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">List Updated, Level 45Stage to Modify, Pass EXP Level to </t>
-        </is>
-      </c>
-      <c r="E16" s="78" t="n"/>
-      <c r="F16" s="78" t="n"/>
-      <c r="G16" s="78" t="n"/>
-      <c r="H16" s="78" t="n"/>
-      <c r="I16" s="78" t="n"/>
-      <c r="J16" s="78" t="n"/>
-      <c r="K16" s="79" t="n"/>
-      <c r="L16" s="61" t="inlineStr">
+      <c r="B16" s="100" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="101" t="inlineStr">
+        <is>
+          <t>24.08.27</t>
+        </is>
+      </c>
+      <c r="D16" s="102" t="inlineStr">
+        <is>
+          <t>Lv. 9, 19: Intermediate Gem Box ×3; Lv. 44: Advanced Skill Support Box ×5</t>
+        </is>
+      </c>
+      <c r="L16" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M16" s="6" t="n"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="72">
+    <row r="17" ht="18" customHeight="1" s="72">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="60" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>24.08.27</t>
-        </is>
-      </c>
-      <c r="D17" s="48" t="inlineStr">
-        <is>
-          <t>9, 19Level Gem Intermediate Gem Box 3pieces Provide, 44Level Reward Skill Select 5pieces</t>
-        </is>
-      </c>
-      <c r="E17" s="78" t="n"/>
-      <c r="F17" s="78" t="n"/>
-      <c r="G17" s="78" t="n"/>
-      <c r="H17" s="78" t="n"/>
-      <c r="I17" s="78" t="n"/>
-      <c r="J17" s="78" t="n"/>
-      <c r="K17" s="79" t="n"/>
-      <c r="L17" s="61" t="inlineStr">
+      <c r="B17" s="100" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="101" t="inlineStr">
+        <is>
+          <t>24.09.05</t>
+        </is>
+      </c>
+      <c r="D17" s="102" t="inlineStr">
+        <is>
+          <t>Stamina Potion removed from rank level rewards</t>
+        </is>
+      </c>
+      <c r="L17" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M17" s="6" t="n"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="72">
+    <row r="18" ht="18" customHeight="1" s="72">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="60" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>24.09.05</t>
-        </is>
-      </c>
-      <c r="D18" s="48" t="inlineStr">
-        <is>
-          <t>Rank Level Reward Stamina Potion Remove</t>
-        </is>
-      </c>
-      <c r="E18" s="78" t="n"/>
-      <c r="F18" s="78" t="n"/>
-      <c r="G18" s="78" t="n"/>
-      <c r="H18" s="78" t="n"/>
-      <c r="I18" s="78" t="n"/>
-      <c r="J18" s="78" t="n"/>
-      <c r="K18" s="79" t="n"/>
-      <c r="L18" s="61" t="inlineStr">
+      <c r="B18" s="100" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="101" t="inlineStr">
+        <is>
+          <t>25.01.15</t>
+        </is>
+      </c>
+      <c r="D18" s="102" t="inlineStr">
+        <is>
+          <t>UI updated; XML structure revised</t>
+        </is>
+      </c>
+      <c r="L18" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
       <c r="M18" s="6" t="n"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="72">
+    <row r="19" ht="18" customHeight="1" s="72">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="60" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>25.01.15</t>
-        </is>
-      </c>
-      <c r="D19" s="48" t="inlineStr">
-        <is>
-          <t>UI Updated And XML Structure Update</t>
-        </is>
-      </c>
-      <c r="E19" s="78" t="n"/>
-      <c r="F19" s="78" t="n"/>
-      <c r="G19" s="78" t="n"/>
-      <c r="H19" s="78" t="n"/>
-      <c r="I19" s="78" t="n"/>
-      <c r="J19" s="78" t="n"/>
-      <c r="K19" s="79" t="n"/>
-      <c r="L19" s="61" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
+      <c r="B19" s="100" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="101" t="inlineStr">
+        <is>
+          <t>25.05.30</t>
+        </is>
+      </c>
+      <c r="D19" s="102" t="inlineStr">
+        <is>
+          <t>Mission list, Pass XP, and Pass reward list modified</t>
+        </is>
+      </c>
+      <c r="L19" s="103" t="inlineStr">
+        <is>
+          <t>Jinho Ha</t>
         </is>
       </c>
       <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="62" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" s="63" t="inlineStr">
-        <is>
-          <t>25.05.30</t>
-        </is>
-      </c>
-      <c r="D20" s="64" t="inlineStr">
-        <is>
-          <t>Mission List, Pass EXP, Pass Reward List Modify</t>
-        </is>
-      </c>
-      <c r="E20" s="80" t="n"/>
-      <c r="F20" s="80" t="n"/>
-      <c r="G20" s="80" t="n"/>
-      <c r="H20" s="80" t="n"/>
-      <c r="I20" s="80" t="n"/>
-      <c r="J20" s="80" t="n"/>
-      <c r="K20" s="81" t="n"/>
-      <c r="L20" s="66" t="inlineStr">
-        <is>
-          <t>Jinho Ha</t>
-        </is>
-      </c>
+      <c r="B20" s="62" t="n"/>
+      <c r="C20" s="63" t="n"/>
+      <c r="D20" s="64" t="n"/>
+      <c r="L20" s="66" t="n"/>
       <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="46" t="n"/>
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
-      <c r="E21" s="82" t="n"/>
-      <c r="F21" s="82" t="n"/>
-      <c r="G21" s="82" t="n"/>
-      <c r="H21" s="82" t="n"/>
-      <c r="I21" s="82" t="n"/>
-      <c r="J21" s="82" t="n"/>
-      <c r="K21" s="83" t="n"/>
       <c r="L21" s="46" t="n"/>
     </row>
     <row r="22">
       <c r="D22" s="27" t="n"/>
-      <c r="E22" s="84" t="n"/>
-      <c r="F22" s="84" t="n"/>
-      <c r="G22" s="84" t="n"/>
-      <c r="H22" s="84" t="n"/>
-      <c r="I22" s="84" t="n"/>
-      <c r="J22" s="84" t="n"/>
-      <c r="K22" s="85" t="n"/>
     </row>
     <row r="23">
       <c r="D23" s="27" t="n"/>
-      <c r="E23" s="84" t="n"/>
-      <c r="F23" s="84" t="n"/>
-      <c r="G23" s="84" t="n"/>
-      <c r="H23" s="84" t="n"/>
-      <c r="I23" s="84" t="n"/>
-      <c r="J23" s="84" t="n"/>
-      <c r="K23" s="85" t="n"/>
     </row>
     <row r="24">
       <c r="D24" s="27" t="n"/>
-      <c r="E24" s="84" t="n"/>
-      <c r="F24" s="84" t="n"/>
-      <c r="G24" s="84" t="n"/>
-      <c r="H24" s="84" t="n"/>
-      <c r="I24" s="84" t="n"/>
-      <c r="J24" s="84" t="n"/>
-      <c r="K24" s="85" t="n"/>
     </row>
     <row r="25">
       <c r="D25" s="27" t="n"/>
-      <c r="E25" s="84" t="n"/>
-      <c r="F25" s="84" t="n"/>
-      <c r="G25" s="84" t="n"/>
-      <c r="H25" s="84" t="n"/>
-      <c r="I25" s="84" t="n"/>
-      <c r="J25" s="84" t="n"/>
-      <c r="K25" s="85" t="n"/>
     </row>
     <row r="26">
       <c r="D26" s="27" t="n"/>
-      <c r="E26" s="84" t="n"/>
-      <c r="F26" s="84" t="n"/>
-      <c r="G26" s="84" t="n"/>
-      <c r="H26" s="84" t="n"/>
-      <c r="I26" s="84" t="n"/>
-      <c r="J26" s="84" t="n"/>
-      <c r="K26" s="85" t="n"/>
     </row>
     <row r="27">
       <c r="D27" s="27" t="n"/>
-      <c r="E27" s="84" t="n"/>
-      <c r="F27" s="84" t="n"/>
-      <c r="G27" s="84" t="n"/>
-      <c r="H27" s="84" t="n"/>
-      <c r="I27" s="84" t="n"/>
-      <c r="J27" s="84" t="n"/>
-      <c r="K27" s="85" t="n"/>
     </row>
     <row r="28">
       <c r="D28" s="27" t="n"/>
-      <c r="E28" s="84" t="n"/>
-      <c r="F28" s="84" t="n"/>
-      <c r="G28" s="84" t="n"/>
-      <c r="H28" s="84" t="n"/>
-      <c r="I28" s="84" t="n"/>
-      <c r="J28" s="84" t="n"/>
-      <c r="K28" s="85" t="n"/>
     </row>
     <row r="29">
       <c r="D29" s="27" t="n"/>
-      <c r="E29" s="84" t="n"/>
-      <c r="F29" s="84" t="n"/>
-      <c r="G29" s="84" t="n"/>
-      <c r="H29" s="84" t="n"/>
-      <c r="I29" s="84" t="n"/>
-      <c r="J29" s="84" t="n"/>
-      <c r="K29" s="85" t="n"/>
     </row>
     <row r="30">
       <c r="D30" s="27" t="n"/>
-      <c r="E30" s="84" t="n"/>
-      <c r="F30" s="84" t="n"/>
-      <c r="G30" s="84" t="n"/>
-      <c r="H30" s="84" t="n"/>
-      <c r="I30" s="84" t="n"/>
-      <c r="J30" s="84" t="n"/>
-      <c r="K30" s="85" t="n"/>
     </row>
     <row r="31">
       <c r="D31" s="27" t="n"/>
-      <c r="E31" s="84" t="n"/>
-      <c r="F31" s="84" t="n"/>
-      <c r="G31" s="84" t="n"/>
-      <c r="H31" s="84" t="n"/>
-      <c r="I31" s="84" t="n"/>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="85" t="n"/>
     </row>
     <row r="32">
       <c r="D32" s="27" t="n"/>
-      <c r="E32" s="84" t="n"/>
-      <c r="F32" s="84" t="n"/>
-      <c r="G32" s="84" t="n"/>
-      <c r="H32" s="84" t="n"/>
-      <c r="I32" s="84" t="n"/>
-      <c r="J32" s="84" t="n"/>
-      <c r="K32" s="85" t="n"/>
     </row>
     <row r="33">
       <c r="D33" s="27" t="n"/>
-      <c r="E33" s="84" t="n"/>
-      <c r="F33" s="84" t="n"/>
-      <c r="G33" s="84" t="n"/>
-      <c r="H33" s="84" t="n"/>
-      <c r="I33" s="84" t="n"/>
-      <c r="J33" s="84" t="n"/>
-      <c r="K33" s="85" t="n"/>
     </row>
     <row r="34">
       <c r="D34" s="27" t="n"/>
-      <c r="E34" s="84" t="n"/>
-      <c r="F34" s="84" t="n"/>
-      <c r="G34" s="84" t="n"/>
-      <c r="H34" s="84" t="n"/>
-      <c r="I34" s="84" t="n"/>
-      <c r="J34" s="84" t="n"/>
-      <c r="K34" s="85" t="n"/>
     </row>
     <row r="35">
       <c r="D35" s="27" t="n"/>
-      <c r="E35" s="84" t="n"/>
-      <c r="F35" s="84" t="n"/>
-      <c r="G35" s="84" t="n"/>
-      <c r="H35" s="84" t="n"/>
-      <c r="I35" s="84" t="n"/>
-      <c r="J35" s="84" t="n"/>
-      <c r="K35" s="85" t="n"/>
     </row>
     <row r="36">
       <c r="D36" s="27" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="84" t="n"/>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="85" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="27" t="n"/>
-      <c r="E37" s="84" t="n"/>
-      <c r="F37" s="84" t="n"/>
-      <c r="G37" s="84" t="n"/>
-      <c r="H37" s="84" t="n"/>
-      <c r="I37" s="84" t="n"/>
-      <c r="J37" s="84" t="n"/>
-      <c r="K37" s="85" t="n"/>
     </row>
     <row r="38">
       <c r="D38" s="27" t="n"/>
-      <c r="E38" s="84" t="n"/>
-      <c r="F38" s="84" t="n"/>
-      <c r="G38" s="84" t="n"/>
-      <c r="H38" s="84" t="n"/>
-      <c r="I38" s="84" t="n"/>
-      <c r="J38" s="84" t="n"/>
-      <c r="K38" s="85" t="n"/>
     </row>
     <row r="39">
       <c r="D39" s="27" t="n"/>
-      <c r="E39" s="84" t="n"/>
-      <c r="F39" s="84" t="n"/>
-      <c r="G39" s="84" t="n"/>
-      <c r="H39" s="84" t="n"/>
-      <c r="I39" s="84" t="n"/>
-      <c r="J39" s="84" t="n"/>
-      <c r="K39" s="85" t="n"/>
     </row>
     <row r="40">
       <c r="D40" s="27" t="n"/>
-      <c r="E40" s="84" t="n"/>
-      <c r="F40" s="84" t="n"/>
-      <c r="G40" s="84" t="n"/>
-      <c r="H40" s="84" t="n"/>
-      <c r="I40" s="84" t="n"/>
-      <c r="J40" s="84" t="n"/>
-      <c r="K40" s="85" t="n"/>
     </row>
     <row r="41">
       <c r="D41" s="27" t="n"/>
-      <c r="E41" s="84" t="n"/>
-      <c r="F41" s="84" t="n"/>
-      <c r="G41" s="84" t="n"/>
-      <c r="H41" s="84" t="n"/>
-      <c r="I41" s="84" t="n"/>
-      <c r="J41" s="84" t="n"/>
-      <c r="K41" s="85" t="n"/>
     </row>
     <row r="42">
       <c r="D42" s="27" t="n"/>
-      <c r="E42" s="84" t="n"/>
-      <c r="F42" s="84" t="n"/>
-      <c r="G42" s="84" t="n"/>
-      <c r="H42" s="84" t="n"/>
-      <c r="I42" s="84" t="n"/>
-      <c r="J42" s="84" t="n"/>
-      <c r="K42" s="85" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="D20:K20"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="D34:K34"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D22:K22"/>
-    <mergeCell ref="D31:K31"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="D21:K21"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D27:K27"/>
-    <mergeCell ref="D41:K41"/>
-    <mergeCell ref="D32:K32"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="D37:K37"/>
-    <mergeCell ref="D4:K4"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D30:K30"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D24:K24"/>
-    <mergeCell ref="D42:K42"/>
-    <mergeCell ref="D38:K38"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D29:K29"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D23:K23"/>
-    <mergeCell ref="D35:K35"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
@@ -3089,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F360"/>
+  <dimension ref="A1:F360"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="2.625" customWidth="1" style="9" min="1" max="1"/>
@@ -3108,6 +2844,7 @@
     <col width="2.625" customWidth="1" style="9" min="55" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1" s="72"/>
     <row r="2" ht="16.5" customHeight="1" s="72">
       <c r="B2" s="9" t="n"/>
       <c r="C2" s="9" t="n"/>
@@ -5404,7 +5141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E128"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -5424,6 +5161,7 @@
     <col width="9" customWidth="1" style="8" min="16" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1" s="72"/>
     <row r="2" ht="16.5" customHeight="1" s="72">
       <c r="B2" s="37" t="inlineStr">
         <is>
@@ -5431,6 +5169,7 @@
         </is>
       </c>
     </row>
+    <row r="3" s="72"/>
     <row r="4" ht="16.5" customHeight="1" s="72">
       <c r="B4" s="38" t="inlineStr">
         <is>
@@ -5981,6 +5720,7 @@
         <v>320</v>
       </c>
     </row>
+    <row r="38" s="72"/>
     <row r="39" ht="16.5" customHeight="1" s="72">
       <c r="B39" s="37" t="inlineStr">
         <is>
@@ -5988,6 +5728,7 @@
         </is>
       </c>
     </row>
+    <row r="40" s="72"/>
     <row r="41" ht="16.5" customHeight="1" s="72">
       <c r="B41" s="38" t="inlineStr">
         <is>
@@ -6346,6 +6087,8 @@
         <v>20</v>
       </c>
     </row>
+    <row r="63" s="72"/>
+    <row r="64" s="72"/>
     <row r="65" ht="16.5" customHeight="1" s="72">
       <c r="B65" s="37" t="inlineStr">
         <is>
@@ -6353,6 +6096,7 @@
         </is>
       </c>
     </row>
+    <row r="66" s="72"/>
     <row r="67" ht="16.5" customHeight="1" s="72">
       <c r="B67" s="38" t="inlineStr">
         <is>
@@ -6791,6 +6535,40 @@
         <v>30</v>
       </c>
     </row>
+    <row r="94" s="72"/>
+    <row r="95" s="72"/>
+    <row r="96" s="72"/>
+    <row r="97" s="72"/>
+    <row r="98" s="72"/>
+    <row r="99" s="72"/>
+    <row r="100" s="72"/>
+    <row r="101" s="72"/>
+    <row r="102" s="72"/>
+    <row r="103" s="72"/>
+    <row r="104" s="72"/>
+    <row r="105" s="72"/>
+    <row r="106" s="72"/>
+    <row r="107" s="72"/>
+    <row r="108" s="72"/>
+    <row r="109" s="72"/>
+    <row r="110" s="72"/>
+    <row r="111" s="72"/>
+    <row r="112" s="72"/>
+    <row r="113" s="72"/>
+    <row r="114" s="72"/>
+    <row r="115" s="72"/>
+    <row r="116" s="72"/>
+    <row r="117" s="72"/>
+    <row r="118" s="72"/>
+    <row r="119" s="72"/>
+    <row r="120" s="72"/>
+    <row r="121" s="72"/>
+    <row r="122" s="72"/>
+    <row r="123" s="72"/>
+    <row r="124" s="72"/>
+    <row r="125" s="72"/>
+    <row r="126" s="72"/>
+    <row r="127" s="72"/>
     <row r="128" ht="16.5" customHeight="1" s="72">
       <c r="B128" s="8" t="inlineStr">
         <is>
@@ -6809,12 +6587,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="40" min="1" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1" s="72"/>
     <row r="2" ht="16.5" customHeight="1" s="72">
       <c r="B2" s="37" t="inlineStr">
         <is>
@@ -7582,7 +7361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="44" min="1" max="3"/>
@@ -7590,14 +7369,16 @@
     <col width="9" customWidth="1" style="44" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="1" s="72"/>
+    <row r="2" s="72">
       <c r="B2" s="37" t="inlineStr">
         <is>
           <t>Pass Reward</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="3" s="72"/>
+    <row r="4" s="72">
       <c r="B4" s="45" t="inlineStr">
         <is>
           <t>Level</t>
@@ -7619,7 +7400,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="72">
       <c r="B5" s="43" t="n">
         <v>1</v>
       </c>
@@ -7635,7 +7416,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" s="72">
       <c r="B6" s="43" t="n">
         <v>2</v>
       </c>
@@ -7651,7 +7432,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" s="72">
       <c r="B7" s="43" t="n">
         <v>3</v>
       </c>
@@ -7667,7 +7448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" s="72">
       <c r="B8" s="43" t="n">
         <v>4</v>
       </c>
@@ -7683,7 +7464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" s="72">
       <c r="B9" s="43" t="n">
         <v>5</v>
       </c>
@@ -7699,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" s="72">
       <c r="B10" s="43" t="n">
         <v>6</v>
       </c>
@@ -7715,7 +7496,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" s="72">
       <c r="B11" s="43" t="n">
         <v>7</v>
       </c>
@@ -7731,7 +7512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="72">
       <c r="B12" s="43" t="n">
         <v>8</v>
       </c>
@@ -7747,7 +7528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" s="72">
       <c r="B13" s="43" t="n">
         <v>9</v>
       </c>
@@ -7763,7 +7544,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" s="72">
       <c r="B14" s="43" t="n">
         <v>10</v>
       </c>
@@ -7779,7 +7560,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" s="72">
       <c r="B15" s="43" t="n">
         <v>11</v>
       </c>
@@ -7795,7 +7576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="72">
       <c r="B16" s="43" t="n">
         <v>12</v>
       </c>
@@ -7811,7 +7592,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" s="72">
       <c r="B17" s="43" t="n">
         <v>13</v>
       </c>
@@ -7827,7 +7608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" s="72">
       <c r="B18" s="43" t="n">
         <v>14</v>
       </c>
@@ -7843,7 +7624,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="72">
       <c r="B19" s="43" t="n">
         <v>15</v>
       </c>
@@ -7859,7 +7640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="72">
       <c r="B20" s="43" t="n">
         <v>16</v>
       </c>
@@ -7875,7 +7656,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" s="72">
       <c r="B21" s="43" t="n">
         <v>17</v>
       </c>
@@ -7891,7 +7672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" s="72">
       <c r="B22" s="43" t="n">
         <v>18</v>
       </c>
@@ -7907,7 +7688,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" s="72">
       <c r="B23" s="43" t="n">
         <v>19</v>
       </c>
@@ -7923,7 +7704,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" s="72">
       <c r="B24" s="43" t="n">
         <v>20</v>
       </c>
@@ -7939,7 +7720,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" s="72">
       <c r="B25" s="43" t="n">
         <v>21</v>
       </c>
@@ -7955,7 +7736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="72">
       <c r="B26" s="43" t="n">
         <v>22</v>
       </c>
@@ -7971,7 +7752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" s="72">
       <c r="B27" s="43" t="n">
         <v>23</v>
       </c>
@@ -7987,7 +7768,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" s="72">
       <c r="B28" s="43" t="n">
         <v>24</v>
       </c>
@@ -8003,7 +7784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" s="72">
       <c r="B29" s="43" t="n">
         <v>25</v>
       </c>
@@ -8019,7 +7800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" s="72">
       <c r="B30" s="43" t="n">
         <v>26</v>
       </c>
@@ -8035,7 +7816,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" s="72">
       <c r="B31" s="43" t="n">
         <v>27</v>
       </c>
@@ -8051,7 +7832,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" s="72">
       <c r="B32" s="43" t="n">
         <v>28</v>
       </c>
@@ -8067,7 +7848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" s="72">
       <c r="B33" s="43" t="n">
         <v>29</v>
       </c>
@@ -8083,7 +7864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" s="72">
       <c r="B34" s="43" t="n">
         <v>30</v>
       </c>
@@ -8099,7 +7880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" s="72">
       <c r="B35" s="43" t="n">
         <v>31</v>
       </c>
@@ -8115,7 +7896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" s="72">
       <c r="B36" s="43" t="n">
         <v>32</v>
       </c>
@@ -8131,7 +7912,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" s="72">
       <c r="B37" s="43" t="n">
         <v>33</v>
       </c>
@@ -8147,7 +7928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" s="72">
       <c r="B38" s="43" t="n">
         <v>34</v>
       </c>
@@ -8163,7 +7944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" s="72">
       <c r="B39" s="43" t="n">
         <v>35</v>
       </c>
@@ -8179,7 +7960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" s="72">
       <c r="B40" s="43" t="n">
         <v>36</v>
       </c>
@@ -8195,7 +7976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" s="72">
       <c r="B41" s="43" t="n">
         <v>37</v>
       </c>
@@ -8211,7 +7992,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" s="72">
       <c r="B42" s="43" t="n">
         <v>38</v>
       </c>
@@ -8227,7 +8008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" s="72">
       <c r="B43" s="43" t="n">
         <v>39</v>
       </c>
@@ -8243,7 +8024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" s="72">
       <c r="B44" s="43" t="n">
         <v>40</v>
       </c>
@@ -8259,7 +8040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" s="72">
       <c r="B45" s="43" t="n">
         <v>41</v>
       </c>
@@ -8275,7 +8056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" s="72">
       <c r="B46" s="43" t="n">
         <v>42</v>
       </c>
@@ -8291,7 +8072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" s="72">
       <c r="B47" s="43" t="n">
         <v>43</v>
       </c>
@@ -8307,7 +8088,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" s="72">
       <c r="B48" s="43" t="n">
         <v>44</v>
       </c>
@@ -8323,7 +8104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" s="72">
       <c r="B49" s="43" t="n">
         <v>45</v>
       </c>

--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -2371,18 +2371,18 @@
           <t>Content</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="92" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
+      <c r="L3" s="92" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1" s="72">
       <c r="A4" s="5" t="n"/>
@@ -2399,11 +2399,12 @@
           <t>Initial draft</t>
         </is>
       </c>
-      <c r="L4" s="95" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L4" s="95" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="72">
       <c r="A5" s="5" t="n"/>
@@ -2420,11 +2421,12 @@
           <t>Package reward removed</t>
         </is>
       </c>
-      <c r="L5" s="99" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L5" s="99" t="n"/>
       <c r="M5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="72">
@@ -2442,11 +2444,12 @@
           <t>Past season UI — detailed description added</t>
         </is>
       </c>
-      <c r="L6" s="103" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L6" s="103" t="n"/>
       <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="72">
@@ -2464,11 +2467,12 @@
           <t>Required XP per level specified</t>
         </is>
       </c>
-      <c r="L7" s="103" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L7" s="103" t="n"/>
       <c r="M7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="72">
@@ -2486,11 +2490,12 @@
           <t>All mission types set to cumulative count</t>
         </is>
       </c>
-      <c r="L8" s="103" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L8" s="103" t="n"/>
       <c r="M8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="72">
@@ -2508,11 +2513,12 @@
           <t>Missions split into cumulative vs. quest-progress types</t>
         </is>
       </c>
-      <c r="L9" s="103" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L9" s="103" t="n"/>
       <c r="M9" s="6" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="72">
@@ -2530,11 +2536,12 @@
           <t>Bilibili ranking system content applied</t>
         </is>
       </c>
-      <c r="L10" s="103" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L10" s="103" t="n"/>
       <c r="M10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="72">
@@ -2552,11 +2559,12 @@
           <t>Cosmetic rewards (name tags, titles, profile skins) added to reward pool</t>
         </is>
       </c>
-      <c r="L11" s="103" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L11" s="103" t="n"/>
       <c r="M11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="72">
@@ -2574,11 +2582,12 @@
           <t>Access button changed</t>
         </is>
       </c>
-      <c r="L12" s="103" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L12" s="103" t="n"/>
       <c r="M12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="72">
@@ -2596,11 +2605,12 @@
           <t>HUD rank indicator feature added</t>
         </is>
       </c>
-      <c r="L13" s="103" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L13" s="103" t="n"/>
       <c r="M13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="72">
@@ -2618,11 +2628,12 @@
           <t>Unlock timing specified</t>
         </is>
       </c>
-      <c r="L14" s="103" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L14" s="103" t="n"/>
       <c r="M14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="72">
@@ -2640,11 +2651,12 @@
           <t>List updated; levels changed to 45 tiers; Pass XP halved</t>
         </is>
       </c>
-      <c r="L15" s="103" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L15" s="103" t="n"/>
       <c r="M15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="72">
@@ -2662,11 +2674,12 @@
           <t>Lv. 9, 19: Intermediate Gem Box ×3; Lv. 44: Advanced Skill Support Box ×5</t>
         </is>
       </c>
-      <c r="L16" s="103" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L16" s="103" t="n"/>
       <c r="M16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="72">
@@ -2684,11 +2697,12 @@
           <t>Stamina Potion removed from rank level rewards</t>
         </is>
       </c>
-      <c r="L17" s="103" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L17" s="103" t="n"/>
       <c r="M17" s="6" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="72">
@@ -2706,11 +2720,12 @@
           <t>UI updated; XML structure revised</t>
         </is>
       </c>
-      <c r="L18" s="103" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L18" s="103" t="n"/>
       <c r="M18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="72">
@@ -2728,11 +2743,12 @@
           <t>Mission list, Pass XP, and Pass reward list modified</t>
         </is>
       </c>
-      <c r="L19" s="103" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Jinho Ha</t>
         </is>
       </c>
+      <c r="L19" s="103" t="n"/>
       <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
@@ -6058,7 +6074,7 @@
     <row r="61" ht="16.5" customHeight="1" s="72">
       <c r="B61" s="39" t="inlineStr">
         <is>
-          <t>Silak's Mansion : Monster 500creatures Defeat</t>
+          <t>Mansion of Syllek : Monster 500creatures Defeat</t>
         </is>
       </c>
       <c r="C61" s="39" t="n">
@@ -6074,7 +6090,7 @@
     <row r="62" ht="16.5" customHeight="1" s="72">
       <c r="B62" s="39" t="inlineStr">
         <is>
-          <t>Burning Furnace : Monster 500creatures Defeat</t>
+          <t>Burning Forge : Monster 500creatures Defeat</t>
         </is>
       </c>
       <c r="C62" s="39" t="n">
@@ -6410,7 +6426,7 @@
     <row r="86" ht="16.5" customHeight="1" s="72">
       <c r="B86" s="39" t="inlineStr">
         <is>
-          <t>Silak's Mansion : Monster 1,000creatures Defeat</t>
+          <t>Mansion of Syllek : Monster 1,000creatures Defeat</t>
         </is>
       </c>
       <c r="C86" s="39" t="n">
@@ -6426,7 +6442,7 @@
     <row r="87" ht="16.5" customHeight="1" s="72">
       <c r="B87" s="39" t="inlineStr">
         <is>
-          <t>Burning Furnace : Monster 1,000creatures Defeat</t>
+          <t>Burning Forge : Monster 1,000creatures Defeat</t>
         </is>
       </c>
       <c r="C87" s="39" t="n">

--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -2332,7 +2332,8 @@
     <col width="8" customWidth="1" style="27" min="2" max="2"/>
     <col width="12" customWidth="1" style="27" min="3" max="3"/>
     <col width="75" customWidth="1" style="27" min="4" max="15"/>
-    <col width="18" customWidth="1" style="72" min="12" max="12"/>
+    <col width="18" customWidth="1" style="72" min="5" max="5"/>
+    <col width="8.43" customWidth="1" style="72" min="12" max="12"/>
     <col width="11.375" bestFit="1" customWidth="1" style="27" min="16" max="16"/>
     <col width="9" customWidth="1" style="27" min="17" max="16384"/>
   </cols>
@@ -2901,7 +2902,7 @@
       <c r="B6" s="9" t="n"/>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>- Encourages continuous player visits</t>
+          <t>- Encourages consistent player visits</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -2911,7 +2912,7 @@
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>- Provides means for players to intuitively understand their game progress</t>
+          <t>- Gives players an intuitive way to gauge their game progress</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
@@ -2921,7 +2922,7 @@
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>- Provides diverse cosmetics through Season Pass rewards to showcase to other players</t>
+          <t>- Offers diverse cosmetic rewards through the Season Pass to showcase to other players</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -5275,7 +5276,7 @@
     <row r="9" ht="16.5" customHeight="1" s="72">
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 1times Clear</t>
+          <t>Dark Temple 1× Clear</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
@@ -5291,7 +5292,7 @@
     <row r="10" ht="16.5" customHeight="1" s="72">
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 3times Clear</t>
+          <t>Dark Temple 3× Clear</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
@@ -5307,7 +5308,7 @@
     <row r="11" ht="16.5" customHeight="1" s="72">
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 5times Clear</t>
+          <t>Dark Temple 5× Clear</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
@@ -5323,7 +5324,7 @@
     <row r="12" ht="16.5" customHeight="1" s="72">
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 10times Complete</t>
+          <t xml:space="preserve"> Minute 10× Complete</t>
         </is>
       </c>
       <c r="C12" s="39" t="n">
@@ -5339,7 +5340,7 @@
     <row r="13" ht="16.5" customHeight="1" s="72">
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 30times Complete</t>
+          <t xml:space="preserve"> Minute 30× Complete</t>
         </is>
       </c>
       <c r="C13" s="39" t="n">
@@ -5355,7 +5356,7 @@
     <row r="14" ht="16.5" customHeight="1" s="72">
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 50times Complete</t>
+          <t xml:space="preserve"> Minute 50× Complete</t>
         </is>
       </c>
       <c r="C14" s="39" t="n">
@@ -5371,7 +5372,7 @@
     <row r="15" ht="16.5" customHeight="1" s="72">
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 1times Clear</t>
+          <t>Dungeon 1× Clear</t>
         </is>
       </c>
       <c r="C15" s="39" t="n">
@@ -5387,7 +5388,7 @@
     <row r="16" ht="16.5" customHeight="1" s="72">
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 5times Clear</t>
+          <t>Dungeon 5× Clear</t>
         </is>
       </c>
       <c r="C16" s="39" t="n">
@@ -5403,7 +5404,7 @@
     <row r="17" ht="16.5" customHeight="1" s="72">
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 10times Clear</t>
+          <t>Dungeon 10× Clear</t>
         </is>
       </c>
       <c r="C17" s="39" t="n">
@@ -5419,7 +5420,7 @@
     <row r="18" ht="16.5" customHeight="1" s="72">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 15times Clear</t>
+          <t>Dungeon 15× Clear</t>
         </is>
       </c>
       <c r="C18" s="39" t="n">
@@ -5531,7 +5532,7 @@
     <row r="25" ht="16.5" customHeight="1" s="72">
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 1times Summon</t>
+          <t>Star's Apostle 1× Summon</t>
         </is>
       </c>
       <c r="C25" s="39" t="n">
@@ -5547,7 +5548,7 @@
     <row r="26" ht="16.5" customHeight="1" s="72">
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 5times Summon</t>
+          <t>Star's Apostle 5× Summon</t>
         </is>
       </c>
       <c r="C26" s="39" t="n">
@@ -5563,7 +5564,7 @@
     <row r="27" ht="16.5" customHeight="1" s="72">
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 10times Summon</t>
+          <t>Star's Apostle 10× Summon</t>
         </is>
       </c>
       <c r="C27" s="39" t="n">
@@ -5579,7 +5580,7 @@
     <row r="28" ht="16.5" customHeight="1" s="72">
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 5times</t>
+          <t>Star's Apostle Level 5×</t>
         </is>
       </c>
       <c r="C28" s="39" t="n">
@@ -5595,7 +5596,7 @@
     <row r="29" ht="16.5" customHeight="1" s="72">
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 10times</t>
+          <t>Star's Apostle Level 10×</t>
         </is>
       </c>
       <c r="C29" s="39" t="n">
@@ -5659,7 +5660,7 @@
     <row r="33" ht="16.5" customHeight="1" s="72">
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>Field 10times Memoir</t>
+          <t>Field 10× Memoir</t>
         </is>
       </c>
       <c r="C33" s="39" t="n">
@@ -5675,7 +5676,7 @@
     <row r="34" ht="16.5" customHeight="1" s="72">
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>Field 30times Memoir</t>
+          <t>Field 30× Memoir</t>
         </is>
       </c>
       <c r="C34" s="39" t="n">
@@ -5691,7 +5692,7 @@
     <row r="35" ht="16.5" customHeight="1" s="72">
       <c r="B35" s="39" t="inlineStr">
         <is>
-          <t>Field 50times Memoir</t>
+          <t>Field 50× Memoir</t>
         </is>
       </c>
       <c r="C35" s="39" t="n">
@@ -5707,7 +5708,7 @@
     <row r="36" ht="16.5" customHeight="1" s="72">
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>Dimensional Gate 10times utilize</t>
+          <t>Dimensional Gate 10× utilize</t>
         </is>
       </c>
       <c r="C36" s="39" t="n">
@@ -5723,7 +5724,7 @@
     <row r="37" ht="16.5" customHeight="1" s="72">
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>※ Weekly EXP My/The 2500, Star's Apostle Summon 1times until if done 1500 Obtain Possible</t>
+          <t>※ Weekly EXP My/The 2500, Star's Apostle Summon 1× until if done 1500 Obtain Possible</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -5818,7 +5819,7 @@
     <row r="45" ht="16.5" customHeight="1" s="72">
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 8times Clear</t>
+          <t>Dark Temple 8× Clear</t>
         </is>
       </c>
       <c r="C45" s="39" t="n">
@@ -5834,7 +5835,7 @@
     <row r="46" ht="16.5" customHeight="1" s="72">
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 100times Complete</t>
+          <t xml:space="preserve"> Minute 100× Complete</t>
         </is>
       </c>
       <c r="C46" s="39" t="n">
@@ -5850,7 +5851,7 @@
     <row r="47" ht="16.5" customHeight="1" s="72">
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 20times Clear</t>
+          <t>Dungeon 20× Clear</t>
         </is>
       </c>
       <c r="C47" s="39" t="n">
@@ -5898,7 +5899,7 @@
     <row r="50" ht="16.5" customHeight="1" s="72">
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 30times Summon</t>
+          <t>Star's Apostle 30× Summon</t>
         </is>
       </c>
       <c r="C50" s="39" t="n">
@@ -5914,7 +5915,7 @@
     <row r="51" ht="16.5" customHeight="1" s="72">
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 50times Summon</t>
+          <t>Star's Apostle 50× Summon</t>
         </is>
       </c>
       <c r="C51" s="39" t="n">
@@ -5930,7 +5931,7 @@
     <row r="52" ht="16.5" customHeight="1" s="72">
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 50times</t>
+          <t>Star's Apostle Level 50×</t>
         </is>
       </c>
       <c r="C52" s="39" t="n">
@@ -5946,7 +5947,7 @@
     <row r="53" ht="16.5" customHeight="1" s="72">
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 100times</t>
+          <t>Star's Apostle Level 100×</t>
         </is>
       </c>
       <c r="C53" s="39" t="n">
@@ -6010,7 +6011,7 @@
     <row r="57" ht="16.5" customHeight="1" s="72">
       <c r="B57" s="39" t="inlineStr">
         <is>
-          <t>Field 100times Memoir</t>
+          <t>Field 100× Memoir</t>
         </is>
       </c>
       <c r="C57" s="39" t="n">
@@ -6186,7 +6187,7 @@
     <row r="71" ht="16.5" customHeight="1" s="72">
       <c r="B71" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 10times Clear</t>
+          <t>Dark Temple 10× Clear</t>
         </is>
       </c>
       <c r="C71" s="39" t="n">
@@ -6202,7 +6203,7 @@
     <row r="72" ht="16.5" customHeight="1" s="72">
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 200times Complete</t>
+          <t xml:space="preserve"> Minute 200× Complete</t>
         </is>
       </c>
       <c r="C72" s="39" t="n">
@@ -6218,7 +6219,7 @@
     <row r="73" ht="16.5" customHeight="1" s="72">
       <c r="B73" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 30times Clear</t>
+          <t>Dungeon 30× Clear</t>
         </is>
       </c>
       <c r="C73" s="39" t="n">
@@ -6266,7 +6267,7 @@
     <row r="76" ht="16.5" customHeight="1" s="72">
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 100times Summon</t>
+          <t>Star's Apostle 100× Summon</t>
         </is>
       </c>
       <c r="C76" s="39" t="n">
@@ -6314,7 +6315,7 @@
     <row r="79" ht="16.5" customHeight="1" s="72">
       <c r="B79" s="39" t="inlineStr">
         <is>
-          <t>Field 200times Memoir</t>
+          <t>Field 200× Memoir</t>
         </is>
       </c>
       <c r="C79" s="39" t="n">
@@ -7873,7 +7874,7 @@
       </c>
       <c r="D33" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CGrade/Tier Gem </t>
+          <t xml:space="preserve">CGrade Gem </t>
         </is>
       </c>
       <c r="E33" s="43" t="n">
@@ -7953,7 +7954,7 @@
       </c>
       <c r="D38" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">UCGrade/Tier Gem </t>
+          <t xml:space="preserve">UCGrade Gem </t>
         </is>
       </c>
       <c r="E38" s="43" t="n">
@@ -8049,7 +8050,7 @@
       </c>
       <c r="D44" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGrade/Tier Gem </t>
+          <t xml:space="preserve">RGrade Gem </t>
         </is>
       </c>
       <c r="E44" s="43" t="n">

--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -120,8 +120,19 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00AAAAAA"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +155,12 @@
       <patternFill patternType="solid">
         <fgColor theme="1"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2F2"/>
+        <bgColor rgb="00FFF2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -711,7 +728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -986,6 +1003,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2325,101 +2354,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="27" min="1" max="1"/>
     <col width="8" customWidth="1" style="27" min="2" max="2"/>
     <col width="12" customWidth="1" style="27" min="3" max="3"/>
     <col width="75" customWidth="1" style="27" min="4" max="15"/>
-    <col width="18" customWidth="1" style="72" min="5" max="5"/>
-    <col width="8.43" customWidth="1" style="72" min="12" max="12"/>
+    <col width="18" customWidth="1" style="72" min="12" max="12"/>
     <col width="11.375" bestFit="1" customWidth="1" style="27" min="16" max="16"/>
     <col width="9" customWidth="1" style="27" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="22" customHeight="1" s="72">
-      <c r="B2" s="91" t="inlineStr">
+    <row r="1" ht="25" customHeight="1" s="72">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="72"/>
+    <row r="3" ht="18" customHeight="1" s="72">
+      <c r="B3" s="91" t="inlineStr">
         <is>
           <t>Document History : Season Pass</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="72">
-      <c r="B3" s="92" t="inlineStr">
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="72">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C4" s="92" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D3" s="92" t="inlineStr">
+      <c r="D4" s="92" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="92" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" s="72">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="94" t="inlineStr">
-        <is>
-          <t>24.04.22</t>
-        </is>
-      </c>
-      <c r="D4" s="94" t="inlineStr">
-        <is>
-          <t>Initial draft</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
-      <c r="L4" s="95" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="92" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="72">
       <c r="A5" s="5" t="n"/>
-      <c r="B5" s="96" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="97" t="inlineStr">
-        <is>
-          <t>24.05.27</t>
-        </is>
-      </c>
-      <c r="D5" s="98" t="inlineStr">
-        <is>
-          <t>Package reward removed</t>
+      <c r="B5" s="93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="94" t="inlineStr">
+        <is>
+          <t>24.04.22</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
+        <is>
+          <t>Initial draft</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -2427,22 +2440,21 @@
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L5" s="99" t="n"/>
-      <c r="M5" s="6" t="n"/>
+      <c r="L5" s="95" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="72">
       <c r="A6" s="5" t="n"/>
-      <c r="B6" s="100" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="101" t="inlineStr">
-        <is>
-          <t>24.05.28</t>
-        </is>
-      </c>
-      <c r="D6" s="102" t="inlineStr">
-        <is>
-          <t>Past season UI — detailed description added</t>
+      <c r="B6" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="97" t="inlineStr">
+        <is>
+          <t>24.05.27</t>
+        </is>
+      </c>
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>Package reward removed</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -2450,22 +2462,22 @@
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L6" s="103" t="n"/>
+      <c r="L6" s="99" t="n"/>
       <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="72">
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="101" t="inlineStr">
         <is>
-          <t>24.05.29</t>
+          <t>24.05.28</t>
         </is>
       </c>
       <c r="D7" s="102" t="inlineStr">
         <is>
-          <t>Required XP per level specified</t>
+          <t>Past season UI — detailed description added</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -2479,7 +2491,7 @@
     <row r="8" ht="18" customHeight="1" s="72">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="101" t="inlineStr">
         <is>
@@ -2488,7 +2500,7 @@
       </c>
       <c r="D8" s="102" t="inlineStr">
         <is>
-          <t>All mission types set to cumulative count</t>
+          <t>Required XP per level specified</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -2502,16 +2514,16 @@
     <row r="9" ht="18" customHeight="1" s="72">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="101" t="inlineStr">
         <is>
-          <t>24.06.24</t>
+          <t>24.05.29</t>
         </is>
       </c>
       <c r="D9" s="102" t="inlineStr">
         <is>
-          <t>Missions split into cumulative vs. quest-progress types</t>
+          <t>All mission types set to cumulative count</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -2525,7 +2537,7 @@
     <row r="10" ht="18" customHeight="1" s="72">
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="101" t="inlineStr">
         <is>
@@ -2534,7 +2546,7 @@
       </c>
       <c r="D10" s="102" t="inlineStr">
         <is>
-          <t>Bilibili ranking system content applied</t>
+          <t>Missions split into cumulative vs. quest-progress types</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -2548,7 +2560,7 @@
     <row r="11" ht="18" customHeight="1" s="72">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="101" t="inlineStr">
         <is>
@@ -2557,7 +2569,7 @@
       </c>
       <c r="D11" s="102" t="inlineStr">
         <is>
-          <t>Cosmetic rewards (name tags, titles, profile skins) added to reward pool</t>
+          <t>Bilibili ranking system content applied</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -2571,16 +2583,16 @@
     <row r="12" ht="18" customHeight="1" s="72">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="101" t="inlineStr">
         <is>
-          <t>24.07.11</t>
+          <t>24.06.24</t>
         </is>
       </c>
       <c r="D12" s="102" t="inlineStr">
         <is>
-          <t>Access button changed</t>
+          <t>Cosmetic rewards (name tags, titles, profile skins) added to reward pool</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -2594,16 +2606,16 @@
     <row r="13" ht="18" customHeight="1" s="72">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="101" t="inlineStr">
         <is>
-          <t>24.07.15</t>
+          <t>24.07.11</t>
         </is>
       </c>
       <c r="D13" s="102" t="inlineStr">
         <is>
-          <t>HUD rank indicator feature added</t>
+          <t>Access button changed</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -2617,16 +2629,16 @@
     <row r="14" ht="18" customHeight="1" s="72">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="101" t="inlineStr">
         <is>
-          <t>24.07.22</t>
+          <t>24.07.15</t>
         </is>
       </c>
       <c r="D14" s="102" t="inlineStr">
         <is>
-          <t>Unlock timing specified</t>
+          <t>HUD rank indicator feature added</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -2640,16 +2652,16 @@
     <row r="15" ht="18" customHeight="1" s="72">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="101" t="inlineStr">
         <is>
-          <t>24.08.26</t>
+          <t>24.07.22</t>
         </is>
       </c>
       <c r="D15" s="102" t="inlineStr">
         <is>
-          <t>List updated; levels changed to 45 tiers; Pass XP halved</t>
+          <t>Unlock timing specified</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -2663,16 +2675,16 @@
     <row r="16" ht="18" customHeight="1" s="72">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="101" t="inlineStr">
         <is>
-          <t>24.08.27</t>
+          <t>24.08.26</t>
         </is>
       </c>
       <c r="D16" s="102" t="inlineStr">
         <is>
-          <t>Lv. 9, 19: Intermediate Gem Box ×3; Lv. 44: Advanced Skill Support Box ×5</t>
+          <t>List updated; levels changed to 45 tiers; Pass XP halved</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -2686,16 +2698,16 @@
     <row r="17" ht="18" customHeight="1" s="72">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="100" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="101" t="inlineStr">
         <is>
-          <t>24.09.05</t>
+          <t>24.08.27</t>
         </is>
       </c>
       <c r="D17" s="102" t="inlineStr">
         <is>
-          <t>Stamina Potion removed from rank level rewards</t>
+          <t>Lv. 9, 19: Intermediate Gem Box ×3; Lv. 44: Advanced Skill Support Box ×5</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -2709,16 +2721,16 @@
     <row r="18" ht="18" customHeight="1" s="72">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="101" t="inlineStr">
         <is>
-          <t>25.01.15</t>
+          <t>24.09.05</t>
         </is>
       </c>
       <c r="D18" s="102" t="inlineStr">
         <is>
-          <t>UI updated; XML structure revised</t>
+          <t>Stamina Potion removed from rank level rewards</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -2732,21 +2744,21 @@
     <row r="19" ht="18" customHeight="1" s="72">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="101" t="inlineStr">
         <is>
-          <t>25.05.30</t>
+          <t>25.01.15</t>
         </is>
       </c>
       <c r="D19" s="102" t="inlineStr">
         <is>
-          <t>Mission list, Pass XP, and Pass reward list modified</t>
+          <t>UI updated; XML structure revised</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>Jinho Ha</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
       <c r="L19" s="103" t="n"/>
@@ -2754,20 +2766,40 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="63" t="n"/>
-      <c r="D20" s="64" t="n"/>
-      <c r="L20" s="66" t="n"/>
+      <c r="B20" s="100" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="101" t="inlineStr">
+        <is>
+          <t>25.05.30</t>
+        </is>
+      </c>
+      <c r="D20" s="102" t="inlineStr">
+        <is>
+          <t>Mission list, Pass XP, and Pass reward list modified</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Jinho Ha</t>
+        </is>
+      </c>
+      <c r="L20" s="103" t="n"/>
       <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
-      <c r="L21" s="46" t="n"/>
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="62" t="n"/>
+      <c r="C21" s="63" t="n"/>
+      <c r="D21" s="64" t="n"/>
+      <c r="L21" s="66" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="D22" s="27" t="n"/>
+      <c r="B22" s="46" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
+      <c r="L22" s="46" t="n"/>
     </row>
     <row r="23">
       <c r="D23" s="27" t="n"/>
@@ -2829,7 +2861,13 @@
     <row r="42">
       <c r="D42" s="27" t="n"/>
     </row>
+    <row r="43">
+      <c r="D43" s="27" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
@@ -2842,7 +2880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F360"/>
+  <dimension ref="A1:H361"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="2.625" customWidth="1" style="9" min="1" max="1"/>
@@ -2861,50 +2899,47 @@
     <col width="2.625" customWidth="1" style="9" min="55" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="72"/>
-    <row r="2" ht="16.5" customHeight="1" s="72">
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-    </row>
+    <row r="1" ht="25" customHeight="1" s="72">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="72"/>
     <row r="3" ht="16.5" customHeight="1" s="72">
       <c r="B3" s="9" t="n"/>
-      <c r="C3" s="67" t="inlineStr">
-        <is>
-          <t>Season Pass</t>
-        </is>
-      </c>
+      <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="72">
       <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="67" t="inlineStr">
+        <is>
+          <t>Season Pass</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="72">
       <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>■ Design Intent</t>
-        </is>
-      </c>
+      <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="72">
       <c r="B6" s="9" t="n"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>- Encourages consistent player visits</t>
-        </is>
-      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>■ Design Intent</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
     </row>
@@ -2912,7 +2947,7 @@
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>- Gives players an intuitive way to gauge their game progress</t>
+          <t>- Encourages continuous player visits</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
@@ -2922,7 +2957,7 @@
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>- Offers diverse cosmetic rewards through the Season Pass to showcase to other players</t>
+          <t>- Provides means for players to intuitively understand their game progress</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -2930,43 +2965,46 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="72">
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="10" t="n"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>- Provides diverse cosmetics through Season Pass rewards to showcase to other players</t>
+        </is>
+      </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="72">
-      <c r="A10" s="68" t="n"/>
-      <c r="B10" s="69" t="n"/>
-      <c r="C10" s="70" t="inlineStr">
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="72">
+      <c r="A11" s="68" t="n"/>
+      <c r="B11" s="69" t="n"/>
+      <c r="C11" s="70" t="inlineStr">
         <is>
           <t>■ UI</t>
         </is>
       </c>
-      <c r="D10" s="69" t="n"/>
-      <c r="E10" s="69" t="n"/>
-      <c r="F10" s="69" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="72">
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
+      <c r="D11" s="69" t="n"/>
+      <c r="E11" s="69" t="n"/>
+      <c r="F11" s="69" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="72">
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>■ Access Method</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="72">
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>■ Access Method</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -2992,7 +3030,13 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
     </row>
-    <row r="17" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="17" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
     <row r="18" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="19" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="20" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3005,29 +3049,29 @@
     <row r="27" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="28" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="29" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="30" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C30" s="9" t="inlineStr">
+    <row r="30" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="31" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>- Main Menu → Click Rank button</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="32" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C32" s="9" t="inlineStr">
+    <row r="32" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="33" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>■ Unlock Timing</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C33" s="24" t="inlineStr">
+    <row r="34" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>- Quest: During Hermit's Forest [Talking Owl]</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="35" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="36" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="37" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3045,21 +3089,21 @@
     <row r="49" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="50" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="51" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="52" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C52" s="9" t="inlineStr">
+    <row r="52" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="53" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>■ UI Composition</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C53" s="10" t="inlineStr">
+    <row r="54" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>- Main Screen</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="55" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="56" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="57" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3082,167 +3126,133 @@
     <row r="74" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="75" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="76" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="77" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C77" s="29" t="inlineStr">
+    <row r="77" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="78" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>time(s)</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C78" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>Back</t>
-        </is>
-      </c>
-      <c r="E78" s="17" t="inlineStr">
-        <is>
-          <t>On click, go back</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C79" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>Pass Type</t>
-        </is>
-      </c>
-      <c r="E79" s="14" t="inlineStr">
-        <is>
-          <t>On click, display that pass type information on right screen.</t>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>On click, go back</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C80" s="86" t="n"/>
       <c r="D80" s="86" t="n"/>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>On click, display that pass type information on right screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C81" s="86" t="n"/>
+      <c r="D81" s="86" t="n"/>
+      <c r="E81" s="16" t="inlineStr">
         <is>
           <t>Season Reward Selectapplied state to UI Info Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C81" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D81" s="29" t="inlineStr">
-        <is>
-          <t>Pass Rank Icon</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
-        <is>
-          <t>Click when, Separate's Function None/N/A.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C82" s="86" t="n"/>
       <c r="D82" s="86" t="n"/>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>Click when, Separate's Function None/N/A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C83" s="86" t="n"/>
+      <c r="D83" s="86" t="n"/>
+      <c r="E83" s="16" t="inlineStr">
         <is>
           <t>Current Pass's Rank Icon to Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C83" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D83" s="29" t="inlineStr">
-        <is>
-          <t>Pass Name</t>
-        </is>
-      </c>
-      <c r="E83" s="14" t="inlineStr">
-        <is>
-          <t>Click when, Separate's Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C84" s="86" t="n"/>
       <c r="D84" s="86" t="n"/>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Click when, Separate's Function None/N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C85" s="86" t="n"/>
+      <c r="D85" s="86" t="n"/>
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>Current Pass's TRName Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C85" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D85" s="29" t="inlineStr">
-        <is>
-          <t>Pass Time Remaining</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>Click when, Separate's Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C86" s="86" t="n"/>
       <c r="D86" s="86" t="n"/>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>Click when, Separate's Function None/N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C87" s="86" t="n"/>
+      <c r="D87" s="86" t="n"/>
+      <c r="E87" s="16" t="inlineStr">
         <is>
           <t>Current Pass's Deadline Time DDDay HH when MMMinute to Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C87" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D87" s="29" t="inlineStr">
-        <is>
-          <t>Select Past Season</t>
-        </is>
-      </c>
-      <c r="E87" s="14" t="inlineStr">
-        <is>
-          <t>(#1) Click when, All season Dropdown to Display. Again Click when, Window close</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C88" s="87" t="n"/>
       <c r="D88" s="87" t="n"/>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>(#2) Click when, Corresponding season's Season Pass Display</t>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>(#1) Click when, All season Dropdown to Display. Again Click when, Window close</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C89" s="87" t="n"/>
       <c r="D89" s="87" t="n"/>
-      <c r="E89" s="26" t="n"/>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>(#2) Click when, Corresponding season's Season Pass Display</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C90" s="87" t="n"/>
       <c r="D90" s="87" t="n"/>
-      <c r="E90" s="15" t="n"/>
+      <c r="E90" s="26" t="n"/>
     </row>
     <row r="91" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C91" s="87" t="n"/>
@@ -3297,72 +3307,50 @@
     <row r="101" ht="13.5" customFormat="1" customHeight="1" s="9">
       <c r="C101" s="86" t="n"/>
       <c r="D101" s="86" t="n"/>
-      <c r="E101" s="16" t="inlineStr">
+      <c r="E101" s="15" t="n"/>
+    </row>
+    <row r="102" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C102" s="86" t="n"/>
+      <c r="D102" s="86" t="n"/>
+      <c r="E102" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Reward Claim Date case, Corresponding season UI in </t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C102" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D102" s="30" t="inlineStr">
-        <is>
-          <t>Progress Bar</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>(Achieve EXP / Corresponding season in Maximum to can present EXP) number Display</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C103" s="86" t="n"/>
-      <c r="D103" s="88" t="n"/>
-      <c r="E103" s="16" t="inlineStr">
+      <c r="D103" s="86" t="n"/>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>(Achieve EXP / Corresponding season in Maximum to can present EXP) number Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C104" s="86" t="n"/>
+      <c r="D104" s="88" t="n"/>
+      <c r="E104" s="16" t="inlineStr">
         <is>
           <t>Achieve Degree Progress Bar form to Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C104" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="D104" s="30" t="inlineStr">
-        <is>
-          <t>Season Reward Tab</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>Click when, Corresponding Button Highlight And Corresponding season's Season Reward List Below Display</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C105" s="86" t="n"/>
       <c r="D105" s="88" t="n"/>
-      <c r="E105" s="16" t="inlineStr">
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>Click when, Corresponding Button Highlight And Corresponding season's Season Reward List Below Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C106" s="86" t="n"/>
+      <c r="D106" s="88" t="n"/>
+      <c r="E106" s="16" t="inlineStr">
         <is>
           <t>Again Click when, Separate's None/N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C106" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="D106" s="30" t="inlineStr">
-        <is>
-          <t>Weekly Mission Tab</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>On click, highlight button and display weekly mission list below</t>
         </is>
       </c>
     </row>
@@ -3371,55 +3359,43 @@
       <c r="D107" s="89" t="n"/>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>Again Click when, Separate's None/N/A</t>
+          <t>On click, highlight button and display weekly mission list below</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C108" s="86" t="n"/>
       <c r="D108" s="88" t="n"/>
-      <c r="E108" s="16" t="inlineStr">
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>Again Click when, Separate's None/N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C109" s="86" t="n"/>
+      <c r="D109" s="88" t="n"/>
+      <c r="E109" s="16" t="inlineStr">
         <is>
           <t>one week reset DD HH displayed</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C109" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="D109" s="30" t="inlineStr">
-        <is>
-          <t>Season Mission Tab</t>
-        </is>
-      </c>
-      <c r="E109" s="15" t="inlineStr">
-        <is>
-          <t>Click when, Corresponding Button Highlight And Corresponding season's season Mission Info List Below Display</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C110" s="86" t="n"/>
       <c r="D110" s="88" t="n"/>
-      <c r="E110" s="16" t="inlineStr">
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Click when, Corresponding Button Highlight And Corresponding season's season Mission Info List Below Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C111" s="86" t="n"/>
+      <c r="D111" s="88" t="n"/>
+      <c r="E111" s="16" t="inlineStr">
         <is>
           <t>Again Click when, Separate's None/N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C111" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="D111" s="30" t="inlineStr">
-        <is>
-          <t>Challenge Mission Tab</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Mission Enter Impossible when, Click case</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3404,7 @@
       <c r="D112" s="89" t="n"/>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>-Corresponding Tab to Move Without System Message Display “{PassLevel_TRName} Unlock.”</t>
+          <t xml:space="preserve"> Mission Enter Impossible when, Click case</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3413,7 @@
       <c r="D113" s="89" t="n"/>
       <c r="E113" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mission Enter Possible when, Click case</t>
+          <t>-Corresponding Tab to Move Without System Message Display “{PassLevel_TRName} Unlock.”</t>
         </is>
       </c>
     </row>
@@ -3446,31 +3422,25 @@
       <c r="D114" s="89" t="n"/>
       <c r="E114" s="15" t="inlineStr">
         <is>
-          <t>-Corresponding Button Highlight And Corresponding season's Mission Info List Below Display</t>
+          <t xml:space="preserve"> Mission Enter Possible when, Click case</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C115" s="86" t="n"/>
       <c r="D115" s="88" t="n"/>
-      <c r="E115" s="16" t="inlineStr">
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>-Corresponding Button Highlight And Corresponding season's Mission Info List Below Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C116" s="86" t="n"/>
+      <c r="D116" s="88" t="n"/>
+      <c r="E116" s="16" t="inlineStr">
         <is>
           <t>-Again Click when, Separate's None/N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C116" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="D116" s="30" t="inlineStr">
-        <is>
-          <t>Claimed Season Reward</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>Already Claim Season Reward Display</t>
         </is>
       </c>
     </row>
@@ -3479,31 +3449,25 @@
       <c r="D117" s="89" t="n"/>
       <c r="E117" s="15" t="inlineStr">
         <is>
-          <t>Click when, Item tooltip Display</t>
+          <t>Already Claim Season Reward Display</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C118" s="86" t="n"/>
       <c r="D118" s="88" t="n"/>
-      <c r="E118" s="16" t="inlineStr">
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Click when, Item tooltip Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C119" s="86" t="n"/>
+      <c r="D119" s="88" t="n"/>
+      <c r="E119" s="16" t="inlineStr">
         <is>
           <t>Greyscale processing And green V Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C119" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="D119" s="30" t="inlineStr">
-        <is>
-          <t>Claimable Season Reward</t>
-        </is>
-      </c>
-      <c r="E119" s="15" t="inlineStr">
-        <is>
-          <t>Claim can present Season Reward Display</t>
         </is>
       </c>
     </row>
@@ -3512,52 +3476,54 @@
       <c r="D120" s="89" t="n"/>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>Click when, Item Claim After Claim Season Reward to Change Display</t>
+          <t>Claim can present Season Reward Display</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C121" s="86" t="n"/>
       <c r="D121" s="88" t="n"/>
-      <c r="E121" s="16" t="inlineStr">
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>Click when, Item Claim After Claim Season Reward to Change Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C122" s="86" t="n"/>
+      <c r="D122" s="88" t="n"/>
+      <c r="E122" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Item Reward Claim UI </t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C122" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D122" s="30" t="inlineStr">
-        <is>
-          <t>Unclaimed Season Reward</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="inlineStr">
-        <is>
-          <t>Claim can without Season Reward Display</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C123" s="86" t="n"/>
       <c r="D123" s="88" t="n"/>
-      <c r="E123" s="16" t="inlineStr">
+      <c r="E123" s="15" t="inlineStr">
+        <is>
+          <t>Claim can without Season Reward Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C124" s="86" t="n"/>
+      <c r="D124" s="88" t="n"/>
+      <c r="E124" s="16" t="inlineStr">
         <is>
           <t>Click when, Item tooltip Display</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="125" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C125" s="10" t="inlineStr">
+    <row r="125" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="126" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>- Each Mission Tab</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="127" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="128" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="129" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3581,203 +3547,167 @@
     <row r="147" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="148" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="149" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="150" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C150" s="29" t="inlineStr">
+    <row r="150" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="151" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C151" s="29" t="inlineStr">
         <is>
           <t>time(s)</t>
         </is>
       </c>
-      <c r="D150" s="29" t="inlineStr">
+      <c r="D151" s="29" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E150" s="29" t="inlineStr">
+      <c r="E151" s="29" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C151" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" s="29" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-      <c r="E151" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="152" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C152" s="87" t="n"/>
       <c r="D152" s="87" t="n"/>
-      <c r="E152" s="71" t="inlineStr">
-        <is>
-          <t>Corresponding Mission's TRName And Desc Display</t>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="153" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C153" s="86" t="n"/>
       <c r="D153" s="86" t="n"/>
-      <c r="E153" s="20" t="inlineStr">
+      <c r="E153" s="71" t="inlineStr">
+        <is>
+          <t>Corresponding Mission's TRName And Desc Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C154" s="86" t="n"/>
+      <c r="D154" s="86" t="n"/>
+      <c r="E154" s="20" t="inlineStr">
         <is>
           <t>(achieve / ) displayed</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C154" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D154" s="29" t="inlineStr">
-        <is>
-          <t>Reward Display</t>
-        </is>
-      </c>
-      <c r="E154" s="19" t="inlineStr">
-        <is>
-          <t>Corresponding Mission Achieve when, Obtaindoing Reward Display</t>
         </is>
       </c>
     </row>
     <row r="155" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C155" s="86" t="n"/>
       <c r="D155" s="86" t="n"/>
-      <c r="E155" s="20" t="inlineStr">
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>Corresponding Mission Achieve when, Obtaindoing Reward Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C156" s="86" t="n"/>
+      <c r="D156" s="86" t="n"/>
+      <c r="E156" s="20" t="inlineStr">
         <is>
           <t>Click when, Item tooltip Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C156" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D156" s="29" t="inlineStr">
-        <is>
-          <t>Claim Reward Button</t>
-        </is>
-      </c>
-      <c r="E156" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Corresponding Mission's Reward Obtain And Corresponding List Below to My Complete processing</t>
         </is>
       </c>
     </row>
     <row r="157" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C157" s="86" t="n"/>
       <c r="D157" s="86" t="n"/>
-      <c r="E157" s="20" t="inlineStr">
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Corresponding Mission's Reward Obtain And Corresponding List Below to My Complete processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C158" s="86" t="n"/>
+      <c r="D158" s="86" t="n"/>
+      <c r="E158" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Item Reward Claim UI </t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C158" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D158" s="29" t="inlineStr">
-        <is>
-          <t>Complete List</t>
-        </is>
-      </c>
-      <c r="E158" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="159" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C159" s="86" t="n"/>
       <c r="D159" s="86" t="n"/>
-      <c r="E159" s="20" t="inlineStr">
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Function None/N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C160" s="86" t="n"/>
+      <c r="D160" s="86" t="n"/>
+      <c r="E160" s="20" t="inlineStr">
         <is>
           <t>Corresponding List Greyscale processing, Reward Icon green V Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C160" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="D160" s="29" t="inlineStr">
-        <is>
-          <t>this week obtain possible EXP displayed</t>
-        </is>
-      </c>
-      <c r="E160" s="19" t="inlineStr">
-        <is>
-          <t>(achieve EXP / this week EXP) displayed</t>
         </is>
       </c>
     </row>
     <row r="161" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C161" s="87" t="n"/>
       <c r="D161" s="87" t="n"/>
-      <c r="E161" s="71" t="inlineStr">
-        <is>
-          <t>Achieve Degree Progress Bar form to Display</t>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>(achieve EXP / this week EXP) displayed</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C162" s="86" t="n"/>
       <c r="D162" s="86" t="n"/>
-      <c r="E162" s="20" t="inlineStr">
+      <c r="E162" s="71" t="inlineStr">
+        <is>
+          <t>Achieve Degree Progress Bar form to Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C163" s="86" t="n"/>
+      <c r="D163" s="86" t="n"/>
+      <c r="E163" s="20" t="inlineStr">
         <is>
           <t>Weekly Mission Tab in only Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C163" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D163" s="29" t="inlineStr">
-        <is>
-          <t>Claim All Button</t>
-        </is>
-      </c>
-      <c r="E163" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Claim Available All Reward time(s) Obtain</t>
         </is>
       </c>
     </row>
     <row r="164" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C164" s="87" t="n"/>
       <c r="D164" s="87" t="n"/>
-      <c r="E164" s="71" t="inlineStr">
-        <is>
-          <t>Claim Available Reward without case Greyscale processing</t>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Claim Available All Reward time(s) Obtain</t>
         </is>
       </c>
     </row>
     <row r="165" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C165" s="86" t="n"/>
       <c r="D165" s="86" t="n"/>
-      <c r="E165" s="20" t="inlineStr">
+      <c r="E165" s="71" t="inlineStr">
+        <is>
+          <t>Claim Available Reward without case Greyscale processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C166" s="86" t="n"/>
+      <c r="D166" s="86" t="n"/>
+      <c r="E166" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Claim Possible Reward without state in Click when,“Obtain Available Reward.”System Message </t>
         </is>
       </c>
     </row>
-    <row r="166" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="167" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C167" s="10" t="inlineStr">
+    <row r="167" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="168" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C168" s="10" t="inlineStr">
         <is>
           <t>- types applied season Display</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="169" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="170" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="171" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3796,79 +3726,69 @@
     <row r="184" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="185" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="186" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="187" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C187" s="29" t="inlineStr">
+    <row r="187" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="188" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C188" s="29" t="inlineStr">
         <is>
           <t>time(s)</t>
         </is>
       </c>
-      <c r="D187" s="29" t="inlineStr">
+      <c r="D188" s="29" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E187" s="29" t="inlineStr">
+      <c r="E188" s="29" t="inlineStr">
         <is>
           <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C188" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D188" s="29" t="inlineStr">
-        <is>
-          <t>Reward Claim Time</t>
-        </is>
-      </c>
-      <c r="E188" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="189" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C189" s="86" t="n"/>
       <c r="D189" s="86" t="n"/>
-      <c r="E189" s="20" t="inlineStr">
+      <c r="E189" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Function None/N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="224.25" customFormat="1" customHeight="1" s="9">
+      <c r="C190" s="86" t="n"/>
+      <c r="D190" s="86" t="n"/>
+      <c r="E190" s="20" t="inlineStr">
         <is>
           <t>Corresponding season's Reward Claim Available Date DDDay HH when MMMinute to Display</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="224.25" customFormat="1" customHeight="1" s="9">
-      <c r="C190" s="29" t="n">
+    <row r="191" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C191" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="D190" s="29" t="inlineStr">
+      <c r="D191" s="29" t="inlineStr">
         <is>
           <t>Tab Area</t>
         </is>
       </c>
-      <c r="E190" s="25" t="inlineStr">
+      <c r="E191" s="25" t="inlineStr">
         <is>
           <t>Weekly Mission Tab Remove
 season Mission, Mission Tab Click when Each Mission All Deactivate state to DisplayDone/Applied</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C191" s="23" t="n"/>
-      <c r="D191" s="23" t="n"/>
-      <c r="E191" s="18" t="n"/>
-    </row>
     <row r="192" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C192" s="10" t="inlineStr">
-        <is>
-          <t>- HUD</t>
-        </is>
-      </c>
+      <c r="C192" s="23" t="n"/>
       <c r="D192" s="23" t="n"/>
       <c r="E192" s="18" t="n"/>
     </row>
     <row r="193" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C193" s="23" t="n"/>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>- HUD</t>
+        </is>
+      </c>
       <c r="D193" s="23" t="n"/>
       <c r="E193" s="18" t="n"/>
     </row>
@@ -3948,11 +3868,9 @@
       <c r="E208" s="18" t="n"/>
     </row>
     <row r="209" ht="16.5" customHeight="1" s="72">
-      <c r="B209" s="9" t="n"/>
       <c r="C209" s="23" t="n"/>
       <c r="D209" s="23" t="n"/>
       <c r="E209" s="18" t="n"/>
-      <c r="F209" s="9" t="n"/>
     </row>
     <row r="210" ht="16.5" customHeight="1" s="72">
       <c r="B210" s="9" t="n"/>
@@ -3963,11 +3881,7 @@
     </row>
     <row r="211" ht="16.5" customHeight="1" s="72">
       <c r="B211" s="9" t="n"/>
-      <c r="C211" s="24" t="inlineStr">
-        <is>
-          <t>- Screen Below Current season's Rank Icon Display</t>
-        </is>
-      </c>
+      <c r="C211" s="23" t="n"/>
       <c r="D211" s="23" t="n"/>
       <c r="E211" s="18" t="n"/>
       <c r="F211" s="9" t="n"/>
@@ -3976,7 +3890,7 @@
       <c r="B212" s="9" t="n"/>
       <c r="C212" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Button to Click also Separate's Function None/N/A</t>
+          <t>- Screen Below Current season's Rank Icon Display</t>
         </is>
       </c>
       <c r="D212" s="23" t="n"/>
@@ -3987,7 +3901,7 @@
       <c r="B213" s="9" t="n"/>
       <c r="C213" s="24" t="inlineStr">
         <is>
-          <t>- , area</t>
+          <t xml:space="preserve"> - Button to Click also Separate's Function None/N/A</t>
         </is>
       </c>
       <c r="D213" s="23" t="n"/>
@@ -3996,57 +3910,57 @@
     </row>
     <row r="214" ht="16.5" customHeight="1" s="72">
       <c r="B214" s="9" t="n"/>
-      <c r="C214" s="23" t="n"/>
+      <c r="C214" s="24" t="inlineStr">
+        <is>
+          <t>- , area</t>
+        </is>
+      </c>
       <c r="D214" s="23" t="n"/>
       <c r="E214" s="18" t="n"/>
       <c r="F214" s="9" t="n"/>
     </row>
     <row r="215" ht="16.5" customHeight="1" s="72">
-      <c r="A215" s="68" t="n"/>
-      <c r="B215" s="69" t="n"/>
-      <c r="C215" s="70" t="inlineStr">
+      <c r="B215" s="9" t="n"/>
+      <c r="C215" s="23" t="n"/>
+      <c r="D215" s="23" t="n"/>
+      <c r="E215" s="18" t="n"/>
+      <c r="F215" s="9" t="n"/>
+    </row>
+    <row r="216" ht="16.5" customHeight="1" s="72">
+      <c r="A216" s="68" t="n"/>
+      <c r="B216" s="69" t="n"/>
+      <c r="C216" s="70" t="inlineStr">
         <is>
           <t>■ Details</t>
         </is>
       </c>
-      <c r="D215" s="69" t="n"/>
-      <c r="E215" s="69" t="n"/>
-      <c r="F215" s="69" t="n"/>
-    </row>
-    <row r="216" ht="16.5" customHeight="1" s="72">
-      <c r="B216" s="9" t="n"/>
-      <c r="C216" s="9" t="inlineStr">
-        <is>
-          <t>※ Current Season Pass document reflects ranking system requested by Bilibili.</t>
-        </is>
-      </c>
-      <c r="D216" s="9" t="n"/>
-      <c r="E216" s="9" t="n"/>
-      <c r="F216" s="9" t="n"/>
+      <c r="D216" s="69" t="n"/>
+      <c r="E216" s="69" t="n"/>
+      <c r="F216" s="69" t="n"/>
     </row>
     <row r="217" ht="16.5" customHeight="1" s="72">
       <c r="B217" s="9" t="n"/>
-      <c r="C217" s="9" t="n"/>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>※ Current Season Pass document reflects ranking system requested by Bilibili.</t>
+        </is>
+      </c>
       <c r="D217" s="9" t="n"/>
       <c r="E217" s="9" t="n"/>
       <c r="F217" s="9" t="n"/>
     </row>
     <row r="218" ht="16.5" customHeight="1" s="72">
       <c r="B218" s="9" t="n"/>
-      <c r="C218" s="9" t="inlineStr">
-        <is>
-          <t>■ Season and Mission Structure</t>
-        </is>
-      </c>
+      <c r="C218" s="9" t="n"/>
       <c r="D218" s="9" t="n"/>
       <c r="E218" s="9" t="n"/>
       <c r="F218" s="9" t="n"/>
     </row>
     <row r="219" ht="16.5" customHeight="1" s="72">
       <c r="B219" s="9" t="n"/>
-      <c r="C219" s="10" t="inlineStr">
-        <is>
-          <t>- Each pass activates as a season for a set duration</t>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>■ Season and Mission Structure</t>
         </is>
       </c>
       <c r="D219" s="9" t="n"/>
@@ -4057,7 +3971,7 @@
       <c r="B220" s="9" t="n"/>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>→ Start and end of all periods based on specified date server region time 06:00</t>
+          <t>- Each pass activates as a season for a set duration</t>
         </is>
       </c>
       <c r="D220" s="9" t="n"/>
@@ -4068,7 +3982,7 @@
       <c r="B221" s="9" t="n"/>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>- During season progression, complete weekly, season, and challenge missions to earn pass XP and levels</t>
+          <t>→ Start and end of all periods based on specified date server region time 06:00</t>
         </is>
       </c>
       <c r="D221" s="9" t="n"/>
@@ -4077,9 +3991,9 @@
     </row>
     <row r="222" ht="16.5" customHeight="1" s="72">
       <c r="B222" s="9" t="n"/>
-      <c r="C222" s="9" t="inlineStr">
-        <is>
-          <t>→ Weekly missions: Reset each week with weekly XP limit</t>
+      <c r="C222" s="10" t="inlineStr">
+        <is>
+          <t>- During season progression, complete weekly, season, and challenge missions to earn pass XP and levels</t>
         </is>
       </c>
       <c r="D222" s="9" t="n"/>
@@ -4090,7 +4004,7 @@
       <c r="B223" s="9" t="n"/>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>→ Season missions: Completable until season ends</t>
+          <t>→ Weekly missions: Reset each week with weekly XP limit</t>
         </is>
       </c>
       <c r="D223" s="9" t="n"/>
@@ -4101,7 +4015,7 @@
       <c r="B224" s="9" t="n"/>
       <c r="C224" s="9" t="inlineStr">
         <is>
-          <t>→ Challenge missions: Revealed when reaching specific pass level</t>
+          <t>→ Season missions: Completable until season ends</t>
         </is>
       </c>
       <c r="D224" s="9" t="n"/>
@@ -4109,237 +4023,232 @@
       <c r="F224" s="9" t="n"/>
     </row>
     <row r="225" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="B225" s="9" t="n"/>
       <c r="C225" s="9" t="inlineStr">
         <is>
+          <t>→ Challenge missions: Revealed when reaching specific pass level</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="n"/>
+      <c r="E225" s="9" t="n"/>
+      <c r="F225" s="9" t="n"/>
+    </row>
+    <row r="226" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C226" s="9" t="inlineStr">
+        <is>
           <t>→ For cumulative missions, progress counts even before challenge mission appears</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C226" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
     <row r="227" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C227" s="10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C228" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve"> ● Cumulative</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C228" s="9" t="inlineStr">
-        <is>
-          <t>) composition , 300 , Challenge Mission , 300/1,000</t>
         </is>
       </c>
     </row>
     <row r="229" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Weekly Mission : Shard 10 use</t>
+          <t>) composition , 300 , Challenge Mission , 300/1,000</t>
         </is>
       </c>
     </row>
     <row r="230" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> season Mission : Shard 100 use</t>
+          <t xml:space="preserve"> Weekly Mission : Shard 10 use</t>
         </is>
       </c>
     </row>
     <row r="231" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C231" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve"> season Mission : Shard 100 use</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C232" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Mission : Shard 1,000 use</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C232" s="10" t="inlineStr">
+    <row r="233" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C233" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> ● Quest Progress when Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C233" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> when) Below and as follows Composition when, Weekly Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
         </is>
       </c>
     </row>
     <row r="234" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Weekly Mission : Monster 10creatures Defeat</t>
+          <t xml:space="preserve"> when) Below and as follows Composition when, Weekly Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
         </is>
       </c>
     </row>
     <row r="235" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> season Mission : Monster 100creatures Defeat</t>
+          <t xml:space="preserve"> Weekly Mission : Monster 10creatures Defeat</t>
         </is>
       </c>
     </row>
     <row r="236" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mission : Monster 1,000creatures Defeat</t>
+          <t xml:space="preserve"> season Mission : Monster 100creatures Defeat</t>
         </is>
       </c>
     </row>
     <row r="237" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C237" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Mission : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C238" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">※ Each Mission's Type according to 's after Cumulative, Quest Progress when Count Select </t>
         </is>
       </c>
     </row>
-    <row r="238" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="239" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C239" s="9" t="inlineStr">
+    <row r="239" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="240" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C240" s="9" t="inlineStr">
         <is>
           <t>■ Rewards</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C240" s="10" t="inlineStr">
-        <is>
-          <t>- One season reward granted upon reaching each pass level</t>
         </is>
       </c>
     </row>
     <row r="241" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>- Rewards can include premium currency, exclusive name tags, titles, profile skins, and cosmetics</t>
+          <t>- One season reward granted upon reaching each pass level</t>
         </is>
       </c>
     </row>
     <row r="242" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Reward's 's after Modify Possible</t>
+          <t>- Rewards can include premium currency, exclusive name tags, titles, profile skins, and cosmetics</t>
         </is>
       </c>
     </row>
     <row r="243" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>- Pass XP and rewards granted upon completing each mission</t>
+          <t xml:space="preserve"> → Reward's 's after Modify Possible</t>
         </is>
       </c>
     </row>
     <row r="244" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>- All rewards obtained by clicking their icon</t>
+          <t>- Pass XP and rewards granted upon completing each mission</t>
         </is>
       </c>
     </row>
     <row r="245" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → through Providedoing case None/N/A</t>
+          <t>- All rewards obtained by clicking their icon</t>
         </is>
       </c>
     </row>
     <row r="246" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C246" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve"> → through Providedoing case None/N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C247" s="10" t="inlineStr">
+        <is>
           <t>- Unclaimed rewards can be collected for a period after season ends</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C247" s="9" t="inlineStr">
-        <is>
-          <t>→ Missions cannot be completed after season ends</t>
         </is>
       </c>
     </row>
     <row r="248" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C248" s="9" t="inlineStr">
         <is>
-          <t>→ Weekly mission rewards and progress reset at season end</t>
+          <t>→ Missions cannot be completed after season ends</t>
         </is>
       </c>
     </row>
     <row r="249" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C249" s="9" t="inlineStr">
         <is>
+          <t>→ Weekly mission rewards and progress reset at season end</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C250" s="9" t="inlineStr">
+        <is>
           <t>→ If pass levels up from claiming already-completed season/challenge mission rewards, season rewards can be claimed</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C250" s="10" t="inlineStr">
+    <row r="251" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C251" s="10" t="inlineStr">
         <is>
           <t>→ If reward collection period passes after season ends, no rewards can be claimed</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="252" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C252" s="9" t="inlineStr">
+    <row r="252" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="253" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C253" s="9" t="inlineStr">
         <is>
           <t>■ Season Rank</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C253" s="10" t="inlineStr">
+    <row r="254" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C254" s="10" t="inlineStr">
         <is>
           <t>- Divided into 9 total stages by season level range. Icon and number change in UI each rank increase</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C254" s="28" t="inlineStr">
+    <row r="255" ht="66.75" customFormat="1" customHeight="1" s="9">
+      <c r="C255" s="28" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D254" s="28" t="inlineStr">
+      <c r="D255" s="28" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E254" s="28" t="inlineStr">
+      <c r="E255" s="28" t="inlineStr">
         <is>
           <t>Icon</t>
         </is>
       </c>
-      <c r="F254" s="21" t="inlineStr">
+      <c r="F255" s="21" t="inlineStr">
         <is>
           <t>Level Range</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="66.75" customFormat="1" customHeight="1" s="9">
-      <c r="C255" s="22" t="n">
+    <row r="256" ht="66.75" customFormat="1" customHeight="1" s="9">
+      <c r="C256" s="22" t="n">
         <v>1</v>
-      </c>
-      <c r="D255" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E255" s="21" t="n"/>
-      <c r="F255" s="28" t="inlineStr">
-        <is>
-          <t>1 ~ 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="66.75" customFormat="1" customHeight="1" s="9">
-      <c r="C256" s="28" t="n">
-        <v>2</v>
       </c>
       <c r="D256" s="21" t="inlineStr">
         <is>
@@ -4349,143 +4258,158 @@
       <c r="E256" s="21" t="n"/>
       <c r="F256" s="28" t="inlineStr">
         <is>
-          <t>10 ~ 17</t>
+          <t>1 ~ 9</t>
         </is>
       </c>
     </row>
     <row r="257" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C257" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D257" s="21" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E257" s="21" t="n"/>
       <c r="F257" s="28" t="inlineStr">
         <is>
-          <t>18 ~ 24</t>
+          <t>10 ~ 17</t>
         </is>
       </c>
     </row>
     <row r="258" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C258" s="28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D258" s="21" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="E258" s="21" t="n"/>
       <c r="F258" s="28" t="inlineStr">
         <is>
-          <t>25 ~ 30</t>
+          <t>18 ~ 24</t>
         </is>
       </c>
     </row>
     <row r="259" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C259" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D259" s="21" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="E259" s="21" t="n"/>
       <c r="F259" s="28" t="inlineStr">
         <is>
-          <t>31 ~ 35</t>
+          <t>25 ~ 30</t>
         </is>
       </c>
     </row>
     <row r="260" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C260" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D260" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="E260" s="21" t="n"/>
       <c r="F260" s="28" t="inlineStr">
         <is>
-          <t>36 ~ 39</t>
+          <t>31 ~ 35</t>
         </is>
       </c>
     </row>
     <row r="261" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C261" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D261" s="21" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E261" s="21" t="n"/>
       <c r="F261" s="28" t="inlineStr">
         <is>
-          <t>40 ~ 42</t>
+          <t>36 ~ 39</t>
         </is>
       </c>
     </row>
     <row r="262" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C262" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D262" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> That/I</t>
+          <t>Grandmaster</t>
         </is>
       </c>
       <c r="E262" s="21" t="n"/>
       <c r="F262" s="28" t="inlineStr">
         <is>
-          <t>43 ~ 44</t>
+          <t>40 ~ 42</t>
         </is>
       </c>
     </row>
     <row r="263" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C263" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D263" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> That/I</t>
+        </is>
+      </c>
+      <c r="E263" s="21" t="n"/>
+      <c r="F263" s="28" t="inlineStr">
+        <is>
+          <t>43 ~ 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C264" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="D263" s="21" t="inlineStr">
+      <c r="D264" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"> before</t>
         </is>
       </c>
-      <c r="E263" s="21" t="n"/>
-      <c r="F263" s="28" t="n">
+      <c r="E264" s="21" t="n"/>
+      <c r="F264" s="28" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="264" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="265" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C265" s="9" t="inlineStr">
+    <row r="265" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="266" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C266" s="9" t="inlineStr">
         <is>
           <t>■ XML</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C266" s="10" t="inlineStr">
+    <row r="267" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C267" s="10" t="inlineStr">
         <is>
           <t>- Pass.xml</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C267" s="9" t="inlineStr">
+    <row r="268" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C268" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> → Date, Season Reward Content, Weekly, season, Mission Correspondingdoing Quest ID input</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="269" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="270" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="271" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -4506,13 +4430,7 @@
     <row r="286" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="287" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="288" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="289" ht="16.5" customHeight="1" s="72">
-      <c r="B289" s="9" t="n"/>
-      <c r="C289" s="9" t="n"/>
-      <c r="D289" s="9" t="n"/>
-      <c r="E289" s="9" t="n"/>
-      <c r="F289" s="9" t="n"/>
-    </row>
+    <row r="289" ht="16.5" customHeight="1" s="72"/>
     <row r="290" ht="16.5" customHeight="1" s="72">
       <c r="B290" s="9" t="n"/>
       <c r="C290" s="9" t="n"/>
@@ -4584,39 +4502,26 @@
       <c r="F299" s="9" t="n"/>
     </row>
     <row r="300" ht="16.5" customHeight="1" s="72">
-      <c r="B300" s="28" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C300" s="90" t="n"/>
-      <c r="D300" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E300" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="B300" s="9" t="n"/>
+      <c r="D300" s="9" t="n"/>
+      <c r="E300" s="9" t="n"/>
       <c r="F300" s="9" t="n"/>
     </row>
     <row r="301" ht="16.5" customHeight="1" s="72">
       <c r="B301" s="28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C301" s="90" t="n"/>
       <c r="D301" s="28" t="inlineStr">
         <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="E301" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E301" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
       <c r="F301" s="9" t="n"/>
@@ -4624,18 +4529,18 @@
     <row r="302" ht="16.5" customHeight="1" s="72">
       <c r="B302" s="28" t="inlineStr">
         <is>
-          <t>TRName</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C302" s="90" t="n"/>
       <c r="D302" s="28" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E302" s="21" t="inlineStr">
         <is>
-          <t>Corresponding season's Name</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F302" s="9" t="n"/>
@@ -4643,18 +4548,18 @@
     <row r="303" ht="16.5" customHeight="1" s="72">
       <c r="B303" s="28" t="inlineStr">
         <is>
-          <t>ScheduleID</t>
+          <t>TRName</t>
         </is>
       </c>
       <c r="C303" s="90" t="n"/>
       <c r="D303" s="28" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E303" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corresponding season's Day Schedule.xml's ID and matching when Day </t>
+          <t>Corresponding season's Name</t>
         </is>
       </c>
       <c r="F303" s="9" t="n"/>
@@ -4662,7 +4567,7 @@
     <row r="304" ht="16.5" customHeight="1" s="72">
       <c r="B304" s="28" t="inlineStr">
         <is>
-          <t>RewardScheduleID</t>
+          <t>ScheduleID</t>
         </is>
       </c>
       <c r="C304" s="90" t="n"/>
@@ -4673,7 +4578,7 @@
       </c>
       <c r="E304" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corresponding season's Reward Obtain Possible Schedule.xml's ID and matching when Day </t>
+          <t xml:space="preserve">Corresponding season's Day Schedule.xml's ID and matching when Day </t>
         </is>
       </c>
       <c r="F304" s="9" t="n"/>
@@ -4681,16 +4586,35 @@
     <row r="305" ht="134.25" customHeight="1" s="72">
       <c r="B305" s="28" t="inlineStr">
         <is>
+          <t>RewardScheduleID</t>
+        </is>
+      </c>
+      <c r="C305" s="90" t="n"/>
+      <c r="D305" s="28" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E305" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corresponding season's Reward Obtain Possible Schedule.xml's ID and matching when Day </t>
+        </is>
+      </c>
+      <c r="F305" s="9" t="n"/>
+    </row>
+    <row r="306" ht="85.5" customHeight="1" s="72">
+      <c r="B306" s="28" t="inlineStr">
+        <is>
           <t>Mission</t>
         </is>
       </c>
-      <c r="C305" s="90" t="n"/>
-      <c r="D305" s="21" t="inlineStr">
+      <c r="C306" s="90" t="n"/>
+      <c r="D306" s="21" t="inlineStr">
         <is>
           <t>String, Int</t>
         </is>
       </c>
-      <c r="E305" s="13" t="inlineStr">
+      <c r="E306" s="13" t="inlineStr">
         <is>
           <t>Repeat range and EXP cap for Weekly, Seasonal, and Challenge missions. Enter the linked Quest ID.
 - PassMission
@@ -4704,21 +4628,21 @@
 - Quest: Quest ID for the mission</t>
         </is>
       </c>
-      <c r="F305" s="9" t="n"/>
-    </row>
-    <row r="306" ht="85.5" customHeight="1" s="72">
-      <c r="B306" s="29" t="inlineStr">
+      <c r="F306" s="9" t="n"/>
+    </row>
+    <row r="307" ht="16.5" customHeight="1" s="72">
+      <c r="B307" s="29" t="inlineStr">
         <is>
           <t>RewardByLevel</t>
         </is>
       </c>
-      <c r="C306" s="90" t="n"/>
-      <c r="D306" s="21" t="inlineStr">
+      <c r="C307" s="90" t="n"/>
+      <c r="D307" s="21" t="inlineStr">
         <is>
           <t>String, Int</t>
         </is>
       </c>
-      <c r="E306" s="13" t="inlineStr">
+      <c r="E307" s="13" t="inlineStr">
         <is>
           <t>season Level per Reward Content input
 -ID : season Level
@@ -4728,31 +4652,20 @@
  → Count : Providedoing Item's can input</t>
         </is>
       </c>
-      <c r="F306" s="9" t="n"/>
-    </row>
-    <row r="307" ht="16.5" customHeight="1" s="72">
-      <c r="B307" s="9" t="n"/>
-      <c r="C307" s="9" t="n"/>
-      <c r="D307" s="9" t="n"/>
-      <c r="E307" s="18" t="n"/>
       <c r="F307" s="9" t="n"/>
     </row>
     <row r="308" ht="16.5" customHeight="1" s="72">
       <c r="B308" s="9" t="n"/>
-      <c r="C308" s="10" t="inlineStr">
-        <is>
-          <t>- Quest_Pass.xml</t>
-        </is>
-      </c>
+      <c r="C308" s="9" t="n"/>
       <c r="D308" s="9" t="n"/>
       <c r="E308" s="18" t="n"/>
       <c r="F308" s="9" t="n"/>
     </row>
     <row r="309" ht="16.5" customHeight="1" s="72">
       <c r="B309" s="9" t="n"/>
-      <c r="C309" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> → Each Mission Content's Quest Data input</t>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>- Quest_Pass.xml</t>
         </is>
       </c>
       <c r="D309" s="9" t="n"/>
@@ -4763,7 +4676,7 @@
       <c r="B310" s="9" t="n"/>
       <c r="C310" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Achievement, Always's and Same Data Structure use</t>
+          <t xml:space="preserve"> → Each Mission Content's Quest Data input</t>
         </is>
       </c>
       <c r="D310" s="9" t="n"/>
@@ -4774,7 +4687,7 @@
       <c r="B311" s="9" t="n"/>
       <c r="C311" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  → Match the ID value in this data to Pass.xml to determine whether the quest is Weekly, Seasonal, or Challenge.</t>
+          <t xml:space="preserve"> → Achievement, Always's and Same Data Structure use</t>
         </is>
       </c>
       <c r="D311" s="9" t="n"/>
@@ -4783,7 +4696,11 @@
     </row>
     <row r="312" ht="16.5" customHeight="1" s="72">
       <c r="B312" s="9" t="n"/>
-      <c r="C312" s="9" t="n"/>
+      <c r="C312" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Match the ID value in this data to Pass.xml to determine whether the quest is Weekly, Seasonal, or Challenge.</t>
+        </is>
+      </c>
       <c r="D312" s="9" t="n"/>
       <c r="E312" s="18" t="n"/>
       <c r="F312" s="9" t="n"/>
@@ -4845,7 +4762,11 @@
       <c r="F320" s="9" t="n"/>
     </row>
     <row r="321" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="B321" s="9" t="n"/>
+      <c r="C321" s="9" t="n"/>
+      <c r="D321" s="9" t="n"/>
       <c r="E321" s="18" t="n"/>
+      <c r="F321" s="9" t="n"/>
     </row>
     <row r="322" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="E322" s="18" t="n"/>
@@ -4875,22 +4796,22 @@
       <c r="E330" s="18" t="n"/>
     </row>
     <row r="331" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C331" s="10" t="inlineStr">
+      <c r="E331" s="18" t="n"/>
+    </row>
+    <row r="332" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C332" s="10" t="inlineStr">
         <is>
           <t>- PassLevel.xml</t>
         </is>
       </c>
-      <c r="E331" s="18" t="n"/>
-    </row>
-    <row r="332" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C332" s="9" t="inlineStr">
+      <c r="E332" s="18" t="n"/>
+    </row>
+    <row r="333" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C333" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> → Each Level Display Icon input</t>
         </is>
       </c>
-      <c r="E332" s="18" t="n"/>
-    </row>
-    <row r="333" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="E333" s="18" t="n"/>
     </row>
     <row r="334" ht="16.5" customFormat="1" customHeight="1" s="9">
@@ -4918,110 +4839,110 @@
       <c r="E341" s="18" t="n"/>
     </row>
     <row r="342" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C342" s="28" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D342" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E342" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="E342" s="18" t="n"/>
     </row>
     <row r="343" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C343" s="28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D343" s="28" t="inlineStr">
         <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="E343" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E343" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="344" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C344" s="28" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D344" s="28" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Int</t>
         </is>
       </c>
       <c r="E344" s="21" t="inlineStr">
         <is>
-          <t>Corresponding Level's Name</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="345" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C345" s="28" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D345" s="28" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E345" s="21" t="inlineStr">
+        <is>
+          <t>Corresponding Level's Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C346" s="28" t="inlineStr">
+        <is>
           <t>TRName</t>
         </is>
       </c>
-      <c r="D345" s="28" t="inlineStr">
+      <c r="D346" s="28" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="E345" s="21" t="inlineStr">
+      <c r="E346" s="21" t="inlineStr">
         <is>
           <t>Corresponding Level's TRName</t>
         </is>
       </c>
     </row>
-    <row r="346" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C346" s="21" t="inlineStr">
+    <row r="347" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C347" s="21" t="inlineStr">
         <is>
           <t>SymbolImage</t>
         </is>
       </c>
-      <c r="D346" s="28" t="inlineStr">
+      <c r="D347" s="28" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="E346" s="21" t="inlineStr">
+      <c r="E347" s="21" t="inlineStr">
         <is>
           <t>Corresponding Level in Display Icon Image Name input</t>
         </is>
       </c>
     </row>
-    <row r="347" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="E347" s="18" t="n"/>
-    </row>
     <row r="348" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C348" s="10" t="inlineStr">
+      <c r="E348" s="18" t="n"/>
+    </row>
+    <row r="349" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C349" s="10" t="inlineStr">
         <is>
           <t>- PassEXP.xml</t>
         </is>
       </c>
-      <c r="E348" s="18" t="n"/>
-    </row>
-    <row r="349" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C349" s="9" t="inlineStr">
+      <c r="E349" s="18" t="n"/>
+    </row>
+    <row r="350" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C350" s="9" t="inlineStr">
         <is>
           <t>EXP enter</t>
         </is>
       </c>
-      <c r="E349" s="18" t="n"/>
-    </row>
-    <row r="350" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="E350" s="18" t="n"/>
     </row>
     <row r="351" ht="16.5" customFormat="1" customHeight="1" s="9">
@@ -5046,58 +4967,61 @@
       <c r="E357" s="18" t="n"/>
     </row>
     <row r="358" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C358" s="28" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D358" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E358" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="E358" s="18" t="n"/>
     </row>
     <row r="359" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C359" s="28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D359" s="28" t="inlineStr">
         <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="E359" s="21" t="inlineStr">
-        <is>
-          <t>Each season Level</t>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E359" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="360" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C360" s="28" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D360" s="28" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E360" s="21" t="inlineStr">
+        <is>
+          <t>Each season Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="C361" s="28" t="inlineStr">
+        <is>
           <t>EXPForTier1</t>
         </is>
       </c>
-      <c r="D360" s="28" t="inlineStr">
+      <c r="D361" s="28" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
-      <c r="E360" s="21" t="inlineStr">
+      <c r="E361" s="21" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="48">
     <mergeCell ref="C163:C165"/>
     <mergeCell ref="D106:D108"/>
     <mergeCell ref="B302:C302"/>
@@ -5109,6 +5033,7 @@
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="C156:C157"/>
     <mergeCell ref="C85:C86"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="D154:D155"/>
     <mergeCell ref="B303:C303"/>
     <mergeCell ref="C106:C108"/>
@@ -5158,7 +5083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -5178,1186 +5103,1561 @@
     <col width="9" customWidth="1" style="8" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="72"/>
-    <row r="2" ht="16.5" customHeight="1" s="72">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="1" ht="25" customHeight="1" s="72">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="72"/>
+    <row r="3" s="72">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>Weekly Mission List</t>
         </is>
       </c>
     </row>
-    <row r="3" s="72"/>
-    <row r="4" ht="16.5" customHeight="1" s="72">
-      <c r="B4" s="38" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="72"/>
+    <row r="5" ht="16.5" customHeight="1" s="72">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Mission Content</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>CompleteDay</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="72">
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>Monster Defeat 100creatures</t>
-        </is>
-      </c>
-      <c r="C5" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" s="39" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="72">
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 300creatures</t>
+          <t>Monster Defeat 100creatures</t>
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E6" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D6" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="72">
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 500creatures</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="39" t="n">
-        <v>60</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>10</v>
+          <t>Monster Defeat 300creatures</t>
+        </is>
+      </c>
+      <c r="C7" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="72">
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 1,000creatures</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E8" s="39" t="n">
-        <v>10</v>
+          <t>Monster Defeat 500creatures</t>
+        </is>
+      </c>
+      <c r="C8" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="72">
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 1× Clear</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="39" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" s="39" t="n">
-        <v>10</v>
+          <t>Monster Defeat 1,000creatures</t>
+        </is>
+      </c>
+      <c r="C9" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="72">
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 3× Clear</t>
-        </is>
-      </c>
-      <c r="C10" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" s="39" t="n">
-        <v>10</v>
+          <t>Dark Temple 1times Clear</t>
+        </is>
+      </c>
+      <c r="C10" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="72">
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 5× Clear</t>
-        </is>
-      </c>
-      <c r="C11" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="39" t="n">
-        <v>160</v>
-      </c>
-      <c r="E11" s="39" t="n">
-        <v>10</v>
+          <t>Dark Temple 3times Clear</t>
+        </is>
+      </c>
+      <c r="C11" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="72">
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 10× Complete</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E12" s="39" t="n">
-        <v>10</v>
+          <t>Dark Temple 5times Clear</t>
+        </is>
+      </c>
+      <c r="C12" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="72">
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 30× Complete</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E13" s="39" t="n">
-        <v>10</v>
+          <t xml:space="preserve"> Minute 10times Complete</t>
+        </is>
+      </c>
+      <c r="C13" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="72">
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 50× Complete</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="39" t="n">
-        <v>120</v>
-      </c>
-      <c r="E14" s="39" t="n">
-        <v>10</v>
+          <t xml:space="preserve"> Minute 30times Complete</t>
+        </is>
+      </c>
+      <c r="C14" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="72">
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 1× Clear</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" s="39" t="n">
-        <v>10</v>
+          <t xml:space="preserve"> Minute 50times Complete</t>
+        </is>
+      </c>
+      <c r="C15" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="72">
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 5× Clear</t>
+          <t>Dungeon 1times Clear</t>
         </is>
       </c>
       <c r="C16" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="72">
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 10× Clear</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E17" s="39" t="n">
-        <v>10</v>
+          <t>Dungeon 5times Clear</t>
+        </is>
+      </c>
+      <c r="C17" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="72">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 15× Clear</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="E18" s="39" t="n">
-        <v>10</v>
+          <t>Dungeon 10times Clear</t>
+        </is>
+      </c>
+      <c r="C18" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="72">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>times 10pieces use</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E19" s="39" t="n">
-        <v>10</v>
+          <t>Dungeon 15times Clear</t>
+        </is>
+      </c>
+      <c r="C19" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="72">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>times 30pieces use</t>
+          <t>times 10pieces use</t>
         </is>
       </c>
       <c r="C20" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="72">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>times 50pieces use</t>
-        </is>
-      </c>
-      <c r="C21" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="39" t="n">
-        <v>60</v>
-      </c>
-      <c r="E21" s="39" t="n">
-        <v>10</v>
+          <t>times 30pieces use</t>
+        </is>
+      </c>
+      <c r="C21" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="72">
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t>Relic 10pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E22" s="39" t="n">
-        <v>10</v>
+          <t>times 50pieces use</t>
+        </is>
+      </c>
+      <c r="C22" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="72">
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t>Relic 50pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C23" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E23" s="39" t="n">
-        <v>10</v>
+          <t>Relic 10pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C23" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="72">
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t>Relic 100pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C24" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="39" t="n">
-        <v>120</v>
-      </c>
-      <c r="E24" s="39" t="n">
-        <v>10</v>
+          <t>Relic 50pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C24" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="72">
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 1× Summon</t>
-        </is>
-      </c>
-      <c r="C25" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E25" s="39" t="n">
-        <v>10</v>
+          <t>Relic 100pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C25" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="72">
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 5× Summon</t>
+          <t>Star's Apostle 1times Summon</t>
         </is>
       </c>
       <c r="C26" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E26" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D26" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="72">
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 10× Summon</t>
-        </is>
-      </c>
-      <c r="C27" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="39" t="n">
-        <v>60</v>
-      </c>
-      <c r="E27" s="39" t="n">
-        <v>10</v>
+          <t>Star's Apostle 5times Summon</t>
+        </is>
+      </c>
+      <c r="C27" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="72">
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 5×</t>
-        </is>
-      </c>
-      <c r="C28" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="39" t="n">
-        <v>10</v>
+          <t>Star's Apostle 10times Summon</t>
+        </is>
+      </c>
+      <c r="C28" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="72">
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 10×</t>
+          <t>Star's Apostle Level 5times</t>
         </is>
       </c>
       <c r="C29" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E29" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="72">
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t>Shard 10,000 use</t>
-        </is>
-      </c>
-      <c r="C30" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E30" s="39" t="n">
-        <v>10</v>
+          <t>Star's Apostle Level 10times</t>
+        </is>
+      </c>
+      <c r="C30" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="72">
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t>Shard 50,000 use</t>
+          <t>Shard 10,000 use</t>
         </is>
       </c>
       <c r="C31" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E31" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D31" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="72">
       <c r="B32" s="39" t="inlineStr">
         <is>
-          <t>Shard 100,000 use</t>
-        </is>
-      </c>
-      <c r="C32" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="39" t="n">
-        <v>60</v>
-      </c>
-      <c r="E32" s="39" t="n">
-        <v>10</v>
+          <t>Shard 50,000 use</t>
+        </is>
+      </c>
+      <c r="C32" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="72">
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>Field 10× Memoir</t>
-        </is>
-      </c>
-      <c r="C33" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E33" s="39" t="n">
-        <v>10</v>
+          <t>Shard 100,000 use</t>
+        </is>
+      </c>
+      <c r="C33" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="72">
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>Field 30× Memoir</t>
+          <t>Field 10times Memoir</t>
         </is>
       </c>
       <c r="C34" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="E34" s="39" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D34" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="72">
       <c r="B35" s="39" t="inlineStr">
         <is>
-          <t>Field 50× Memoir</t>
-        </is>
-      </c>
-      <c r="C35" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" s="39" t="n">
-        <v>60</v>
-      </c>
-      <c r="E35" s="39" t="n">
-        <v>10</v>
+          <t>Field 30times Memoir</t>
+        </is>
+      </c>
+      <c r="C35" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="72">
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>Dimensional Gate 10× utilize</t>
-        </is>
-      </c>
-      <c r="C36" s="39" t="n">
+          <t>Field 50times Memoir</t>
+        </is>
+      </c>
+      <c r="C36" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="72">
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>Dimensional Gate 10times utilize</t>
+        </is>
+      </c>
+      <c r="C37" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" s="39" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="72">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>※ Weekly EXP My/The 2500, Star's Apostle Summon 1× until if done 1500 Obtain Possible</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="38" s="72"/>
-    <row r="39" ht="16.5" customHeight="1" s="72">
-      <c r="B39" s="37" t="inlineStr">
+      <c r="D37" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" s="72">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>※ Weekly EXP My/The 2500, Star's Apostle Summon 1times until if done 1500 Obtain Possible</t>
+        </is>
+      </c>
+      <c r="C38" s="106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="72"/>
+    <row r="40" s="72">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>season Mission List</t>
         </is>
       </c>
     </row>
-    <row r="40" s="72"/>
-    <row r="41" ht="16.5" customHeight="1" s="72">
-      <c r="B41" s="38" t="inlineStr">
+    <row r="41" ht="16.5" customHeight="1" s="72"/>
+    <row r="42" ht="16.5" customHeight="1" s="72">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>Mission Content</t>
         </is>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>CompleteDay</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
+      <c r="D42" s="38" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
-      <c r="E41" s="38" t="inlineStr">
+      <c r="E42" s="38" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="72">
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>Monster Defeat 10,000creatures</t>
-        </is>
-      </c>
-      <c r="C42" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="39" t="n">
-        <v>200</v>
-      </c>
-      <c r="E42" s="39" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="72">
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 30,000creatures</t>
-        </is>
-      </c>
-      <c r="C43" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" s="39" t="n">
-        <v>300</v>
-      </c>
-      <c r="E43" s="39" t="n">
-        <v>20</v>
+          <t>Monster Defeat 10,000creatures</t>
+        </is>
+      </c>
+      <c r="C43" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="72">
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 50,000creatures</t>
-        </is>
-      </c>
-      <c r="C44" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="39" t="n">
-        <v>400</v>
-      </c>
-      <c r="E44" s="39" t="n">
-        <v>20</v>
+          <t>Monster Defeat 30,000creatures</t>
+        </is>
+      </c>
+      <c r="C44" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="72">
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 8× Clear</t>
-        </is>
-      </c>
-      <c r="C45" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D45" s="39" t="n">
-        <v>900</v>
-      </c>
-      <c r="E45" s="39" t="n">
-        <v>20</v>
+          <t>Monster Defeat 50,000creatures</t>
+        </is>
+      </c>
+      <c r="C45" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="72">
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 100× Complete</t>
-        </is>
-      </c>
-      <c r="C46" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D46" s="39" t="n">
-        <v>800</v>
-      </c>
-      <c r="E46" s="39" t="n">
-        <v>20</v>
+          <t>Dark Temple 8times Clear</t>
+        </is>
+      </c>
+      <c r="C46" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="72">
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 20× Clear</t>
-        </is>
-      </c>
-      <c r="C47" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="D47" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E47" s="39" t="n">
-        <v>20</v>
+          <t xml:space="preserve"> Minute 100times Complete</t>
+        </is>
+      </c>
+      <c r="C47" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="72">
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>times 100pieces use</t>
-        </is>
-      </c>
-      <c r="C48" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D48" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E48" s="39" t="n">
-        <v>20</v>
+          <t>Dungeon 20times Clear</t>
+        </is>
+      </c>
+      <c r="C48" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="72">
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Relic 150pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C49" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D49" s="39" t="n">
-        <v>800</v>
-      </c>
-      <c r="E49" s="39" t="n">
-        <v>20</v>
+          <t>times 100pieces use</t>
+        </is>
+      </c>
+      <c r="C49" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="72">
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 30× Summon</t>
-        </is>
-      </c>
-      <c r="C50" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="39" t="n">
-        <v>200</v>
-      </c>
-      <c r="E50" s="39" t="n">
-        <v>20</v>
+          <t>Relic 150pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C50" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="72">
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 50× Summon</t>
-        </is>
-      </c>
-      <c r="C51" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="39" t="n">
-        <v>300</v>
-      </c>
-      <c r="E51" s="39" t="n">
-        <v>20</v>
+          <t>Star's Apostle 30times Summon</t>
+        </is>
+      </c>
+      <c r="C51" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="72">
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 50×</t>
-        </is>
-      </c>
-      <c r="C52" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="39" t="n">
-        <v>200</v>
-      </c>
-      <c r="E52" s="39" t="n">
-        <v>20</v>
+          <t>Star's Apostle 50times Summon</t>
+        </is>
+      </c>
+      <c r="C52" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="72">
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 100×</t>
-        </is>
-      </c>
-      <c r="C53" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="D53" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E53" s="39" t="n">
-        <v>20</v>
+          <t>Star's Apostle Level 50times</t>
+        </is>
+      </c>
+      <c r="C53" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="72">
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Shard 200,000 use</t>
-        </is>
-      </c>
-      <c r="C54" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="39" t="n">
-        <v>300</v>
-      </c>
-      <c r="E54" s="39" t="n">
-        <v>20</v>
+          <t>Star's Apostle Level 100times</t>
+        </is>
+      </c>
+      <c r="C54" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="72">
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Shard 500,000 use</t>
-        </is>
-      </c>
-      <c r="C55" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D55" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E55" s="39" t="n">
-        <v>20</v>
+          <t>Shard 200,000 use</t>
+        </is>
+      </c>
+      <c r="C55" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="72">
       <c r="B56" s="39" t="inlineStr">
         <is>
-          <t>Shard 700,000 use</t>
-        </is>
-      </c>
-      <c r="C56" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="D56" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E56" s="39" t="n">
-        <v>20</v>
+          <t>Shard 500,000 use</t>
+        </is>
+      </c>
+      <c r="C56" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="72">
       <c r="B57" s="39" t="inlineStr">
         <is>
-          <t>Field 100× Memoir</t>
-        </is>
-      </c>
-      <c r="C57" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" s="39" t="n">
-        <v>400</v>
-      </c>
-      <c r="E57" s="39" t="n">
-        <v>20</v>
+          <t>Shard 700,000 use</t>
+        </is>
+      </c>
+      <c r="C57" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="72">
       <c r="B58" s="39" t="inlineStr">
         <is>
-          <t>Knight's Garden : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C58" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="E58" s="39" t="n">
-        <v>20</v>
+          <t>Field 100times Memoir</t>
+        </is>
+      </c>
+      <c r="C58" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="72">
       <c r="B59" s="39" t="inlineStr">
         <is>
-          <t>Spring Waterway : Monster 500creatures Defeat</t>
+          <t>Knight's Garden : Monster 500creatures Defeat</t>
         </is>
       </c>
       <c r="C59" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" s="39" t="n">
-        <v>200</v>
-      </c>
-      <c r="E59" s="39" t="n">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="D59" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="72">
       <c r="B60" s="39" t="inlineStr">
         <is>
-          <t>Salt Mine : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C60" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="39" t="n">
-        <v>300</v>
-      </c>
-      <c r="E60" s="39" t="n">
-        <v>20</v>
+          <t>Spring Waterway : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C60" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="72">
       <c r="B61" s="39" t="inlineStr">
         <is>
-          <t>Mansion of Syllek : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C61" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D61" s="39" t="n">
-        <v>400</v>
-      </c>
-      <c r="E61" s="39" t="n">
-        <v>20</v>
+          <t>Salt Mine : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C61" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" s="72">
       <c r="B62" s="39" t="inlineStr">
         <is>
+          <t>Mansion of Syllek : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C62" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" s="72">
+      <c r="B63" s="39" t="inlineStr">
+        <is>
           <t>Burning Forge : Monster 500creatures Defeat</t>
         </is>
       </c>
-      <c r="C62" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E62" s="39" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" s="72"/>
+      <c r="C63" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="64" s="72"/>
-    <row r="65" ht="16.5" customHeight="1" s="72">
-      <c r="B65" s="37" t="inlineStr">
+    <row r="65" ht="16.5" customHeight="1" s="72"/>
+    <row r="66" s="72">
+      <c r="B66" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> Mission List</t>
         </is>
       </c>
     </row>
-    <row r="66" s="72"/>
-    <row r="67" ht="16.5" customHeight="1" s="72">
-      <c r="B67" s="38" t="inlineStr">
+    <row r="67" ht="16.5" customHeight="1" s="72"/>
+    <row r="68" ht="16.5" customHeight="1" s="72">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t>Mission Content</t>
         </is>
       </c>
-      <c r="C67" s="38" t="inlineStr">
+      <c r="C68" s="38" t="inlineStr">
         <is>
           <t>CompleteDay</t>
         </is>
       </c>
-      <c r="D67" s="38" t="inlineStr">
+      <c r="D68" s="38" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
-      <c r="E67" s="38" t="inlineStr">
+      <c r="E68" s="38" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
-      </c>
-    </row>
-    <row r="68" ht="16.5" customHeight="1" s="72">
-      <c r="B68" s="39" t="inlineStr">
-        <is>
-          <t>Monster Defeat 100,000creatures</t>
-        </is>
-      </c>
-      <c r="C68" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D68" s="39" t="n">
-        <v>400</v>
-      </c>
-      <c r="E68" s="39" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="72">
       <c r="B69" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 200,000creatures</t>
-        </is>
-      </c>
-      <c r="C69" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D69" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E69" s="39" t="n">
-        <v>30</v>
+          <t>Monster Defeat 100,000creatures</t>
+        </is>
+      </c>
+      <c r="C69" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="72">
       <c r="B70" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 300,000creatures</t>
-        </is>
-      </c>
-      <c r="C70" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D70" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E70" s="39" t="n">
-        <v>30</v>
+          <t>Monster Defeat 200,000creatures</t>
+        </is>
+      </c>
+      <c r="C70" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="72">
       <c r="B71" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 10× Clear</t>
-        </is>
-      </c>
-      <c r="C71" s="39" t="n">
-        <v>22</v>
-      </c>
-      <c r="D71" s="39" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E71" s="39" t="n">
-        <v>30</v>
+          <t>Monster Defeat 300,000creatures</t>
+        </is>
+      </c>
+      <c r="C71" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="72">
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 200× Complete</t>
-        </is>
-      </c>
-      <c r="C72" s="39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D72" s="39" t="n">
-        <v>800</v>
-      </c>
-      <c r="E72" s="39" t="n">
-        <v>30</v>
+          <t>Dark Temple 10times Clear</t>
+        </is>
+      </c>
+      <c r="C72" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="72">
       <c r="B73" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 30× Clear</t>
-        </is>
-      </c>
-      <c r="C73" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D73" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E73" s="39" t="n">
-        <v>30</v>
+          <t xml:space="preserve"> Minute 200times Complete</t>
+        </is>
+      </c>
+      <c r="C73" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="72">
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>times 500pieces use</t>
-        </is>
-      </c>
-      <c r="C74" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D74" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E74" s="39" t="n">
-        <v>30</v>
+          <t>Dungeon 30times Clear</t>
+        </is>
+      </c>
+      <c r="C74" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="72">
       <c r="B75" s="39" t="inlineStr">
         <is>
-          <t>Relic 200pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C75" s="39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D75" s="39" t="n">
-        <v>800</v>
-      </c>
-      <c r="E75" s="39" t="n">
-        <v>30</v>
+          <t>times 500pieces use</t>
+        </is>
+      </c>
+      <c r="C75" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="72">
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 100× Summon</t>
-        </is>
-      </c>
-      <c r="C76" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D76" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E76" s="39" t="n">
-        <v>30</v>
+          <t>Relic 200pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C76" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="72">
       <c r="B77" s="39" t="inlineStr">
         <is>
-          <t>Shard 1,000,000 use</t>
-        </is>
-      </c>
-      <c r="C77" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D77" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E77" s="39" t="n">
-        <v>30</v>
+          <t>Star's Apostle 100times Summon</t>
+        </is>
+      </c>
+      <c r="C77" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="72">
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>Shard 5,000,000 use</t>
-        </is>
-      </c>
-      <c r="C78" s="39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D78" s="39" t="n">
-        <v>800</v>
-      </c>
-      <c r="E78" s="39" t="n">
-        <v>30</v>
+          <t>Shard 1,000,000 use</t>
+        </is>
+      </c>
+      <c r="C78" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="72">
       <c r="B79" s="39" t="inlineStr">
         <is>
-          <t>Field 200× Memoir</t>
-        </is>
-      </c>
-      <c r="C79" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E79" s="39" t="n">
-        <v>30</v>
+          <t>Shard 5,000,000 use</t>
+        </is>
+      </c>
+      <c r="C79" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="72">
       <c r="B80" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Without Normal/Regular Difficulty 's Defeat</t>
-        </is>
-      </c>
-      <c r="C80" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D80" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E80" s="39" t="n">
-        <v>30</v>
+          <t>Field 200times Memoir</t>
+        </is>
+      </c>
+      <c r="C80" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="16.5" customHeight="1" s="72">
       <c r="B81" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Without Normal/Regular Difficulty Defeat</t>
-        </is>
-      </c>
-      <c r="C81" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="D81" s="39" t="n">
-        <v>700</v>
-      </c>
-      <c r="E81" s="39" t="n">
-        <v>30</v>
+          <t xml:space="preserve"> Without Normal/Regular Difficulty 's Defeat</t>
+        </is>
+      </c>
+      <c r="C81" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="72">
@@ -6366,193 +6666,286 @@
           <t xml:space="preserve"> Without Normal/Regular Difficulty Defeat</t>
         </is>
       </c>
-      <c r="C82" s="39" t="n">
-        <v>14</v>
-      </c>
-      <c r="D82" s="39" t="n">
-        <v>800</v>
-      </c>
-      <c r="E82" s="39" t="n">
-        <v>30</v>
+      <c r="C82" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="16.5" customHeight="1" s="72">
       <c r="B83" s="39" t="inlineStr">
         <is>
-          <t>Knight's Garden : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C83" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D83" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E83" s="39" t="n">
-        <v>30</v>
+          <t xml:space="preserve"> Without Normal/Regular Difficulty Defeat</t>
+        </is>
+      </c>
+      <c r="C83" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="72">
       <c r="B84" s="39" t="inlineStr">
         <is>
-          <t>Spring Waterway : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C84" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D84" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E84" s="39" t="n">
-        <v>30</v>
+          <t>Knight's Garden : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C84" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1" s="72">
       <c r="B85" s="39" t="inlineStr">
         <is>
-          <t>Salt Mine : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C85" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D85" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E85" s="39" t="n">
-        <v>30</v>
+          <t>Spring Waterway : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C85" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="72">
       <c r="B86" s="39" t="inlineStr">
         <is>
-          <t>Mansion of Syllek : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C86" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D86" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E86" s="39" t="n">
-        <v>30</v>
+          <t>Salt Mine : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C86" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" s="72">
       <c r="B87" s="39" t="inlineStr">
         <is>
-          <t>Burning Forge : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C87" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="D87" s="39" t="n">
-        <v>600</v>
-      </c>
-      <c r="E87" s="39" t="n">
-        <v>30</v>
+          <t>Mansion of Syllek : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C87" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="72">
       <c r="B88" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Sealed Garden 3 to Clear </t>
-        </is>
-      </c>
-      <c r="C88" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D88" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E88" s="39" t="n">
-        <v>30</v>
+          <t>Burning Forge : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C88" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D88" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="72">
       <c r="B89" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Sealed Waterway 3 to Clear </t>
-        </is>
-      </c>
-      <c r="C89" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D89" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E89" s="39" t="n">
-        <v>30</v>
+          <t xml:space="preserve">All Sealed Garden 3 to Clear </t>
+        </is>
+      </c>
+      <c r="C89" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D89" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" s="72">
       <c r="B90" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Sealed Mine 3 to Clear </t>
-        </is>
-      </c>
-      <c r="C90" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D90" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E90" s="39" t="n">
-        <v>30</v>
+          <t xml:space="preserve">All Sealed Waterway 3 to Clear </t>
+        </is>
+      </c>
+      <c r="C90" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="16.5" customHeight="1" s="72">
       <c r="B91" s="39" t="inlineStr">
         <is>
-          <t>Knight's Garden Exploration Mission All Complete</t>
-        </is>
-      </c>
-      <c r="C91" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D91" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E91" s="39" t="n">
-        <v>30</v>
+          <t xml:space="preserve">All Sealed Mine 3 to Clear </t>
+        </is>
+      </c>
+      <c r="C91" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="72">
       <c r="B92" s="39" t="inlineStr">
         <is>
-          <t>Spring Waterway Exploration Mission All Complete</t>
-        </is>
-      </c>
-      <c r="C92" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D92" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E92" s="39" t="n">
-        <v>30</v>
+          <t>Knight's Garden Exploration Mission All Complete</t>
+        </is>
+      </c>
+      <c r="C92" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="72">
       <c r="B93" s="39" t="inlineStr">
         <is>
+          <t>Spring Waterway Exploration Mission All Complete</t>
+        </is>
+      </c>
+      <c r="C93" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" s="72">
+      <c r="B94" s="39" t="inlineStr">
+        <is>
           <t>Salt Mine Exploration Mission All Complete</t>
         </is>
       </c>
-      <c r="C93" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D93" s="39" t="n">
-        <v>500</v>
-      </c>
-      <c r="E93" s="39" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="94" s="72"/>
+      <c r="C94" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="95" s="72"/>
     <row r="96" s="72"/>
     <row r="97" s="72"/>
@@ -6586,14 +6979,18 @@
     <row r="125" s="72"/>
     <row r="126" s="72"/>
     <row r="127" s="72"/>
-    <row r="128" ht="16.5" customHeight="1" s="72">
-      <c r="B128" s="8" t="inlineStr">
+    <row r="128" ht="16.5" customHeight="1" s="72"/>
+    <row r="129">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>■ season Level Reward</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6604,770 +7001,1044 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="40" min="1" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="72"/>
-    <row r="2" ht="16.5" customHeight="1" s="72">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="1" ht="25" customHeight="1" s="72">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="72"/>
+    <row r="3" ht="16.5" customHeight="1" s="72">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="72">
-      <c r="B3" s="40" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="72">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>※ EXP</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="72">
-      <c r="B4" s="41" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="72">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Cumulative </t>
         </is>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="72">
-      <c r="B5" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>Bronze1</t>
-        </is>
-      </c>
-      <c r="D5" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="72">
       <c r="B6" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
+          <t>Bronze1</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="72">
+      <c r="B7" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
           <t>Bronze2</t>
         </is>
       </c>
-      <c r="D6" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="43" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" s="72">
-      <c r="B7" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="D7" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="72">
+      <c r="B8" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>Bronze3</t>
         </is>
       </c>
-      <c r="D7" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" s="72">
-      <c r="B8" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="D8" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="72">
+      <c r="B9" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>Bronze4</t>
         </is>
       </c>
-      <c r="D8" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="E8" s="43" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" s="72">
-      <c r="B9" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="D9" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="72">
+      <c r="B10" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>Bronze5</t>
         </is>
       </c>
-      <c r="D9" s="43" t="n">
-        <v>80</v>
-      </c>
-      <c r="E9" s="43" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="72">
-      <c r="B10" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="D10" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="72">
+      <c r="B11" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>Bronze6</t>
         </is>
       </c>
-      <c r="D10" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="72">
-      <c r="B11" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="D11" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="72">
+      <c r="B12" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>Bronze7</t>
         </is>
       </c>
-      <c r="D11" s="43" t="n">
-        <v>120</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="72">
-      <c r="B12" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="D12" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="72">
+      <c r="B13" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>Bronze8</t>
         </is>
       </c>
-      <c r="D12" s="43" t="n">
-        <v>140</v>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" s="72">
-      <c r="B13" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="D13" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="72">
+      <c r="B14" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
         <is>
           <t>Bronze9</t>
         </is>
       </c>
-      <c r="D13" s="43" t="n">
-        <v>160</v>
-      </c>
-      <c r="E13" s="43" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="72">
-      <c r="B14" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="D14" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" s="72">
+      <c r="B15" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
         <is>
           <t>Silver10</t>
         </is>
       </c>
-      <c r="D14" s="43" t="n">
-        <v>180</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" s="72">
-      <c r="B15" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="D15" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="72">
+      <c r="B16" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
         <is>
           <t>Silver11</t>
         </is>
       </c>
-      <c r="D15" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" s="72">
-      <c r="B16" s="43" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="D16" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="72">
+      <c r="B17" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
         <is>
           <t>Silver12</t>
         </is>
       </c>
-      <c r="D16" s="43" t="n">
-        <v>220</v>
-      </c>
-      <c r="E16" s="43" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" s="72">
-      <c r="B17" s="43" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="D17" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="72">
+      <c r="B18" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
         <is>
           <t>Silver13</t>
         </is>
       </c>
-      <c r="D17" s="43" t="n">
-        <v>240</v>
-      </c>
-      <c r="E17" s="43" t="n">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="72">
-      <c r="B18" s="43" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="D18" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="72">
+      <c r="B19" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>Silver14</t>
         </is>
       </c>
-      <c r="D18" s="43" t="n">
-        <v>260</v>
-      </c>
-      <c r="E18" s="43" t="n">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="72">
-      <c r="B19" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="D19" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" s="72">
+      <c r="B20" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
         <is>
           <t>Silver15</t>
         </is>
       </c>
-      <c r="D19" s="43" t="n">
-        <v>280</v>
-      </c>
-      <c r="E19" s="43" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="72">
-      <c r="B20" s="43" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="D20" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="72">
+      <c r="B21" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>Silver16</t>
         </is>
       </c>
-      <c r="D20" s="43" t="n">
-        <v>300</v>
-      </c>
-      <c r="E20" s="43" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" s="72">
-      <c r="B21" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="D21" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="72">
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>Silver17</t>
         </is>
       </c>
-      <c r="D21" s="43" t="n">
-        <v>320</v>
-      </c>
-      <c r="E21" s="43" t="n">
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="72">
-      <c r="B22" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="D22" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="72">
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>Gold18</t>
         </is>
       </c>
-      <c r="D22" s="43" t="n">
-        <v>340</v>
-      </c>
-      <c r="E22" s="43" t="n">
-        <v>3060</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="72">
-      <c r="B23" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="D23" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="72">
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>Gold19</t>
         </is>
       </c>
-      <c r="D23" s="43" t="n">
-        <v>370</v>
-      </c>
-      <c r="E23" s="43" t="n">
-        <v>3430</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" s="72">
-      <c r="B24" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="D24" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="72">
+      <c r="B25" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>Gold20</t>
         </is>
       </c>
-      <c r="D24" s="43" t="n">
-        <v>400</v>
-      </c>
-      <c r="E24" s="43" t="n">
-        <v>3830</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="72">
-      <c r="B25" s="43" t="n">
-        <v>21</v>
-      </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="D25" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="72">
+      <c r="B26" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>Gold21</t>
         </is>
       </c>
-      <c r="D25" s="43" t="n">
-        <v>430</v>
-      </c>
-      <c r="E25" s="43" t="n">
-        <v>4260</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="72">
-      <c r="B26" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="D26" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="72">
+      <c r="B27" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>Gold22</t>
         </is>
       </c>
-      <c r="D26" s="43" t="n">
-        <v>460</v>
-      </c>
-      <c r="E26" s="43" t="n">
-        <v>4720</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" s="72">
-      <c r="B27" s="43" t="n">
-        <v>23</v>
-      </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="D27" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="72">
+      <c r="B28" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>Gold23</t>
         </is>
       </c>
-      <c r="D27" s="43" t="n">
-        <v>490</v>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" s="72">
-      <c r="B28" s="43" t="n">
-        <v>24</v>
-      </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="D28" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="72">
+      <c r="B29" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Gold24</t>
         </is>
       </c>
-      <c r="D28" s="43" t="n">
-        <v>520</v>
-      </c>
-      <c r="E28" s="43" t="n">
-        <v>5730</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" s="72">
-      <c r="B29" s="43" t="n">
-        <v>25</v>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="D29" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="72">
+      <c r="B30" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
         <is>
           <t>Platinum25</t>
         </is>
       </c>
-      <c r="D29" s="43" t="n">
-        <v>550</v>
-      </c>
-      <c r="E29" s="43" t="n">
-        <v>6280</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="72">
-      <c r="B30" s="43" t="n">
-        <v>26</v>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="D30" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" s="72">
+      <c r="B31" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
         <is>
           <t>Platinum26</t>
         </is>
       </c>
-      <c r="D30" s="43" t="n">
-        <v>580</v>
-      </c>
-      <c r="E30" s="43" t="n">
-        <v>6860</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" s="72">
-      <c r="B31" s="43" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="D31" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="72">
+      <c r="B32" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>Platinum27</t>
         </is>
       </c>
-      <c r="D31" s="43" t="n">
-        <v>610</v>
-      </c>
-      <c r="E31" s="43" t="n">
-        <v>7470</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" s="72">
-      <c r="B32" s="43" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="D32" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="72">
+      <c r="B33" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>Platinum28</t>
         </is>
       </c>
-      <c r="D32" s="43" t="n">
-        <v>640</v>
-      </c>
-      <c r="E32" s="43" t="n">
-        <v>8110</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" s="72">
-      <c r="B33" s="43" t="n">
-        <v>29</v>
-      </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="D33" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="72">
+      <c r="B34" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
         <is>
           <t>Platinum29</t>
         </is>
       </c>
-      <c r="D33" s="43" t="n">
-        <v>670</v>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>8780</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="72">
-      <c r="B34" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="D34" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="72">
+      <c r="B35" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>Platinum30</t>
         </is>
       </c>
-      <c r="D34" s="43" t="n">
-        <v>700</v>
-      </c>
-      <c r="E34" s="43" t="n">
-        <v>9480</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" s="72">
-      <c r="B35" s="43" t="n">
-        <v>31</v>
-      </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="D35" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="72">
+      <c r="B36" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="inlineStr">
         <is>
           <t>Diamond31</t>
         </is>
       </c>
-      <c r="D35" s="43" t="n">
-        <v>740</v>
-      </c>
-      <c r="E35" s="43" t="n">
-        <v>10220</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="72">
-      <c r="B36" s="43" t="n">
-        <v>32</v>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="D36" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="72">
+      <c r="B37" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Diamond32</t>
         </is>
       </c>
-      <c r="D36" s="43" t="n">
-        <v>780</v>
-      </c>
-      <c r="E36" s="43" t="n">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="72">
-      <c r="B37" s="43" t="n">
-        <v>33</v>
-      </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="D37" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="72">
+      <c r="B38" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="inlineStr">
         <is>
           <t>Diamond33</t>
         </is>
       </c>
-      <c r="D37" s="43" t="n">
-        <v>820</v>
-      </c>
-      <c r="E37" s="43" t="n">
-        <v>11820</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="72">
-      <c r="B38" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="D38" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="72">
+      <c r="B39" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
         <is>
           <t>Diamond34</t>
         </is>
       </c>
-      <c r="D38" s="43" t="n">
-        <v>860</v>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>12680</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="72">
-      <c r="B39" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="D39" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="72">
+      <c r="B40" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>Diamond35</t>
         </is>
       </c>
-      <c r="D39" s="43" t="n">
-        <v>900</v>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>13580</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="72">
-      <c r="B40" s="43" t="n">
-        <v>36</v>
-      </c>
-      <c r="C40" s="43" t="inlineStr">
+      <c r="D40" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="72">
+      <c r="B41" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
         <is>
           <t>Ascended Master36</t>
         </is>
       </c>
-      <c r="D40" s="43" t="n">
-        <v>940</v>
-      </c>
-      <c r="E40" s="43" t="n">
-        <v>14520</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" s="72">
-      <c r="B41" s="43" t="n">
-        <v>37</v>
-      </c>
-      <c r="C41" s="43" t="inlineStr">
+      <c r="D41" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="72">
+      <c r="B42" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
         <is>
           <t>Ascended Master37</t>
         </is>
       </c>
-      <c r="D41" s="43" t="n">
-        <v>980</v>
-      </c>
-      <c r="E41" s="43" t="n">
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="72">
-      <c r="B42" s="43" t="n">
-        <v>38</v>
-      </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="D42" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="72">
+      <c r="B43" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
         <is>
           <t>Ascended Master38</t>
         </is>
       </c>
-      <c r="D42" s="43" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E42" s="43" t="n">
-        <v>16520</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1" s="72">
-      <c r="B43" s="43" t="n">
-        <v>39</v>
-      </c>
-      <c r="C43" s="43" t="inlineStr">
+      <c r="D43" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="72">
+      <c r="B44" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
         <is>
           <t>Ascended Master39</t>
         </is>
       </c>
-      <c r="D43" s="43" t="n">
-        <v>1060</v>
-      </c>
-      <c r="E43" s="43" t="n">
-        <v>17580</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1" s="72">
-      <c r="B44" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" s="43" t="inlineStr">
+      <c r="D44" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="72">
+      <c r="B45" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="inlineStr">
         <is>
           <t>Grandmaster40</t>
         </is>
       </c>
-      <c r="D44" s="43" t="n">
-        <v>1110</v>
-      </c>
-      <c r="E44" s="43" t="n">
-        <v>18690</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" customHeight="1" s="72">
-      <c r="B45" s="43" t="n">
-        <v>41</v>
-      </c>
-      <c r="C45" s="43" t="inlineStr">
+      <c r="D45" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="72">
+      <c r="B46" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="inlineStr">
         <is>
           <t>Grandmaster41</t>
         </is>
       </c>
-      <c r="D45" s="43" t="n">
-        <v>1160</v>
-      </c>
-      <c r="E45" s="43" t="n">
-        <v>19850</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="72">
-      <c r="B46" s="43" t="n">
-        <v>42</v>
-      </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="D46" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="72">
+      <c r="B47" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>Grandmaster42</t>
         </is>
       </c>
-      <c r="D46" s="43" t="n">
-        <v>1210</v>
-      </c>
-      <c r="E46" s="43" t="n">
-        <v>21060</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" s="72">
-      <c r="B47" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="D47" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="72">
+      <c r="B48" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>Challenger43</t>
         </is>
       </c>
-      <c r="D47" s="43" t="n">
-        <v>1260</v>
-      </c>
-      <c r="E47" s="43" t="n">
-        <v>22320</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" s="72">
-      <c r="B48" s="43" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="43" t="inlineStr">
+      <c r="D48" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="72">
+      <c r="B49" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>Challenger44</t>
         </is>
       </c>
-      <c r="D48" s="43" t="n">
-        <v>1310</v>
-      </c>
-      <c r="E48" s="43" t="n">
-        <v>23630</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="72">
-      <c r="B49" s="43" t="n">
-        <v>45</v>
-      </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="D49" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>Legend45</t>
         </is>
       </c>
-      <c r="D49" s="43" t="n">
-        <v>1370</v>
-      </c>
-      <c r="E49" s="43" t="n">
-        <v>25000</v>
+      <c r="D50" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7378,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="44" min="1" max="3"/>
@@ -7386,607 +8057,786 @@
     <col width="9" customWidth="1" style="44" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="72"/>
-    <row r="2" s="72">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="1" ht="25" customHeight="1" s="72">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" s="72"/>
+    <row r="3" s="72">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>Pass Reward</t>
         </is>
       </c>
     </row>
-    <row r="3" s="72"/>
-    <row r="4" s="72">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4" s="72"/>
+    <row r="5" s="72">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="5" s="72">
-      <c r="B5" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="43" t="inlineStr">
-        <is>
-          <t>Shard</t>
-        </is>
-      </c>
-      <c r="E5" s="43" t="n">
-        <v>10000</v>
       </c>
     </row>
     <row r="6" s="72">
       <c r="B6" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="n">
-        <v>20</v>
+          <t>Shard</t>
+        </is>
+      </c>
+      <c r="E6" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="7" s="72">
-      <c r="B7" s="43" t="n">
-        <v>3</v>
+      <c r="B7" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C7" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> applied Each</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>10</v>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E7" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="8" s="72">
-      <c r="B8" s="43" t="n">
-        <v>4</v>
+      <c r="B8" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C8" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E8" s="43" t="n">
-        <v>10</v>
+          <t xml:space="preserve"> applied Each</t>
+        </is>
+      </c>
+      <c r="E8" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="9" s="72">
-      <c r="B9" s="43" t="n">
-        <v>5</v>
+      <c r="B9" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C9" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E9" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" s="72">
+      <c r="B10" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
           <t xml:space="preserve">R also </t>
         </is>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E10" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="72">
-      <c r="B10" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
+    <row r="11" s="72">
+      <c r="B11" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Experience Fragment</t>
         </is>
       </c>
-      <c r="E10" s="43" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" s="72">
-      <c r="B11" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="E11" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="72">
+      <c r="B12" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> applied Each</t>
         </is>
       </c>
-      <c r="E11" s="43" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" s="72">
-      <c r="B12" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="E12" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="72">
+      <c r="B13" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> applied </t>
         </is>
       </c>
-      <c r="E12" s="43" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" s="72">
-      <c r="B13" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="E13" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" s="72">
+      <c r="B14" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
         <is>
           <t>Shard</t>
         </is>
       </c>
-      <c r="E13" s="43" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" s="72">
-      <c r="B14" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="E14" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" s="72">
+      <c r="B15" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="E14" s="43" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" s="72">
-      <c r="B15" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="E15" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" s="72">
+      <c r="B16" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
         <is>
           <t>Experience Fragment</t>
         </is>
       </c>
-      <c r="E15" s="43" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" s="72">
-      <c r="B16" s="43" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="E16" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" s="72">
+      <c r="B17" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> applied Each</t>
         </is>
       </c>
-      <c r="E16" s="43" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" s="72">
-      <c r="B17" s="43" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="E17" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" s="72">
+      <c r="B18" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>Shining Modify</t>
         </is>
       </c>
-      <c r="E17" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" s="72">
-      <c r="B18" s="43" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="E18" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" s="72">
+      <c r="B19" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>Shard</t>
         </is>
       </c>
-      <c r="E18" s="43" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="19" s="72">
-      <c r="B19" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="E19" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="72">
+      <c r="B20" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">SR also </t>
         </is>
       </c>
-      <c r="E19" s="43" t="n">
+      <c r="E20" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20" s="72">
-      <c r="B20" s="43" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
+    <row r="21" s="72">
+      <c r="B21" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Shard</t>
         </is>
       </c>
-      <c r="E20" s="43" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="21" s="72">
-      <c r="B21" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="C21" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="E21" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="72">
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Time's </t>
         </is>
       </c>
-      <c r="E21" s="43" t="n">
+      <c r="E22" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22" s="72">
-      <c r="B22" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
+    <row r="23" s="72">
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
         <is>
           <t>Experience Fragment</t>
         </is>
       </c>
-      <c r="E22" s="43" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" s="72">
-      <c r="B23" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="E23" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="72">
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> applied </t>
         </is>
       </c>
-      <c r="E23" s="43" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" s="72">
-      <c r="B24" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="E24" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" s="72">
+      <c r="B25" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="E24" s="43" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25" s="72">
-      <c r="B25" s="43" t="n">
-        <v>21</v>
-      </c>
-      <c r="C25" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="E25" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="72">
+      <c r="B26" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">during </t>
         </is>
       </c>
-      <c r="E25" s="43" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" s="72">
-      <c r="B26" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="C26" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="E26" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="72">
+      <c r="B27" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> integer 1pieces </t>
         </is>
       </c>
-      <c r="E26" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" s="72">
-      <c r="B27" s="43" t="n">
-        <v>23</v>
-      </c>
-      <c r="C27" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="E27" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" s="72">
+      <c r="B28" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>Experience Fragment</t>
         </is>
       </c>
-      <c r="E27" s="43" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="28" s="72">
-      <c r="B28" s="43" t="n">
-        <v>24</v>
-      </c>
-      <c r="C28" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="E28" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" s="72">
+      <c r="B29" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Shining Modify</t>
         </is>
       </c>
-      <c r="E28" s="43" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" s="72">
-      <c r="B29" s="43" t="n">
-        <v>25</v>
-      </c>
-      <c r="C29" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
+      <c r="E29" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="72">
+      <c r="B30" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> 's Spirit</t>
         </is>
       </c>
-      <c r="E29" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" s="72">
-      <c r="B30" s="43" t="n">
-        <v>26</v>
-      </c>
-      <c r="C30" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="E30" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="72">
+      <c r="B31" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>Experience Fragment</t>
         </is>
       </c>
-      <c r="E30" s="43" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" s="72">
-      <c r="B31" s="43" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="E31" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="72">
+      <c r="B32" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Shard</t>
         </is>
       </c>
-      <c r="E31" s="43" t="n">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="32" s="72">
-      <c r="B32" s="43" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="E32" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" s="72">
+      <c r="B33" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> integer 1pieces </t>
         </is>
       </c>
-      <c r="E32" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" s="72">
-      <c r="B33" s="43" t="n">
-        <v>29</v>
-      </c>
-      <c r="C33" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CGrade Gem </t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>5</v>
+      <c r="E33" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="34" s="72">
-      <c r="B34" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="C34" s="43" t="n">
-        <v>8</v>
+      <c r="B34" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D34" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">40 </t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="n">
+          <t xml:space="preserve">CGrade/Tier Gem </t>
+        </is>
+      </c>
+      <c r="E34" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" s="72">
+      <c r="B35" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35" s="72">
-      <c r="B35" s="43" t="n">
-        <v>31</v>
-      </c>
-      <c r="C35" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" s="43" t="inlineStr">
+    <row r="36" s="72">
+      <c r="B36" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E35" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" s="72">
-      <c r="B36" s="43" t="n">
-        <v>32</v>
-      </c>
-      <c r="C36" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="E36" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" s="72">
+      <c r="B37" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Shining Modify</t>
         </is>
       </c>
-      <c r="E36" s="43" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" s="72">
-      <c r="B37" s="43" t="n">
-        <v>33</v>
-      </c>
-      <c r="C37" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
+      <c r="E37" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" s="72">
+      <c r="B38" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> integer 1pieces </t>
         </is>
       </c>
-      <c r="E37" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" s="72">
-      <c r="B38" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="C38" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UCGrade Gem </t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>5</v>
+      <c r="E38" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="39" s="72">
-      <c r="B39" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="C39" s="43" t="n">
-        <v>8</v>
+      <c r="B39" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D39" s="43" t="inlineStr">
         <is>
+          <t xml:space="preserve">UCGrade/Tier Gem </t>
+        </is>
+      </c>
+      <c r="E39" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" s="72">
+      <c r="B40" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
           <t xml:space="preserve"> applied also </t>
-        </is>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" s="72">
-      <c r="B40" s="43" t="n">
-        <v>36</v>
-      </c>
-      <c r="C40" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time's </t>
         </is>
       </c>
       <c r="E40" s="43" t="n">
@@ -7994,150 +8844,221 @@
       </c>
     </row>
     <row r="41" s="72">
-      <c r="B41" s="43" t="n">
-        <v>37</v>
-      </c>
-      <c r="C41" s="43" t="n">
-        <v>9</v>
+      <c r="B41" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Time's </t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" s="72">
+      <c r="B42" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
           <t xml:space="preserve"> applied Each</t>
         </is>
       </c>
-      <c r="E41" s="43" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="42" s="72">
-      <c r="B42" s="43" t="n">
-        <v>38</v>
-      </c>
-      <c r="C42" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="E42" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" s="72">
+      <c r="B43" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>Shining Modify</t>
         </is>
       </c>
-      <c r="E42" s="43" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" s="72">
-      <c r="B43" s="43" t="n">
-        <v>39</v>
-      </c>
-      <c r="C43" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="E43" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="72">
+      <c r="B44" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E43" s="43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" s="72">
-      <c r="B44" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D44" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RGrade Gem </t>
-        </is>
-      </c>
-      <c r="E44" s="43" t="n">
-        <v>5</v>
+      <c r="E44" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="45" s="72">
-      <c r="B45" s="43" t="n">
-        <v>41</v>
-      </c>
-      <c r="C45" s="43" t="n">
-        <v>10</v>
+      <c r="B45" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D45" s="43" t="inlineStr">
         <is>
+          <t xml:space="preserve">RGrade/Tier Gem </t>
+        </is>
+      </c>
+      <c r="E45" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" s="72">
+      <c r="B46" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
           <t>per's Spirit</t>
         </is>
       </c>
-      <c r="E45" s="43" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" s="72">
-      <c r="B46" s="43" t="n">
-        <v>42</v>
-      </c>
-      <c r="C46" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40 </t>
-        </is>
-      </c>
-      <c r="E46" s="43" t="n">
+      <c r="E46" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" s="72">
+      <c r="B47" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="47" s="72">
-      <c r="B47" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="C47" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="D47" s="43" t="inlineStr">
+    <row r="48" s="72">
+      <c r="B48" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
         <is>
           <t>Soul</t>
         </is>
       </c>
-      <c r="E47" s="43" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" s="72">
-      <c r="B48" s="43" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="43" t="n">
-        <v>13</v>
-      </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="E48" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" s="72">
+      <c r="B49" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> applied also </t>
-        </is>
-      </c>
-      <c r="E48" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" s="72">
-      <c r="B49" s="43" t="n">
-        <v>45</v>
-      </c>
-      <c r="C49" s="43" t="n">
-        <v>14</v>
-      </c>
-      <c r="D49" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E49" s="43" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="50">
+      <c r="B50" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -120,19 +120,8 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="00CC0000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00AAAAAA"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -155,12 +144,6 @@
       <patternFill patternType="solid">
         <fgColor theme="1"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2F2"/>
-        <bgColor rgb="00FFF2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -728,7 +711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,18 +986,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2354,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="27" min="1" max="1"/>
@@ -2366,103 +2337,102 @@
     <col width="9" customWidth="1" style="27" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="72">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" s="72"/>
+    <row r="1"/>
+    <row r="2" ht="22" customHeight="1" s="72">
+      <c r="B2" s="91" t="inlineStr">
+        <is>
+          <t>Document History : Season Pass</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+    </row>
     <row r="3" ht="18" customHeight="1" s="72">
-      <c r="B3" s="91" t="inlineStr">
-        <is>
-          <t>Document History : Season Pass</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
+      <c r="B3" s="92" t="n"/>
+      <c r="C3" s="92" t="n"/>
+      <c r="D3" s="92" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="92" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1" s="72">
-      <c r="B4" s="92" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="93" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D4" s="92" t="inlineStr">
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Date</t>
+        </is>
+      </c>
+      <c r="D4" s="94" t="inlineStr">
         <is>
           <t>Content</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="L4" s="95" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="92" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="72">
       <c r="A5" s="5" t="n"/>
-      <c r="B5" s="93" t="n">
+      <c r="B5" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="97" t="inlineStr">
         <is>
           <t>24.04.22</t>
         </is>
       </c>
-      <c r="D5" s="94" t="inlineStr">
+      <c r="D5" s="98" t="inlineStr">
         <is>
           <t>Initial draft</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="L5" s="99" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L5" s="95" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="72">
       <c r="A6" s="5" t="n"/>
-      <c r="B6" s="96" t="n">
+      <c r="B6" s="100" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="97" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>24.05.27</t>
         </is>
       </c>
-      <c r="D6" s="98" t="inlineStr">
+      <c r="D6" s="102" t="inlineStr">
         <is>
           <t>Package reward removed</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="L6" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L6" s="99" t="n"/>
       <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="72">
@@ -2480,12 +2450,11 @@
           <t>Past season UI — detailed description added</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="L7" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L7" s="103" t="n"/>
       <c r="M7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="72">
@@ -2503,12 +2472,11 @@
           <t>Required XP per level specified</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="L8" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L8" s="103" t="n"/>
       <c r="M8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="72">
@@ -2526,12 +2494,11 @@
           <t>All mission types set to cumulative count</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="L9" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L9" s="103" t="n"/>
       <c r="M9" s="6" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="72">
@@ -2546,15 +2513,14 @@
       </c>
       <c r="D10" s="102" t="inlineStr">
         <is>
-          <t>Missions split into cumulative vs. quest-progress types</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
+          <t>Mission designed Content according to Cumulative, Quest Progress when to Categorize Possible</t>
+        </is>
+      </c>
+      <c r="L10" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L10" s="103" t="n"/>
       <c r="M10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="72">
@@ -2569,15 +2535,14 @@
       </c>
       <c r="D11" s="102" t="inlineStr">
         <is>
-          <t>Bilibili ranking system content applied</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
+          <t>Current Bilibili ranking system content applied</t>
+        </is>
+      </c>
+      <c r="L11" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L11" s="103" t="n"/>
       <c r="M11" s="6" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="72">
@@ -2592,15 +2557,14 @@
       </c>
       <c r="D12" s="102" t="inlineStr">
         <is>
-          <t>Cosmetic rewards (name tags, titles, profile skins) added to reward pool</t>
-        </is>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
+          <t>Reward Content Name Tag, Title, Profile Skin Etc.'s Cosmetic Item Provide can Yes/Available</t>
+        </is>
+      </c>
+      <c r="L12" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L12" s="103" t="n"/>
       <c r="M12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="72">
@@ -2618,12 +2582,11 @@
           <t>Access button changed</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="L13" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L13" s="103" t="n"/>
       <c r="M13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="72">
@@ -2638,15 +2601,14 @@
       </c>
       <c r="D14" s="102" t="inlineStr">
         <is>
-          <t>HUD rank indicator feature added</t>
-        </is>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
+          <t>HUD rank preview function added</t>
+        </is>
+      </c>
+      <c r="L14" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L14" s="103" t="n"/>
       <c r="M14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="72">
@@ -2661,15 +2623,14 @@
       </c>
       <c r="D15" s="102" t="inlineStr">
         <is>
-          <t>Unlock timing specified</t>
-        </is>
-      </c>
-      <c r="E15" s="0" t="inlineStr">
+          <t>Unlock timing added</t>
+        </is>
+      </c>
+      <c r="L15" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L15" s="103" t="n"/>
       <c r="M15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="72">
@@ -2684,15 +2645,14 @@
       </c>
       <c r="D16" s="102" t="inlineStr">
         <is>
-          <t>List updated; levels changed to 45 tiers; Pass XP halved</t>
-        </is>
-      </c>
-      <c r="E16" s="0" t="inlineStr">
+          <t>List updated; max level set to 45; pass XP per level adjusted</t>
+        </is>
+      </c>
+      <c r="L16" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L16" s="103" t="n"/>
       <c r="M16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="72">
@@ -2707,15 +2667,14 @@
       </c>
       <c r="D17" s="102" t="inlineStr">
         <is>
-          <t>Lv. 9, 19: Intermediate Gem Box ×3; Lv. 44: Advanced Skill Support Box ×5</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
+          <t>9, 19Level Gem Intermediate Gem Box 3pieces Provide, 44Level Reward Skill Select 5pieces</t>
+        </is>
+      </c>
+      <c r="L17" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L17" s="103" t="n"/>
       <c r="M17" s="6" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="72">
@@ -2733,12 +2692,11 @@
           <t>Stamina Potion removed from rank level rewards</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="L18" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L18" s="103" t="n"/>
       <c r="M18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="72">
@@ -2756,50 +2714,43 @@
           <t>UI updated; XML structure revised</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="L19" s="103" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
-      <c r="L19" s="103" t="n"/>
       <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="100" t="n">
+      <c r="B20" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="101" t="inlineStr">
+      <c r="C20" s="63" t="inlineStr">
         <is>
           <t>25.05.30</t>
         </is>
       </c>
-      <c r="D20" s="102" t="inlineStr">
-        <is>
-          <t>Mission list, Pass XP, and Pass reward list modified</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="D20" s="64" t="inlineStr">
+        <is>
+          <t>Mission list, pass XP, and pass rewards modified</t>
+        </is>
+      </c>
+      <c r="L20" s="66" t="inlineStr">
         <is>
           <t>Jinho Ha</t>
         </is>
       </c>
-      <c r="L20" s="103" t="n"/>
       <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="62" t="n"/>
-      <c r="C21" s="63" t="n"/>
-      <c r="D21" s="64" t="n"/>
-      <c r="L21" s="66" t="n"/>
-      <c r="M21" s="6" t="n"/>
+      <c r="B21" s="46" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
+      <c r="L21" s="46" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="46" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
-      <c r="L22" s="46" t="n"/>
+      <c r="D22" s="27" t="n"/>
     </row>
     <row r="23">
       <c r="D23" s="27" t="n"/>
@@ -2861,13 +2812,7 @@
     <row r="42">
       <c r="D42" s="27" t="n"/>
     </row>
-    <row r="43">
-      <c r="D43" s="27" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
@@ -2880,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H361"/>
+  <dimension ref="A2:F360"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="2.625" customWidth="1" style="9" min="1" max="1"/>
@@ -2899,47 +2844,50 @@
     <col width="2.625" customWidth="1" style="9" min="55" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="72">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="72"/>
+    <row r="1" s="72"/>
+    <row r="2" ht="16.5" customHeight="1" s="72">
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+    </row>
     <row r="3" ht="16.5" customHeight="1" s="72">
       <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
+      <c r="C3" s="67" t="inlineStr">
+        <is>
+          <t>Season Pass</t>
+        </is>
+      </c>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="72">
       <c r="B4" s="9" t="n"/>
-      <c r="C4" s="67" t="inlineStr">
-        <is>
-          <t>Season Pass</t>
-        </is>
-      </c>
+      <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="72">
       <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>■ Design Intent</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="72">
       <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>■ Design Intent</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>- Encourages continuous player visits</t>
+        </is>
+      </c>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
     </row>
@@ -2947,7 +2895,7 @@
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>- Encourages continuous player visits</t>
+          <t>- Provides means for players to intuitively understand their game progress</t>
         </is>
       </c>
       <c r="E7" s="9" t="n"/>
@@ -2957,7 +2905,7 @@
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>- Provides means for players to intuitively understand their game progress</t>
+          <t>- Provides diverse cosmetics through Season Pass rewards to showcase to other players</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -2965,46 +2913,43 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="72">
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>- Provides diverse cosmetics through Season Pass rewards to showcase to other players</t>
-        </is>
-      </c>
+      <c r="C9" s="10" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="72">
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
+      <c r="A10" s="68" t="n"/>
+      <c r="B10" s="69" t="n"/>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>■ UI</t>
+        </is>
+      </c>
+      <c r="D10" s="69" t="n"/>
+      <c r="E10" s="69" t="n"/>
+      <c r="F10" s="69" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="72">
-      <c r="A11" s="68" t="n"/>
-      <c r="B11" s="69" t="n"/>
-      <c r="C11" s="70" t="inlineStr">
-        <is>
-          <t>■ UI</t>
-        </is>
-      </c>
-      <c r="D11" s="69" t="n"/>
-      <c r="E11" s="69" t="n"/>
-      <c r="F11" s="69" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="72">
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>■ Access Method</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="72">
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>■ Access Method</t>
-        </is>
-      </c>
+      <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -3030,13 +2975,7 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
     </row>
-    <row r="17" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-    </row>
+    <row r="17" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="18" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="19" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="20" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3049,29 +2988,29 @@
     <row r="27" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="28" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="29" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="30" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="31" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C31" s="9" t="inlineStr">
+    <row r="30" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>- Main Menu → Click Rank button</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="31" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="32" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>■ Unlock Timing</t>
+        </is>
+      </c>
+    </row>
     <row r="33" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>■ Unlock Timing</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>- Quest: During Hermit's Forest [Talking Owl]</t>
         </is>
       </c>
     </row>
+    <row r="34" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="35" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="36" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="37" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3089,21 +3028,21 @@
     <row r="49" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="50" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="51" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="52" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="52" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>■ UI Composition</t>
+        </is>
+      </c>
+    </row>
     <row r="53" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>■ UI Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>- Main Screen</t>
         </is>
       </c>
     </row>
+    <row r="54" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="55" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="56" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="57" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3126,133 +3065,167 @@
     <row r="74" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="75" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="76" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="77" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="77" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>time(s)</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
     <row r="78" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>time(s)</t>
-        </is>
+      <c r="C78" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>On click, go back</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C79" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>Back</t>
-        </is>
-      </c>
-      <c r="E79" s="17" t="inlineStr">
-        <is>
-          <t>On click, go back</t>
+          <t>Pass Type</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>On click, display that pass type information on right screen.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C80" s="86" t="n"/>
       <c r="D80" s="86" t="n"/>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>On click, display that pass type information on right screen.</t>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>Season Reward Selectapplied state to UI Info Display</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C81" s="86" t="n"/>
-      <c r="D81" s="86" t="n"/>
-      <c r="E81" s="16" t="inlineStr">
-        <is>
-          <t>Season Reward Selectapplied state to UI Info Display</t>
+      <c r="C81" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>Pass Rank Icon</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>Click when, Separate's Function None/N/A.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C82" s="86" t="n"/>
       <c r="D82" s="86" t="n"/>
-      <c r="E82" s="14" t="inlineStr">
-        <is>
-          <t>Click when, Separate's Function None/N/A.</t>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>Current Pass's Rank Icon to Display</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C83" s="86" t="n"/>
-      <c r="D83" s="86" t="n"/>
-      <c r="E83" s="16" t="inlineStr">
-        <is>
-          <t>Current Pass's Rank Icon to Display</t>
+      <c r="C83" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>Pass Name</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>Click when, Separate's Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="84" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C84" s="86" t="n"/>
       <c r="D84" s="86" t="n"/>
-      <c r="E84" s="14" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>Current Pass's TRName Display</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C85" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>Pass Time Remaining</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>Click when, Separate's Function None/N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C85" s="86" t="n"/>
-      <c r="D85" s="86" t="n"/>
-      <c r="E85" s="16" t="inlineStr">
-        <is>
-          <t>Current Pass's TRName Display</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C86" s="86" t="n"/>
       <c r="D86" s="86" t="n"/>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Click when, Separate's Function None/N/A</t>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>Current Pass's Deadline Time DDDay HH when MMMinute to Display</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C87" s="86" t="n"/>
-      <c r="D87" s="86" t="n"/>
-      <c r="E87" s="16" t="inlineStr">
-        <is>
-          <t>Current Pass's Deadline Time DDDay HH when MMMinute to Display</t>
+      <c r="C87" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D87" s="29" t="inlineStr">
+        <is>
+          <t>Select Past Season</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>(#1) Click when, All season Dropdown to Display. Again Click when, Window close</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C88" s="87" t="n"/>
       <c r="D88" s="87" t="n"/>
-      <c r="E88" s="14" t="inlineStr">
-        <is>
-          <t>(#1) Click when, All season Dropdown to Display. Again Click when, Window close</t>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>(#2) Click when, Corresponding season's Season Pass Display</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C89" s="87" t="n"/>
       <c r="D89" s="87" t="n"/>
-      <c r="E89" s="15" t="inlineStr">
-        <is>
-          <t>(#2) Click when, Corresponding season's Season Pass Display</t>
-        </is>
-      </c>
+      <c r="E89" s="26" t="n"/>
     </row>
     <row r="90" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C90" s="87" t="n"/>
       <c r="D90" s="87" t="n"/>
-      <c r="E90" s="26" t="n"/>
+      <c r="E90" s="15" t="n"/>
     </row>
     <row r="91" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C91" s="87" t="n"/>
@@ -3307,50 +3280,72 @@
     <row r="101" ht="13.5" customFormat="1" customHeight="1" s="9">
       <c r="C101" s="86" t="n"/>
       <c r="D101" s="86" t="n"/>
-      <c r="E101" s="15" t="n"/>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reward Claim Date case, Corresponding season UI in </t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C102" s="86" t="n"/>
-      <c r="D102" s="86" t="n"/>
-      <c r="E102" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reward Claim Date case, Corresponding season UI in </t>
+      <c r="C102" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D102" s="30" t="inlineStr">
+        <is>
+          <t>Progress Bar</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>(Achieve EXP / Corresponding season in Maximum to can present EXP) number Display</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C103" s="86" t="n"/>
-      <c r="D103" s="86" t="n"/>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>(Achieve EXP / Corresponding season in Maximum to can present EXP) number Display</t>
+      <c r="D103" s="88" t="n"/>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>Achieve Degree Progress Bar form to Display</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C104" s="86" t="n"/>
-      <c r="D104" s="88" t="n"/>
-      <c r="E104" s="16" t="inlineStr">
-        <is>
-          <t>Achieve Degree Progress Bar form to Display</t>
+      <c r="C104" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" s="30" t="inlineStr">
+        <is>
+          <t>Season Reward Tab</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Click when, Corresponding Button Highlight And Corresponding season's Season Reward List Below Display</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C105" s="86" t="n"/>
       <c r="D105" s="88" t="n"/>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>Click when, Corresponding Button Highlight And Corresponding season's Season Reward List Below Display</t>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>Again Click when, Separate's None/N/A</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C106" s="86" t="n"/>
-      <c r="D106" s="88" t="n"/>
-      <c r="E106" s="16" t="inlineStr">
-        <is>
-          <t>Again Click when, Separate's None/N/A</t>
+      <c r="C106" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D106" s="30" t="inlineStr">
+        <is>
+          <t>Weekly Mission Tab</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>On click, highlight button and display weekly mission list below</t>
         </is>
       </c>
     </row>
@@ -3359,43 +3354,55 @@
       <c r="D107" s="89" t="n"/>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>On click, highlight button and display weekly mission list below</t>
+          <t>Again Click when, Separate's None/N/A</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C108" s="86" t="n"/>
       <c r="D108" s="88" t="n"/>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>Again Click when, Separate's None/N/A</t>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>one week reset DD HH displayed</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C109" s="86" t="n"/>
-      <c r="D109" s="88" t="n"/>
-      <c r="E109" s="16" t="inlineStr">
-        <is>
-          <t>one week reset DD HH displayed</t>
+      <c r="C109" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D109" s="30" t="inlineStr">
+        <is>
+          <t>Season Mission Tab</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>Click when, Corresponding Button Highlight And Corresponding season's season Mission Info List Below Display</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C110" s="86" t="n"/>
       <c r="D110" s="88" t="n"/>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>Click when, Corresponding Button Highlight And Corresponding season's season Mission Info List Below Display</t>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>Again Click when, Separate's None/N/A</t>
         </is>
       </c>
     </row>
     <row r="111" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C111" s="86" t="n"/>
-      <c r="D111" s="88" t="n"/>
-      <c r="E111" s="16" t="inlineStr">
-        <is>
-          <t>Again Click when, Separate's None/N/A</t>
+      <c r="C111" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="D111" s="30" t="inlineStr">
+        <is>
+          <t>Challenge Mission Tab</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mission Enter Impossible when, Click case</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3411,7 @@
       <c r="D112" s="89" t="n"/>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mission Enter Impossible when, Click case</t>
+          <t>-Corresponding Tab to Move Without System Message Display “{PassLevel_TRName} Unlock.”</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3420,7 @@
       <c r="D113" s="89" t="n"/>
       <c r="E113" s="15" t="inlineStr">
         <is>
-          <t>-Corresponding Tab to Move Without System Message Display “{PassLevel_TRName} Unlock.”</t>
+          <t xml:space="preserve"> Mission Enter Possible when, Click case</t>
         </is>
       </c>
     </row>
@@ -3422,25 +3429,31 @@
       <c r="D114" s="89" t="n"/>
       <c r="E114" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mission Enter Possible when, Click case</t>
+          <t>-Corresponding Button Highlight And Corresponding season's Mission Info List Below Display</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C115" s="86" t="n"/>
       <c r="D115" s="88" t="n"/>
-      <c r="E115" s="15" t="inlineStr">
-        <is>
-          <t>-Corresponding Button Highlight And Corresponding season's Mission Info List Below Display</t>
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>-Again Click when, Separate's None/N/A</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C116" s="86" t="n"/>
-      <c r="D116" s="88" t="n"/>
-      <c r="E116" s="16" t="inlineStr">
-        <is>
-          <t>-Again Click when, Separate's None/N/A</t>
+      <c r="C116" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" s="30" t="inlineStr">
+        <is>
+          <t>Claimed Season Reward</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>Already Claim Season Reward Display</t>
         </is>
       </c>
     </row>
@@ -3449,25 +3462,31 @@
       <c r="D117" s="89" t="n"/>
       <c r="E117" s="15" t="inlineStr">
         <is>
-          <t>Already Claim Season Reward Display</t>
+          <t>Click when, Item tooltip Display</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C118" s="86" t="n"/>
       <c r="D118" s="88" t="n"/>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>Click when, Item tooltip Display</t>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>Greyscale processing And green V Check</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C119" s="86" t="n"/>
-      <c r="D119" s="88" t="n"/>
-      <c r="E119" s="16" t="inlineStr">
-        <is>
-          <t>Greyscale processing And green V Check</t>
+      <c r="C119" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D119" s="30" t="inlineStr">
+        <is>
+          <t>Claimable Season Reward</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>Claim can present Season Reward Display</t>
         </is>
       </c>
     </row>
@@ -3476,54 +3495,52 @@
       <c r="D120" s="89" t="n"/>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>Claim can present Season Reward Display</t>
+          <t>Click when, Item Claim After Claim Season Reward to Change Display</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C121" s="86" t="n"/>
       <c r="D121" s="88" t="n"/>
-      <c r="E121" s="15" t="inlineStr">
-        <is>
-          <t>Click when, Item Claim After Claim Season Reward to Change Display</t>
+      <c r="E121" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item Reward Claim UI </t>
         </is>
       </c>
     </row>
     <row r="122" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C122" s="86" t="n"/>
-      <c r="D122" s="88" t="n"/>
-      <c r="E122" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Item Reward Claim UI </t>
+      <c r="C122" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D122" s="30" t="inlineStr">
+        <is>
+          <t>Unclaimed Season Reward</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>Claim can without Season Reward Display</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C123" s="86" t="n"/>
       <c r="D123" s="88" t="n"/>
-      <c r="E123" s="15" t="inlineStr">
-        <is>
-          <t>Claim can without Season Reward Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C124" s="86" t="n"/>
-      <c r="D124" s="88" t="n"/>
-      <c r="E124" s="16" t="inlineStr">
+      <c r="E123" s="16" t="inlineStr">
         <is>
           <t>Click when, Item tooltip Display</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="126" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C126" s="10" t="inlineStr">
+    <row r="124" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="125" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>- Each Mission Tab</t>
         </is>
       </c>
     </row>
+    <row r="126" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="127" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="128" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="129" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3547,167 +3564,203 @@
     <row r="147" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="148" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="149" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="150" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="150" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C150" s="29" t="inlineStr">
+        <is>
+          <t>time(s)</t>
+        </is>
+      </c>
+      <c r="D150" s="29" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E150" s="29" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
     <row r="151" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C151" s="29" t="inlineStr">
-        <is>
-          <t>time(s)</t>
-        </is>
+      <c r="C151" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="D151" s="29" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E151" s="29" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="152" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C152" s="87" t="n"/>
       <c r="D152" s="87" t="n"/>
-      <c r="E152" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Function None/N/A</t>
+      <c r="E152" s="71" t="inlineStr">
+        <is>
+          <t>Corresponding Mission's TRName And Desc Display</t>
         </is>
       </c>
     </row>
     <row r="153" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C153" s="86" t="n"/>
       <c r="D153" s="86" t="n"/>
-      <c r="E153" s="71" t="inlineStr">
-        <is>
-          <t>Corresponding Mission's TRName And Desc Display</t>
+      <c r="E153" s="20" t="inlineStr">
+        <is>
+          <t>(achieve / ) displayed</t>
         </is>
       </c>
     </row>
     <row r="154" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C154" s="86" t="n"/>
-      <c r="D154" s="86" t="n"/>
-      <c r="E154" s="20" t="inlineStr">
-        <is>
-          <t>(achieve / ) displayed</t>
+      <c r="C154" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" s="29" t="inlineStr">
+        <is>
+          <t>Reward Display</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>Corresponding Mission Achieve when, Obtaindoing Reward Display</t>
         </is>
       </c>
     </row>
     <row r="155" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C155" s="86" t="n"/>
       <c r="D155" s="86" t="n"/>
-      <c r="E155" s="19" t="inlineStr">
-        <is>
-          <t>Corresponding Mission Achieve when, Obtaindoing Reward Display</t>
+      <c r="E155" s="20" t="inlineStr">
+        <is>
+          <t>Click when, Item tooltip Display</t>
         </is>
       </c>
     </row>
     <row r="156" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C156" s="86" t="n"/>
-      <c r="D156" s="86" t="n"/>
-      <c r="E156" s="20" t="inlineStr">
-        <is>
-          <t>Click when, Item tooltip Display</t>
+      <c r="C156" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" s="29" t="inlineStr">
+        <is>
+          <t>Claim Reward Button</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Corresponding Mission's Reward Obtain And Corresponding List Below to My Complete processing</t>
         </is>
       </c>
     </row>
     <row r="157" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C157" s="86" t="n"/>
       <c r="D157" s="86" t="n"/>
-      <c r="E157" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Corresponding Mission's Reward Obtain And Corresponding List Below to My Complete processing</t>
+      <c r="E157" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item Reward Claim UI </t>
         </is>
       </c>
     </row>
     <row r="158" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C158" s="86" t="n"/>
-      <c r="D158" s="86" t="n"/>
-      <c r="E158" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Item Reward Claim UI </t>
+      <c r="C158" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D158" s="29" t="inlineStr">
+        <is>
+          <t>Complete List</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="159" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C159" s="86" t="n"/>
       <c r="D159" s="86" t="n"/>
-      <c r="E159" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Function None/N/A</t>
+      <c r="E159" s="20" t="inlineStr">
+        <is>
+          <t>Corresponding List Greyscale processing, Reward Icon green V Display</t>
         </is>
       </c>
     </row>
     <row r="160" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C160" s="86" t="n"/>
-      <c r="D160" s="86" t="n"/>
-      <c r="E160" s="20" t="inlineStr">
-        <is>
-          <t>Corresponding List Greyscale processing, Reward Icon green V Display</t>
+      <c r="C160" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D160" s="29" t="inlineStr">
+        <is>
+          <t>this week obtain possible EXP displayed</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>(achieve EXP / this week EXP) displayed</t>
         </is>
       </c>
     </row>
     <row r="161" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C161" s="87" t="n"/>
       <c r="D161" s="87" t="n"/>
-      <c r="E161" s="19" t="inlineStr">
-        <is>
-          <t>(achieve EXP / this week EXP) displayed</t>
+      <c r="E161" s="71" t="inlineStr">
+        <is>
+          <t>Achieve Degree Progress Bar form to Display</t>
         </is>
       </c>
     </row>
     <row r="162" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C162" s="86" t="n"/>
       <c r="D162" s="86" t="n"/>
-      <c r="E162" s="71" t="inlineStr">
-        <is>
-          <t>Achieve Degree Progress Bar form to Display</t>
+      <c r="E162" s="20" t="inlineStr">
+        <is>
+          <t>Weekly Mission Tab in only Display</t>
         </is>
       </c>
     </row>
     <row r="163" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C163" s="86" t="n"/>
-      <c r="D163" s="86" t="n"/>
-      <c r="E163" s="20" t="inlineStr">
-        <is>
-          <t>Weekly Mission Tab in only Display</t>
+      <c r="C163" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" s="29" t="inlineStr">
+        <is>
+          <t>Claim All Button</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Claim Available All Reward time(s) Obtain</t>
         </is>
       </c>
     </row>
     <row r="164" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C164" s="87" t="n"/>
       <c r="D164" s="87" t="n"/>
-      <c r="E164" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Claim Available All Reward time(s) Obtain</t>
+      <c r="E164" s="71" t="inlineStr">
+        <is>
+          <t>Claim Available Reward without case Greyscale processing</t>
         </is>
       </c>
     </row>
     <row r="165" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C165" s="86" t="n"/>
       <c r="D165" s="86" t="n"/>
-      <c r="E165" s="71" t="inlineStr">
-        <is>
-          <t>Claim Available Reward without case Greyscale processing</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C166" s="86" t="n"/>
-      <c r="D166" s="86" t="n"/>
-      <c r="E166" s="20" t="inlineStr">
+      <c r="E165" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Claim Possible Reward without state in Click when,“Obtain Available Reward.”System Message </t>
         </is>
       </c>
     </row>
-    <row r="167" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="168" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C168" s="10" t="inlineStr">
+    <row r="166" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="167" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C167" s="10" t="inlineStr">
         <is>
           <t>- types applied season Display</t>
         </is>
       </c>
     </row>
+    <row r="168" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="169" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="170" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="171" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -3726,69 +3779,79 @@
     <row r="184" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="185" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="186" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="187" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="187" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C187" s="29" t="inlineStr">
+        <is>
+          <t>time(s)</t>
+        </is>
+      </c>
+      <c r="D187" s="29" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E187" s="29" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
     <row r="188" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C188" s="29" t="inlineStr">
-        <is>
-          <t>time(s)</t>
-        </is>
+      <c r="C188" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="D188" s="29" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E188" s="29" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>Reward Claim Time</t>
+        </is>
+      </c>
+      <c r="E188" s="19" t="inlineStr">
+        <is>
+          <t>Click when, Function None/N/A</t>
         </is>
       </c>
     </row>
     <row r="189" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C189" s="86" t="n"/>
       <c r="D189" s="86" t="n"/>
-      <c r="E189" s="19" t="inlineStr">
-        <is>
-          <t>Click when, Function None/N/A</t>
+      <c r="E189" s="20" t="inlineStr">
+        <is>
+          <t>Corresponding season's Reward Claim Available Date DDDay HH when MMMinute to Display</t>
         </is>
       </c>
     </row>
     <row r="190" ht="224.25" customFormat="1" customHeight="1" s="9">
-      <c r="C190" s="86" t="n"/>
-      <c r="D190" s="86" t="n"/>
-      <c r="E190" s="20" t="inlineStr">
-        <is>
-          <t>Corresponding season's Reward Claim Available Date DDDay HH when MMMinute to Display</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C191" s="29" t="n">
+      <c r="C190" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="D191" s="29" t="inlineStr">
+      <c r="D190" s="29" t="inlineStr">
         <is>
           <t>Tab Area</t>
         </is>
       </c>
-      <c r="E191" s="25" t="inlineStr">
+      <c r="E190" s="25" t="inlineStr">
         <is>
           <t>Weekly Mission Tab Remove
 season Mission, Mission Tab Click when Each Mission All Deactivate state to DisplayDone/Applied</t>
         </is>
       </c>
     </row>
+    <row r="191" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C191" s="23" t="n"/>
+      <c r="D191" s="23" t="n"/>
+      <c r="E191" s="18" t="n"/>
+    </row>
     <row r="192" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C192" s="23" t="n"/>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>- HUD</t>
+        </is>
+      </c>
       <c r="D192" s="23" t="n"/>
       <c r="E192" s="18" t="n"/>
     </row>
     <row r="193" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C193" s="10" t="inlineStr">
-        <is>
-          <t>- HUD</t>
-        </is>
-      </c>
+      <c r="C193" s="23" t="n"/>
       <c r="D193" s="23" t="n"/>
       <c r="E193" s="18" t="n"/>
     </row>
@@ -3868,9 +3931,11 @@
       <c r="E208" s="18" t="n"/>
     </row>
     <row r="209" ht="16.5" customHeight="1" s="72">
+      <c r="B209" s="9" t="n"/>
       <c r="C209" s="23" t="n"/>
       <c r="D209" s="23" t="n"/>
       <c r="E209" s="18" t="n"/>
+      <c r="F209" s="9" t="n"/>
     </row>
     <row r="210" ht="16.5" customHeight="1" s="72">
       <c r="B210" s="9" t="n"/>
@@ -3881,7 +3946,11 @@
     </row>
     <row r="211" ht="16.5" customHeight="1" s="72">
       <c r="B211" s="9" t="n"/>
-      <c r="C211" s="23" t="n"/>
+      <c r="C211" s="24" t="inlineStr">
+        <is>
+          <t>- Screen Below Current season's Rank Icon Display</t>
+        </is>
+      </c>
       <c r="D211" s="23" t="n"/>
       <c r="E211" s="18" t="n"/>
       <c r="F211" s="9" t="n"/>
@@ -3890,7 +3959,7 @@
       <c r="B212" s="9" t="n"/>
       <c r="C212" s="24" t="inlineStr">
         <is>
-          <t>- Screen Below Current season's Rank Icon Display</t>
+          <t xml:space="preserve"> - Button to Click also Separate's Function None/N/A</t>
         </is>
       </c>
       <c r="D212" s="23" t="n"/>
@@ -3901,7 +3970,7 @@
       <c r="B213" s="9" t="n"/>
       <c r="C213" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Button to Click also Separate's Function None/N/A</t>
+          <t>- , area</t>
         </is>
       </c>
       <c r="D213" s="23" t="n"/>
@@ -3910,57 +3979,57 @@
     </row>
     <row r="214" ht="16.5" customHeight="1" s="72">
       <c r="B214" s="9" t="n"/>
-      <c r="C214" s="24" t="inlineStr">
-        <is>
-          <t>- , area</t>
-        </is>
-      </c>
+      <c r="C214" s="23" t="n"/>
       <c r="D214" s="23" t="n"/>
       <c r="E214" s="18" t="n"/>
       <c r="F214" s="9" t="n"/>
     </row>
     <row r="215" ht="16.5" customHeight="1" s="72">
-      <c r="B215" s="9" t="n"/>
-      <c r="C215" s="23" t="n"/>
-      <c r="D215" s="23" t="n"/>
-      <c r="E215" s="18" t="n"/>
-      <c r="F215" s="9" t="n"/>
+      <c r="A215" s="68" t="n"/>
+      <c r="B215" s="69" t="n"/>
+      <c r="C215" s="70" t="inlineStr">
+        <is>
+          <t>■ Details</t>
+        </is>
+      </c>
+      <c r="D215" s="69" t="n"/>
+      <c r="E215" s="69" t="n"/>
+      <c r="F215" s="69" t="n"/>
     </row>
     <row r="216" ht="16.5" customHeight="1" s="72">
-      <c r="A216" s="68" t="n"/>
-      <c r="B216" s="69" t="n"/>
-      <c r="C216" s="70" t="inlineStr">
-        <is>
-          <t>■ Details</t>
-        </is>
-      </c>
-      <c r="D216" s="69" t="n"/>
-      <c r="E216" s="69" t="n"/>
-      <c r="F216" s="69" t="n"/>
+      <c r="B216" s="9" t="n"/>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>※ Current Season Pass document reflects ranking system requested by Bilibili.</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="n"/>
+      <c r="E216" s="9" t="n"/>
+      <c r="F216" s="9" t="n"/>
     </row>
     <row r="217" ht="16.5" customHeight="1" s="72">
       <c r="B217" s="9" t="n"/>
-      <c r="C217" s="9" t="inlineStr">
-        <is>
-          <t>※ Current Season Pass document reflects ranking system requested by Bilibili.</t>
-        </is>
-      </c>
+      <c r="C217" s="9" t="n"/>
       <c r="D217" s="9" t="n"/>
       <c r="E217" s="9" t="n"/>
       <c r="F217" s="9" t="n"/>
     </row>
     <row r="218" ht="16.5" customHeight="1" s="72">
       <c r="B218" s="9" t="n"/>
-      <c r="C218" s="9" t="n"/>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>■ Season and Mission Structure</t>
+        </is>
+      </c>
       <c r="D218" s="9" t="n"/>
       <c r="E218" s="9" t="n"/>
       <c r="F218" s="9" t="n"/>
     </row>
     <row r="219" ht="16.5" customHeight="1" s="72">
       <c r="B219" s="9" t="n"/>
-      <c r="C219" s="9" t="inlineStr">
-        <is>
-          <t>■ Season and Mission Structure</t>
+      <c r="C219" s="10" t="inlineStr">
+        <is>
+          <t>- Each pass activates as a season for a set duration</t>
         </is>
       </c>
       <c r="D219" s="9" t="n"/>
@@ -3971,7 +4040,7 @@
       <c r="B220" s="9" t="n"/>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>- Each pass activates as a season for a set duration</t>
+          <t>→ Start and end of all periods based on specified date server region time 06:00</t>
         </is>
       </c>
       <c r="D220" s="9" t="n"/>
@@ -3982,7 +4051,7 @@
       <c r="B221" s="9" t="n"/>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>→ Start and end of all periods based on specified date server region time 06:00</t>
+          <t>- During season progression, complete weekly, season, and challenge missions to earn pass XP and levels</t>
         </is>
       </c>
       <c r="D221" s="9" t="n"/>
@@ -3991,9 +4060,9 @@
     </row>
     <row r="222" ht="16.5" customHeight="1" s="72">
       <c r="B222" s="9" t="n"/>
-      <c r="C222" s="10" t="inlineStr">
-        <is>
-          <t>- During season progression, complete weekly, season, and challenge missions to earn pass XP and levels</t>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>→ Weekly missions: Reset each week with weekly XP limit</t>
         </is>
       </c>
       <c r="D222" s="9" t="n"/>
@@ -4004,7 +4073,7 @@
       <c r="B223" s="9" t="n"/>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>→ Weekly missions: Reset each week with weekly XP limit</t>
+          <t>→ Season missions: Completable until season ends</t>
         </is>
       </c>
       <c r="D223" s="9" t="n"/>
@@ -4015,7 +4084,7 @@
       <c r="B224" s="9" t="n"/>
       <c r="C224" s="9" t="inlineStr">
         <is>
-          <t>→ Season missions: Completable until season ends</t>
+          <t>→ Challenge missions: Revealed when reaching specific pass level</t>
         </is>
       </c>
       <c r="D224" s="9" t="n"/>
@@ -4023,232 +4092,237 @@
       <c r="F224" s="9" t="n"/>
     </row>
     <row r="225" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="B225" s="9" t="n"/>
       <c r="C225" s="9" t="inlineStr">
         <is>
-          <t>→ Challenge missions: Revealed when reaching specific pass level</t>
-        </is>
-      </c>
-      <c r="D225" s="9" t="n"/>
-      <c r="E225" s="9" t="n"/>
-      <c r="F225" s="9" t="n"/>
+          <t>→ For cumulative missions, progress counts even before challenge mission appears</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C226" s="9" t="inlineStr">
-        <is>
-          <t>→ For cumulative missions, progress counts even before challenge mission appears</t>
+      <c r="C226" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="227" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve"> ● Cumulative</t>
         </is>
       </c>
     </row>
     <row r="228" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C228" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ● Cumulative</t>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>) composition , 300 , Challenge Mission , 300/1,000</t>
         </is>
       </c>
     </row>
     <row r="229" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>) composition , 300 , Challenge Mission , 300/1,000</t>
+          <t xml:space="preserve"> Weekly Mission : Shard 10 use</t>
         </is>
       </c>
     </row>
     <row r="230" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C230" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Weekly Mission : Shard 10 use</t>
+          <t xml:space="preserve"> season Mission : Shard 100 use</t>
         </is>
       </c>
     </row>
     <row r="231" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C231" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> season Mission : Shard 100 use</t>
+          <t xml:space="preserve"> Mission : Shard 1,000 use</t>
         </is>
       </c>
     </row>
     <row r="232" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C232" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Mission : Shard 1,000 use</t>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ● Quest Progress when Count</t>
         </is>
       </c>
     </row>
     <row r="233" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C233" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ● Quest Progress when Count</t>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> when) Below and as follows Composition when, Weekly Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
         </is>
       </c>
     </row>
     <row r="234" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> when) Below and as follows Composition when, Weekly Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
+          <t xml:space="preserve"> Weekly Mission : Monster 10creatures Defeat</t>
         </is>
       </c>
     </row>
     <row r="235" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C235" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Weekly Mission : Monster 10creatures Defeat</t>
+          <t xml:space="preserve"> season Mission : Monster 100creatures Defeat</t>
         </is>
       </c>
     </row>
     <row r="236" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> season Mission : Monster 100creatures Defeat</t>
+          <t xml:space="preserve"> Mission : Monster 1,000creatures Defeat</t>
         </is>
       </c>
     </row>
     <row r="237" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C237" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mission : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C238" s="9" t="inlineStr">
-        <is>
           <t xml:space="preserve">※ Each Mission's Type according to 's after Cumulative, Quest Progress when Count Select </t>
         </is>
       </c>
     </row>
-    <row r="239" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="238" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="239" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>■ Rewards</t>
+        </is>
+      </c>
+    </row>
     <row r="240" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C240" s="9" t="inlineStr">
-        <is>
-          <t>■ Rewards</t>
+      <c r="C240" s="10" t="inlineStr">
+        <is>
+          <t>- One season reward granted upon reaching each pass level</t>
         </is>
       </c>
     </row>
     <row r="241" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>- One season reward granted upon reaching each pass level</t>
+          <t>- Rewards can include premium currency, exclusive name tags, titles, profile skins, and cosmetics</t>
         </is>
       </c>
     </row>
     <row r="242" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>- Rewards can include premium currency, exclusive name tags, titles, profile skins, and cosmetics</t>
+          <t xml:space="preserve"> → Reward's 's after Modify Possible</t>
         </is>
       </c>
     </row>
     <row r="243" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Reward's 's after Modify Possible</t>
+          <t>- Pass XP and rewards granted upon completing each mission</t>
         </is>
       </c>
     </row>
     <row r="244" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>- Pass XP and rewards granted upon completing each mission</t>
+          <t>- All rewards obtained by clicking their icon</t>
         </is>
       </c>
     </row>
     <row r="245" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>- All rewards obtained by clicking their icon</t>
+          <t xml:space="preserve"> → through Providedoing case None/N/A</t>
         </is>
       </c>
     </row>
     <row r="246" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → through Providedoing case None/N/A</t>
+          <t>- Unclaimed rewards can be collected for a period after season ends</t>
         </is>
       </c>
     </row>
     <row r="247" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C247" s="10" t="inlineStr">
-        <is>
-          <t>- Unclaimed rewards can be collected for a period after season ends</t>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>→ Missions cannot be completed after season ends</t>
         </is>
       </c>
     </row>
     <row r="248" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C248" s="9" t="inlineStr">
         <is>
-          <t>→ Missions cannot be completed after season ends</t>
+          <t>→ Weekly mission rewards and progress reset at season end</t>
         </is>
       </c>
     </row>
     <row r="249" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C249" s="9" t="inlineStr">
         <is>
-          <t>→ Weekly mission rewards and progress reset at season end</t>
+          <t>→ If pass levels up from claiming already-completed season/challenge mission rewards, season rewards can be claimed</t>
         </is>
       </c>
     </row>
     <row r="250" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C250" s="9" t="inlineStr">
-        <is>
-          <t>→ If pass levels up from claiming already-completed season/challenge mission rewards, season rewards can be claimed</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C251" s="10" t="inlineStr">
+      <c r="C250" s="10" t="inlineStr">
         <is>
           <t>→ If reward collection period passes after season ends, no rewards can be claimed</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="251" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="252" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C252" s="9" t="inlineStr">
+        <is>
+          <t>■ Season Rank</t>
+        </is>
+      </c>
+    </row>
     <row r="253" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C253" s="9" t="inlineStr">
-        <is>
-          <t>■ Season Rank</t>
+      <c r="C253" s="10" t="inlineStr">
+        <is>
+          <t>- Divided into 9 total stages by season level range. Icon and number change in UI each rank increase</t>
         </is>
       </c>
     </row>
     <row r="254" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C254" s="10" t="inlineStr">
-        <is>
-          <t>- Divided into 9 total stages by season level range. Icon and number change in UI each rank increase</t>
+      <c r="C254" s="28" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="D254" s="28" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E254" s="28" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="F254" s="21" t="inlineStr">
+        <is>
+          <t>Level Range</t>
         </is>
       </c>
     </row>
     <row r="255" ht="66.75" customFormat="1" customHeight="1" s="9">
-      <c r="C255" s="28" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D255" s="28" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E255" s="28" t="inlineStr">
-        <is>
-          <t>Icon</t>
-        </is>
-      </c>
-      <c r="F255" s="21" t="inlineStr">
-        <is>
-          <t>Level Range</t>
+      <c r="C255" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E255" s="21" t="n"/>
+      <c r="F255" s="28" t="inlineStr">
+        <is>
+          <t>1 ~ 9</t>
         </is>
       </c>
     </row>
     <row r="256" ht="66.75" customFormat="1" customHeight="1" s="9">
-      <c r="C256" s="22" t="n">
-        <v>1</v>
+      <c r="C256" s="28" t="n">
+        <v>2</v>
       </c>
       <c r="D256" s="21" t="inlineStr">
         <is>
@@ -4258,158 +4332,143 @@
       <c r="E256" s="21" t="n"/>
       <c r="F256" s="28" t="inlineStr">
         <is>
-          <t>1 ~ 9</t>
+          <t>10 ~ 17</t>
         </is>
       </c>
     </row>
     <row r="257" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C257" s="28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D257" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>gold</t>
         </is>
       </c>
       <c r="E257" s="21" t="n"/>
       <c r="F257" s="28" t="inlineStr">
         <is>
-          <t>10 ~ 17</t>
+          <t>18 ~ 24</t>
         </is>
       </c>
     </row>
     <row r="258" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C258" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D258" s="21" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="E258" s="21" t="n"/>
       <c r="F258" s="28" t="inlineStr">
         <is>
-          <t>18 ~ 24</t>
+          <t>25 ~ 30</t>
         </is>
       </c>
     </row>
     <row r="259" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C259" s="28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D259" s="21" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="E259" s="21" t="n"/>
       <c r="F259" s="28" t="inlineStr">
         <is>
-          <t>25 ~ 30</t>
+          <t>31 ~ 35</t>
         </is>
       </c>
     </row>
     <row r="260" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C260" s="28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D260" s="21" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E260" s="21" t="n"/>
       <c r="F260" s="28" t="inlineStr">
         <is>
-          <t>31 ~ 35</t>
+          <t>36 ~ 39</t>
         </is>
       </c>
     </row>
     <row r="261" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C261" s="28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D261" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Grandmaster</t>
         </is>
       </c>
       <c r="E261" s="21" t="n"/>
       <c r="F261" s="28" t="inlineStr">
         <is>
-          <t>36 ~ 39</t>
+          <t>40 ~ 42</t>
         </is>
       </c>
     </row>
     <row r="262" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C262" s="28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D262" s="21" t="inlineStr">
         <is>
-          <t>Grandmaster</t>
+          <t xml:space="preserve"> That/I</t>
         </is>
       </c>
       <c r="E262" s="21" t="n"/>
       <c r="F262" s="28" t="inlineStr">
         <is>
-          <t>40 ~ 42</t>
+          <t>43 ~ 44</t>
         </is>
       </c>
     </row>
     <row r="263" ht="66.75" customFormat="1" customHeight="1" s="9">
       <c r="C263" s="28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D263" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> That/I</t>
+          <t xml:space="preserve"> before</t>
         </is>
       </c>
       <c r="E263" s="21" t="n"/>
-      <c r="F263" s="28" t="inlineStr">
-        <is>
-          <t>43 ~ 44</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C264" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="D264" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> before</t>
-        </is>
-      </c>
-      <c r="E264" s="21" t="n"/>
-      <c r="F264" s="28" t="n">
+      <c r="F263" s="28" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="265" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="264" ht="16.5" customFormat="1" customHeight="1" s="9"/>
+    <row r="265" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>■ XML</t>
+        </is>
+      </c>
+    </row>
     <row r="266" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C266" s="9" t="inlineStr">
-        <is>
-          <t>■ XML</t>
+      <c r="C266" s="10" t="inlineStr">
+        <is>
+          <t>- Pass.xml</t>
         </is>
       </c>
     </row>
     <row r="267" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C267" s="10" t="inlineStr">
-        <is>
-          <t>- Pass.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C268" s="9" t="inlineStr">
+      <c r="C267" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> → Date, Season Reward Content, Weekly, season, Mission Correspondingdoing Quest ID input</t>
         </is>
       </c>
     </row>
+    <row r="268" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="269" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="270" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="271" ht="16.5" customFormat="1" customHeight="1" s="9"/>
@@ -4430,7 +4489,13 @@
     <row r="286" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="287" ht="16.5" customFormat="1" customHeight="1" s="9"/>
     <row r="288" ht="16.5" customFormat="1" customHeight="1" s="9"/>
-    <row r="289" ht="16.5" customHeight="1" s="72"/>
+    <row r="289" ht="16.5" customHeight="1" s="72">
+      <c r="B289" s="9" t="n"/>
+      <c r="C289" s="9" t="n"/>
+      <c r="D289" s="9" t="n"/>
+      <c r="E289" s="9" t="n"/>
+      <c r="F289" s="9" t="n"/>
+    </row>
     <row r="290" ht="16.5" customHeight="1" s="72">
       <c r="B290" s="9" t="n"/>
       <c r="C290" s="9" t="n"/>
@@ -4502,26 +4567,39 @@
       <c r="F299" s="9" t="n"/>
     </row>
     <row r="300" ht="16.5" customHeight="1" s="72">
-      <c r="B300" s="9" t="n"/>
-      <c r="D300" s="9" t="n"/>
-      <c r="E300" s="9" t="n"/>
+      <c r="B300" s="28" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C300" s="90" t="n"/>
+      <c r="D300" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E300" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
       <c r="F300" s="9" t="n"/>
     </row>
     <row r="301" ht="16.5" customHeight="1" s="72">
       <c r="B301" s="28" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C301" s="90" t="n"/>
       <c r="D301" s="28" t="inlineStr">
         <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E301" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E301" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
       <c r="F301" s="9" t="n"/>
@@ -4529,18 +4607,18 @@
     <row r="302" ht="16.5" customHeight="1" s="72">
       <c r="B302" s="28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>TRName</t>
         </is>
       </c>
       <c r="C302" s="90" t="n"/>
       <c r="D302" s="28" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E302" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Corresponding season's Name</t>
         </is>
       </c>
       <c r="F302" s="9" t="n"/>
@@ -4548,18 +4626,18 @@
     <row r="303" ht="16.5" customHeight="1" s="72">
       <c r="B303" s="28" t="inlineStr">
         <is>
-          <t>TRName</t>
+          <t>ScheduleID</t>
         </is>
       </c>
       <c r="C303" s="90" t="n"/>
       <c r="D303" s="28" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E303" s="21" t="inlineStr">
         <is>
-          <t>Corresponding season's Name</t>
+          <t xml:space="preserve">Corresponding season's Day Schedule.xml's ID and matching when Day </t>
         </is>
       </c>
       <c r="F303" s="9" t="n"/>
@@ -4567,7 +4645,7 @@
     <row r="304" ht="16.5" customHeight="1" s="72">
       <c r="B304" s="28" t="inlineStr">
         <is>
-          <t>ScheduleID</t>
+          <t>RewardScheduleID</t>
         </is>
       </c>
       <c r="C304" s="90" t="n"/>
@@ -4578,7 +4656,7 @@
       </c>
       <c r="E304" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corresponding season's Day Schedule.xml's ID and matching when Day </t>
+          <t xml:space="preserve">Corresponding season's Reward Obtain Possible Schedule.xml's ID and matching when Day </t>
         </is>
       </c>
       <c r="F304" s="9" t="n"/>
@@ -4586,35 +4664,16 @@
     <row r="305" ht="134.25" customHeight="1" s="72">
       <c r="B305" s="28" t="inlineStr">
         <is>
-          <t>RewardScheduleID</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="C305" s="90" t="n"/>
-      <c r="D305" s="28" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E305" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corresponding season's Reward Obtain Possible Schedule.xml's ID and matching when Day </t>
-        </is>
-      </c>
-      <c r="F305" s="9" t="n"/>
-    </row>
-    <row r="306" ht="85.5" customHeight="1" s="72">
-      <c r="B306" s="28" t="inlineStr">
-        <is>
-          <t>Mission</t>
-        </is>
-      </c>
-      <c r="C306" s="90" t="n"/>
-      <c r="D306" s="21" t="inlineStr">
+      <c r="D305" s="21" t="inlineStr">
         <is>
           <t>String, Int</t>
         </is>
       </c>
-      <c r="E306" s="13" t="inlineStr">
+      <c r="E305" s="13" t="inlineStr">
         <is>
           <t>Repeat range and EXP cap for Weekly, Seasonal, and Challenge missions. Enter the linked Quest ID.
 - PassMission
@@ -4628,21 +4687,21 @@
 - Quest: Quest ID for the mission</t>
         </is>
       </c>
-      <c r="F306" s="9" t="n"/>
-    </row>
-    <row r="307" ht="16.5" customHeight="1" s="72">
-      <c r="B307" s="29" t="inlineStr">
+      <c r="F305" s="9" t="n"/>
+    </row>
+    <row r="306" ht="85.5" customHeight="1" s="72">
+      <c r="B306" s="29" t="inlineStr">
         <is>
           <t>RewardByLevel</t>
         </is>
       </c>
-      <c r="C307" s="90" t="n"/>
-      <c r="D307" s="21" t="inlineStr">
+      <c r="C306" s="90" t="n"/>
+      <c r="D306" s="21" t="inlineStr">
         <is>
           <t>String, Int</t>
         </is>
       </c>
-      <c r="E307" s="13" t="inlineStr">
+      <c r="E306" s="13" t="inlineStr">
         <is>
           <t>season Level per Reward Content input
 -ID : season Level
@@ -4652,20 +4711,31 @@
  → Count : Providedoing Item's can input</t>
         </is>
       </c>
+      <c r="F306" s="9" t="n"/>
+    </row>
+    <row r="307" ht="16.5" customHeight="1" s="72">
+      <c r="B307" s="9" t="n"/>
+      <c r="C307" s="9" t="n"/>
+      <c r="D307" s="9" t="n"/>
+      <c r="E307" s="18" t="n"/>
       <c r="F307" s="9" t="n"/>
     </row>
     <row r="308" ht="16.5" customHeight="1" s="72">
       <c r="B308" s="9" t="n"/>
-      <c r="C308" s="9" t="n"/>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>- Quest_Pass.xml</t>
+        </is>
+      </c>
       <c r="D308" s="9" t="n"/>
       <c r="E308" s="18" t="n"/>
       <c r="F308" s="9" t="n"/>
     </row>
     <row r="309" ht="16.5" customHeight="1" s="72">
       <c r="B309" s="9" t="n"/>
-      <c r="C309" s="10" t="inlineStr">
-        <is>
-          <t>- Quest_Pass.xml</t>
+      <c r="C309" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> → Each Mission Content's Quest Data input</t>
         </is>
       </c>
       <c r="D309" s="9" t="n"/>
@@ -4676,7 +4746,7 @@
       <c r="B310" s="9" t="n"/>
       <c r="C310" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Each Mission Content's Quest Data input</t>
+          <t xml:space="preserve"> → Achievement, Always's and Same Data Structure use</t>
         </is>
       </c>
       <c r="D310" s="9" t="n"/>
@@ -4687,7 +4757,7 @@
       <c r="B311" s="9" t="n"/>
       <c r="C311" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> → Achievement, Always's and Same Data Structure use</t>
+          <t xml:space="preserve">  → Match the ID value in this data to Pass.xml to determine whether the quest is Weekly, Seasonal, or Challenge.</t>
         </is>
       </c>
       <c r="D311" s="9" t="n"/>
@@ -4696,11 +4766,7 @@
     </row>
     <row r="312" ht="16.5" customHeight="1" s="72">
       <c r="B312" s="9" t="n"/>
-      <c r="C312" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Match the ID value in this data to Pass.xml to determine whether the quest is Weekly, Seasonal, or Challenge.</t>
-        </is>
-      </c>
+      <c r="C312" s="9" t="n"/>
       <c r="D312" s="9" t="n"/>
       <c r="E312" s="18" t="n"/>
       <c r="F312" s="9" t="n"/>
@@ -4762,11 +4828,7 @@
       <c r="F320" s="9" t="n"/>
     </row>
     <row r="321" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="B321" s="9" t="n"/>
-      <c r="C321" s="9" t="n"/>
-      <c r="D321" s="9" t="n"/>
       <c r="E321" s="18" t="n"/>
-      <c r="F321" s="9" t="n"/>
     </row>
     <row r="322" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="E322" s="18" t="n"/>
@@ -4796,22 +4858,22 @@
       <c r="E330" s="18" t="n"/>
     </row>
     <row r="331" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C331" s="10" t="inlineStr">
+        <is>
+          <t>- PassLevel.xml</t>
+        </is>
+      </c>
       <c r="E331" s="18" t="n"/>
     </row>
     <row r="332" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C332" s="10" t="inlineStr">
-        <is>
-          <t>- PassLevel.xml</t>
+      <c r="C332" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> → Each Level Display Icon input</t>
         </is>
       </c>
       <c r="E332" s="18" t="n"/>
     </row>
     <row r="333" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C333" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> → Each Level Display Icon input</t>
-        </is>
-      </c>
       <c r="E333" s="18" t="n"/>
     </row>
     <row r="334" ht="16.5" customFormat="1" customHeight="1" s="9">
@@ -4839,46 +4901,60 @@
       <c r="E341" s="18" t="n"/>
     </row>
     <row r="342" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="E342" s="18" t="n"/>
+      <c r="C342" s="28" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D342" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E342" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C343" s="28" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D343" s="28" t="inlineStr">
         <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E343" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E343" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="344" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C344" s="28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D344" s="28" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E344" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Corresponding Level's Name</t>
         </is>
       </c>
     </row>
     <row r="345" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C345" s="28" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>TRName</t>
         </is>
       </c>
       <c r="D345" s="28" t="inlineStr">
@@ -4888,14 +4964,14 @@
       </c>
       <c r="E345" s="21" t="inlineStr">
         <is>
-          <t>Corresponding Level's Name</t>
+          <t>Corresponding Level's TRName</t>
         </is>
       </c>
     </row>
     <row r="346" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C346" s="28" t="inlineStr">
-        <is>
-          <t>TRName</t>
+      <c r="C346" s="21" t="inlineStr">
+        <is>
+          <t>SymbolImage</t>
         </is>
       </c>
       <c r="D346" s="28" t="inlineStr">
@@ -4905,44 +4981,30 @@
       </c>
       <c r="E346" s="21" t="inlineStr">
         <is>
-          <t>Corresponding Level's TRName</t>
+          <t>Corresponding Level in Display Icon Image Name input</t>
         </is>
       </c>
     </row>
     <row r="347" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C347" s="21" t="inlineStr">
-        <is>
-          <t>SymbolImage</t>
-        </is>
-      </c>
-      <c r="D347" s="28" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="E347" s="21" t="inlineStr">
-        <is>
-          <t>Corresponding Level in Display Icon Image Name input</t>
-        </is>
-      </c>
+      <c r="E347" s="18" t="n"/>
     </row>
     <row r="348" ht="16.5" customFormat="1" customHeight="1" s="9">
+      <c r="C348" s="10" t="inlineStr">
+        <is>
+          <t>- PassEXP.xml</t>
+        </is>
+      </c>
       <c r="E348" s="18" t="n"/>
     </row>
     <row r="349" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C349" s="10" t="inlineStr">
-        <is>
-          <t>- PassEXP.xml</t>
+      <c r="C349" s="9" t="inlineStr">
+        <is>
+          <t>EXP enter</t>
         </is>
       </c>
       <c r="E349" s="18" t="n"/>
     </row>
     <row r="350" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="C350" s="9" t="inlineStr">
-        <is>
-          <t>EXP enter</t>
-        </is>
-      </c>
       <c r="E350" s="18" t="n"/>
     </row>
     <row r="351" ht="16.5" customFormat="1" customHeight="1" s="9">
@@ -4967,29 +5029,43 @@
       <c r="E357" s="18" t="n"/>
     </row>
     <row r="358" ht="16.5" customFormat="1" customHeight="1" s="9">
-      <c r="E358" s="18" t="n"/>
+      <c r="C358" s="28" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D358" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E358" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C359" s="28" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D359" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E359" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="E359" s="21" t="inlineStr">
+        <is>
+          <t>Each season Level</t>
         </is>
       </c>
     </row>
     <row r="360" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C360" s="28" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>EXPForTier1</t>
         </is>
       </c>
       <c r="D360" s="28" t="inlineStr">
@@ -4999,29 +5075,12 @@
       </c>
       <c r="E360" s="21" t="inlineStr">
         <is>
-          <t>Each season Level</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="C361" s="28" t="inlineStr">
-        <is>
-          <t>EXPForTier1</t>
-        </is>
-      </c>
-      <c r="D361" s="28" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="E361" s="21" t="inlineStr">
-        <is>
           <t>EXP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="47">
     <mergeCell ref="C163:C165"/>
     <mergeCell ref="D106:D108"/>
     <mergeCell ref="B302:C302"/>
@@ -5033,7 +5092,6 @@
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="C156:C157"/>
     <mergeCell ref="C85:C86"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="D154:D155"/>
     <mergeCell ref="B303:C303"/>
     <mergeCell ref="C106:C108"/>
@@ -5083,7 +5141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="B2:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="1"/>
@@ -5103,1561 +5161,1186 @@
     <col width="9" customWidth="1" style="8" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="72">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="72"/>
-    <row r="3" s="72">
-      <c r="B3" s="37" t="inlineStr">
+    <row r="1" s="72"/>
+    <row r="2" ht="16.5" customHeight="1" s="72">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>Weekly Mission List</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="72"/>
+    <row r="3" s="72"/>
+    <row r="4" ht="16.5" customHeight="1" s="72">
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Mission Content</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>CompleteDay</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="16.5" customHeight="1" s="72">
-      <c r="B5" s="38" t="inlineStr">
-        <is>
-          <t>Mission Content</t>
-        </is>
-      </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>CompleteDay</t>
-        </is>
-      </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="E5" s="38" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Monster Defeat 100creatures</t>
+        </is>
+      </c>
+      <c r="C5" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="72">
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 100creatures</t>
+          <t>Monster Defeat 300creatures</t>
         </is>
       </c>
       <c r="C6" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="72">
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 300creatures</t>
-        </is>
-      </c>
-      <c r="C7" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Monster Defeat 500creatures</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="72">
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 500creatures</t>
-        </is>
-      </c>
-      <c r="C8" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Monster Defeat 1,000creatures</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="72">
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 1,000creatures</t>
-        </is>
-      </c>
-      <c r="C9" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dark Temple 1times Clear</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="72">
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 1times Clear</t>
-        </is>
-      </c>
-      <c r="C10" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dark Temple 3times Clear</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="72">
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 3times Clear</t>
-        </is>
-      </c>
-      <c r="C11" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dark Temple 5times Clear</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>160</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="72">
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 5times Clear</t>
-        </is>
-      </c>
-      <c r="C12" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Minute 10times Complete</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="72">
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 10times Complete</t>
-        </is>
-      </c>
-      <c r="C13" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Minute 30times Complete</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="72">
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 30times Complete</t>
-        </is>
-      </c>
-      <c r="C14" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Minute 50times Complete</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="39" t="n">
+        <v>120</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="72">
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 50times Complete</t>
-        </is>
-      </c>
-      <c r="C15" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dungeon 1times Clear</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="72">
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 1times Clear</t>
+          <t>Dungeon 5times Clear</t>
         </is>
       </c>
       <c r="C16" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="72">
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 5times Clear</t>
-        </is>
-      </c>
-      <c r="C17" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dungeon 10times Clear</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="72">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 10times Clear</t>
-        </is>
-      </c>
-      <c r="C18" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dungeon 15times Clear</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="72">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 15times Clear</t>
-        </is>
-      </c>
-      <c r="C19" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>times 10pieces use</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="72">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>times 10pieces use</t>
+          <t>times 30pieces use</t>
         </is>
       </c>
       <c r="C20" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D20" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="72">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>times 30pieces use</t>
-        </is>
-      </c>
-      <c r="C21" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>times 50pieces use</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="72">
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t>times 50pieces use</t>
-        </is>
-      </c>
-      <c r="C22" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Relic 10pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="72">
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t>Relic 10pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C23" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Relic 50pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E23" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="72">
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t>Relic 50pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C24" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Relic 100pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="39" t="n">
+        <v>120</v>
+      </c>
+      <c r="E24" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="72">
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t>Relic 100pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C25" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle 1times Summon</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="72">
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 1times Summon</t>
+          <t>Star's Apostle 5times Summon</t>
         </is>
       </c>
       <c r="C26" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D26" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E26" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="72">
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 5times Summon</t>
-        </is>
-      </c>
-      <c r="C27" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle 10times Summon</t>
+        </is>
+      </c>
+      <c r="C27" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="72">
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 10times Summon</t>
-        </is>
-      </c>
-      <c r="C28" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle Level 5times</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="72">
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 5times</t>
+          <t>Star's Apostle Level 10times</t>
         </is>
       </c>
       <c r="C29" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D29" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="72">
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 10times</t>
-        </is>
-      </c>
-      <c r="C30" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 10,000 use</t>
+        </is>
+      </c>
+      <c r="C30" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="72">
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t>Shard 10,000 use</t>
+          <t>Shard 50,000 use</t>
         </is>
       </c>
       <c r="C31" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D31" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="72">
       <c r="B32" s="39" t="inlineStr">
         <is>
-          <t>Shard 50,000 use</t>
-        </is>
-      </c>
-      <c r="C32" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 100,000 use</t>
+        </is>
+      </c>
+      <c r="C32" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="72">
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>Shard 100,000 use</t>
-        </is>
-      </c>
-      <c r="C33" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Field 10times Memoir</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="72">
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>Field 10times Memoir</t>
+          <t>Field 30times Memoir</t>
         </is>
       </c>
       <c r="C34" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D34" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="72">
       <c r="B35" s="39" t="inlineStr">
         <is>
-          <t>Field 30times Memoir</t>
-        </is>
-      </c>
-      <c r="C35" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Field 50times Memoir</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E35" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="72">
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>Field 50times Memoir</t>
-        </is>
-      </c>
-      <c r="C36" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dimensional Gate 10times utilize</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="39" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="72">
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>Dimensional Gate 10times utilize</t>
-        </is>
-      </c>
-      <c r="C37" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" s="72">
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>※ Weekly EXP My/The 2500, Star's Apostle Summon 1times until if done 1500 Obtain Possible</t>
         </is>
       </c>
-      <c r="C38" s="106" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="106" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="106" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="72"/>
-    <row r="40" s="72">
-      <c r="B40" s="37" t="inlineStr">
+      <c r="C37" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="38" s="72"/>
+    <row r="39" ht="16.5" customHeight="1" s="72">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>season Mission List</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="72"/>
+    <row r="40" s="72"/>
+    <row r="41" ht="16.5" customHeight="1" s="72">
+      <c r="B41" s="38" t="inlineStr">
+        <is>
+          <t>Mission Content</t>
+        </is>
+      </c>
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>CompleteDay</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+      <c r="E41" s="38" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+    </row>
     <row r="42" ht="16.5" customHeight="1" s="72">
-      <c r="B42" s="38" t="inlineStr">
-        <is>
-          <t>Mission Content</t>
-        </is>
-      </c>
-      <c r="C42" s="38" t="inlineStr">
-        <is>
-          <t>CompleteDay</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="E42" s="38" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Monster Defeat 10,000creatures</t>
+        </is>
+      </c>
+      <c r="C42" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="39" t="n">
+        <v>200</v>
+      </c>
+      <c r="E42" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="72">
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 10,000creatures</t>
-        </is>
-      </c>
-      <c r="C43" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D43" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Monster Defeat 30,000creatures</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="39" t="n">
+        <v>300</v>
+      </c>
+      <c r="E43" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="72">
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 30,000creatures</t>
-        </is>
-      </c>
-      <c r="C44" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D44" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Monster Defeat 50,000creatures</t>
+        </is>
+      </c>
+      <c r="C44" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="39" t="n">
+        <v>400</v>
+      </c>
+      <c r="E44" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="72">
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 50,000creatures</t>
-        </is>
-      </c>
-      <c r="C45" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dark Temple 8times Clear</t>
+        </is>
+      </c>
+      <c r="C45" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="39" t="n">
+        <v>900</v>
+      </c>
+      <c r="E45" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="72">
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 8times Clear</t>
-        </is>
-      </c>
-      <c r="C46" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Minute 100times Complete</t>
+        </is>
+      </c>
+      <c r="C46" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" s="39" t="n">
+        <v>800</v>
+      </c>
+      <c r="E46" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="72">
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 100times Complete</t>
-        </is>
-      </c>
-      <c r="C47" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dungeon 20times Clear</t>
+        </is>
+      </c>
+      <c r="C47" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E47" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="72">
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 20times Clear</t>
-        </is>
-      </c>
-      <c r="C48" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D48" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>times 100pieces use</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E48" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="72">
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>times 100pieces use</t>
-        </is>
-      </c>
-      <c r="C49" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Relic 150pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C49" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" s="39" t="n">
+        <v>800</v>
+      </c>
+      <c r="E49" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="72">
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>Relic 150pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C50" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle 30times Summon</t>
+        </is>
+      </c>
+      <c r="C50" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="39" t="n">
+        <v>200</v>
+      </c>
+      <c r="E50" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="72">
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 30times Summon</t>
-        </is>
-      </c>
-      <c r="C51" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D51" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle 50times Summon</t>
+        </is>
+      </c>
+      <c r="C51" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="39" t="n">
+        <v>300</v>
+      </c>
+      <c r="E51" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="72">
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 50times Summon</t>
-        </is>
-      </c>
-      <c r="C52" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D52" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle Level 50times</t>
+        </is>
+      </c>
+      <c r="C52" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="39" t="n">
+        <v>200</v>
+      </c>
+      <c r="E52" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="72">
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 50times</t>
-        </is>
-      </c>
-      <c r="C53" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle Level 100times</t>
+        </is>
+      </c>
+      <c r="C53" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E53" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="72">
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle Level 100times</t>
-        </is>
-      </c>
-      <c r="C54" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D54" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 200,000 use</t>
+        </is>
+      </c>
+      <c r="C54" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="39" t="n">
+        <v>300</v>
+      </c>
+      <c r="E54" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="72">
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Shard 200,000 use</t>
-        </is>
-      </c>
-      <c r="C55" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 500,000 use</t>
+        </is>
+      </c>
+      <c r="C55" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E55" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="72">
       <c r="B56" s="39" t="inlineStr">
         <is>
-          <t>Shard 500,000 use</t>
-        </is>
-      </c>
-      <c r="C56" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E56" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 700,000 use</t>
+        </is>
+      </c>
+      <c r="C56" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E56" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="72">
       <c r="B57" s="39" t="inlineStr">
         <is>
-          <t>Shard 700,000 use</t>
-        </is>
-      </c>
-      <c r="C57" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E57" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Field 100times Memoir</t>
+        </is>
+      </c>
+      <c r="C57" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" s="39" t="n">
+        <v>400</v>
+      </c>
+      <c r="E57" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="72">
       <c r="B58" s="39" t="inlineStr">
         <is>
-          <t>Field 100times Memoir</t>
-        </is>
-      </c>
-      <c r="C58" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Knight's Garden : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C58" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="72">
       <c r="B59" s="39" t="inlineStr">
         <is>
-          <t>Knight's Garden : Monster 500creatures Defeat</t>
+          <t>Spring Waterway : Monster 500creatures Defeat</t>
         </is>
       </c>
       <c r="C59" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E59" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="D59" s="39" t="n">
+        <v>200</v>
+      </c>
+      <c r="E59" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="72">
       <c r="B60" s="39" t="inlineStr">
         <is>
-          <t>Spring Waterway : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C60" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Salt Mine : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C60" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="39" t="n">
+        <v>300</v>
+      </c>
+      <c r="E60" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="72">
       <c r="B61" s="39" t="inlineStr">
         <is>
-          <t>Salt Mine : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C61" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silak's Mansion : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C61" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="39" t="n">
+        <v>400</v>
+      </c>
+      <c r="E61" s="39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" s="72">
       <c r="B62" s="39" t="inlineStr">
         <is>
-          <t>Mansion of Syllek : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C62" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" s="72">
-      <c r="B63" s="39" t="inlineStr">
-        <is>
-          <t>Burning Forge : Monster 500creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C63" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
+          <t>Burning Furnace : Monster 500creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C62" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E62" s="39" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" s="72"/>
     <row r="64" s="72"/>
-    <row r="65" ht="16.5" customHeight="1" s="72"/>
-    <row r="66" s="72">
-      <c r="B66" s="37" t="inlineStr">
+    <row r="65" ht="16.5" customHeight="1" s="72">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve"> Mission List</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1" s="72"/>
+    <row r="66" s="72"/>
+    <row r="67" ht="16.5" customHeight="1" s="72">
+      <c r="B67" s="38" t="inlineStr">
+        <is>
+          <t>Mission Content</t>
+        </is>
+      </c>
+      <c r="C67" s="38" t="inlineStr">
+        <is>
+          <t>CompleteDay</t>
+        </is>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+      <c r="E67" s="38" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+    </row>
     <row r="68" ht="16.5" customHeight="1" s="72">
-      <c r="B68" s="38" t="inlineStr">
-        <is>
-          <t>Mission Content</t>
-        </is>
-      </c>
-      <c r="C68" s="38" t="inlineStr">
-        <is>
-          <t>CompleteDay</t>
-        </is>
-      </c>
-      <c r="D68" s="38" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="E68" s="38" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
+      <c r="B68" s="39" t="inlineStr">
+        <is>
+          <t>Monster Defeat 100,000creatures</t>
+        </is>
+      </c>
+      <c r="C68" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="39" t="n">
+        <v>400</v>
+      </c>
+      <c r="E68" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="72">
       <c r="B69" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 100,000creatures</t>
-        </is>
-      </c>
-      <c r="C69" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Monster Defeat 200,000creatures</t>
+        </is>
+      </c>
+      <c r="C69" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E69" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="72">
       <c r="B70" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 200,000creatures</t>
-        </is>
-      </c>
-      <c r="C70" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Monster Defeat 300,000creatures</t>
+        </is>
+      </c>
+      <c r="C70" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D70" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E70" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="72">
       <c r="B71" s="39" t="inlineStr">
         <is>
-          <t>Monster Defeat 300,000creatures</t>
-        </is>
-      </c>
-      <c r="C71" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dark Temple 10times Clear</t>
+        </is>
+      </c>
+      <c r="C71" s="39" t="n">
+        <v>22</v>
+      </c>
+      <c r="D71" s="39" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E71" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="72">
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>Dark Temple 10times Clear</t>
-        </is>
-      </c>
-      <c r="C72" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Minute 200times Complete</t>
+        </is>
+      </c>
+      <c r="C72" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D72" s="39" t="n">
+        <v>800</v>
+      </c>
+      <c r="E72" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="72">
       <c r="B73" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Minute 200times Complete</t>
-        </is>
-      </c>
-      <c r="C73" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Dungeon 30times Clear</t>
+        </is>
+      </c>
+      <c r="C73" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D73" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E73" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="72">
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>Dungeon 30times Clear</t>
-        </is>
-      </c>
-      <c r="C74" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>times 500pieces use</t>
+        </is>
+      </c>
+      <c r="C74" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E74" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="72">
       <c r="B75" s="39" t="inlineStr">
         <is>
-          <t>times 500pieces use</t>
-        </is>
-      </c>
-      <c r="C75" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D75" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Relic 200pieces Obtain</t>
+        </is>
+      </c>
+      <c r="C75" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D75" s="39" t="n">
+        <v>800</v>
+      </c>
+      <c r="E75" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="72">
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>Relic 200pieces Obtain</t>
-        </is>
-      </c>
-      <c r="C76" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Star's Apostle 100times Summon</t>
+        </is>
+      </c>
+      <c r="C76" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E76" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="72">
       <c r="B77" s="39" t="inlineStr">
         <is>
-          <t>Star's Apostle 100times Summon</t>
-        </is>
-      </c>
-      <c r="C77" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 1,000,000 use</t>
+        </is>
+      </c>
+      <c r="C77" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E77" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="72">
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>Shard 1,000,000 use</t>
-        </is>
-      </c>
-      <c r="C78" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Shard 5,000,000 use</t>
+        </is>
+      </c>
+      <c r="C78" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D78" s="39" t="n">
+        <v>800</v>
+      </c>
+      <c r="E78" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="72">
       <c r="B79" s="39" t="inlineStr">
         <is>
-          <t>Shard 5,000,000 use</t>
-        </is>
-      </c>
-      <c r="C79" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Field 200times Memoir</t>
+        </is>
+      </c>
+      <c r="C79" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E79" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="72">
       <c r="B80" s="39" t="inlineStr">
         <is>
-          <t>Field 200times Memoir</t>
-        </is>
-      </c>
-      <c r="C80" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Without Normal/Regular Difficulty 's Defeat</t>
+        </is>
+      </c>
+      <c r="C80" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E80" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="81" ht="16.5" customHeight="1" s="72">
       <c r="B81" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Without Normal/Regular Difficulty 's Defeat</t>
-        </is>
-      </c>
-      <c r="C81" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> Without Normal/Regular Difficulty Defeat</t>
+        </is>
+      </c>
+      <c r="C81" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D81" s="39" t="n">
+        <v>700</v>
+      </c>
+      <c r="E81" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="72">
@@ -6666,286 +6349,193 @@
           <t xml:space="preserve"> Without Normal/Regular Difficulty Defeat</t>
         </is>
       </c>
-      <c r="C82" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C82" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D82" s="39" t="n">
+        <v>800</v>
+      </c>
+      <c r="E82" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="83" ht="16.5" customHeight="1" s="72">
       <c r="B83" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Without Normal/Regular Difficulty Defeat</t>
-        </is>
-      </c>
-      <c r="C83" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Knight's Garden : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D83" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E83" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="72">
       <c r="B84" s="39" t="inlineStr">
         <is>
-          <t>Knight's Garden : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C84" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Spring Waterway : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C84" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D84" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E84" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1" s="72">
       <c r="B85" s="39" t="inlineStr">
         <is>
-          <t>Spring Waterway : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C85" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D85" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E85" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Salt Mine : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C85" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D85" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E85" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="72">
       <c r="B86" s="39" t="inlineStr">
         <is>
-          <t>Salt Mine : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C86" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D86" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E86" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silak's Mansion : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C86" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D86" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E86" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" s="72">
       <c r="B87" s="39" t="inlineStr">
         <is>
-          <t>Mansion of Syllek : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C87" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D87" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Burning Furnace : Monster 1,000creatures Defeat</t>
+        </is>
+      </c>
+      <c r="C87" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="D87" s="39" t="n">
+        <v>600</v>
+      </c>
+      <c r="E87" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="72">
       <c r="B88" s="39" t="inlineStr">
         <is>
-          <t>Burning Forge : Monster 1,000creatures Defeat</t>
-        </is>
-      </c>
-      <c r="C88" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D88" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E88" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve">All Sealed Garden 3 to Clear </t>
+        </is>
+      </c>
+      <c r="C88" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D88" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E88" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="72">
       <c r="B89" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Sealed Garden 3 to Clear </t>
-        </is>
-      </c>
-      <c r="C89" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D89" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E89" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve">All Sealed Waterway 3 to Clear </t>
+        </is>
+      </c>
+      <c r="C89" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E89" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" s="72">
       <c r="B90" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Sealed Waterway 3 to Clear </t>
-        </is>
-      </c>
-      <c r="C90" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D90" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E90" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve">All Sealed Mine 3 to Clear </t>
+        </is>
+      </c>
+      <c r="C90" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E90" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="91" ht="16.5" customHeight="1" s="72">
       <c r="B91" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Sealed Mine 3 to Clear </t>
-        </is>
-      </c>
-      <c r="C91" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D91" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E91" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Knight's Garden Exploration Mission All Complete</t>
+        </is>
+      </c>
+      <c r="C91" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E91" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="72">
       <c r="B92" s="39" t="inlineStr">
         <is>
-          <t>Knight's Garden Exploration Mission All Complete</t>
-        </is>
-      </c>
-      <c r="C92" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D92" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Spring Waterway Exploration Mission All Complete</t>
+        </is>
+      </c>
+      <c r="C92" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E92" s="39" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="72">
       <c r="B93" s="39" t="inlineStr">
         <is>
-          <t>Spring Waterway Exploration Mission All Complete</t>
-        </is>
-      </c>
-      <c r="C93" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D93" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E93" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" s="72">
-      <c r="B94" s="39" t="inlineStr">
-        <is>
           <t>Salt Mine Exploration Mission All Complete</t>
         </is>
       </c>
-      <c r="C94" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E94" s="105" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
+      <c r="C93" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D93" s="39" t="n">
+        <v>500</v>
+      </c>
+      <c r="E93" s="39" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" s="72"/>
     <row r="95" s="72"/>
     <row r="96" s="72"/>
     <row r="97" s="72"/>
@@ -6979,18 +6569,14 @@
     <row r="125" s="72"/>
     <row r="126" s="72"/>
     <row r="127" s="72"/>
-    <row r="128" ht="16.5" customHeight="1" s="72"/>
-    <row r="129">
-      <c r="B129" s="8" t="inlineStr">
+    <row r="128" ht="16.5" customHeight="1" s="72">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>■ season Level Reward</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7001,1044 +6587,770 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="B2:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="40" min="1" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="72">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="72"/>
+    <row r="1" s="72"/>
+    <row r="2" ht="16.5" customHeight="1" s="72">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="16.5" customHeight="1" s="72">
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
+        <is>
+          <t>※ EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="72">
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" s="72">
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>※ EXP</t>
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumulative </t>
         </is>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="72">
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="C5" s="42" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="D5" s="42" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="E5" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cumulative </t>
-        </is>
+      <c r="B5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>Bronze1</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="72">
       <c r="B6" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>Bronze1</t>
+          <t>Bronze2</t>
         </is>
       </c>
       <c r="D6" s="43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E6" s="43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="72">
-      <c r="B7" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B7" s="43" t="n">
+        <v>3</v>
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>Bronze2</t>
-        </is>
-      </c>
-      <c r="D7" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze3</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="72">
-      <c r="B8" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B8" s="43" t="n">
+        <v>4</v>
       </c>
       <c r="C8" s="43" t="inlineStr">
         <is>
-          <t>Bronze3</t>
-        </is>
-      </c>
-      <c r="D8" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze4</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="72">
-      <c r="B9" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B9" s="43" t="n">
+        <v>5</v>
       </c>
       <c r="C9" s="43" t="inlineStr">
         <is>
-          <t>Bronze4</t>
-        </is>
-      </c>
-      <c r="D9" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze5</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="72">
-      <c r="B10" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B10" s="43" t="n">
+        <v>6</v>
       </c>
       <c r="C10" s="43" t="inlineStr">
         <is>
-          <t>Bronze5</t>
-        </is>
-      </c>
-      <c r="D10" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze6</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="43" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="72">
-      <c r="B11" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B11" s="43" t="n">
+        <v>7</v>
       </c>
       <c r="C11" s="43" t="inlineStr">
         <is>
-          <t>Bronze6</t>
-        </is>
-      </c>
-      <c r="D11" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze7</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="72">
-      <c r="B12" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B12" s="43" t="n">
+        <v>8</v>
       </c>
       <c r="C12" s="43" t="inlineStr">
         <is>
-          <t>Bronze7</t>
-        </is>
-      </c>
-      <c r="D12" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze8</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="E12" s="43" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="72">
-      <c r="B13" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B13" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="C13" s="43" t="inlineStr">
         <is>
-          <t>Bronze8</t>
-        </is>
-      </c>
-      <c r="D13" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Bronze9</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>160</v>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="72">
-      <c r="B14" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B14" s="43" t="n">
+        <v>10</v>
       </c>
       <c r="C14" s="43" t="inlineStr">
         <is>
-          <t>Bronze9</t>
-        </is>
-      </c>
-      <c r="D14" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver10</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="72">
-      <c r="B15" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B15" s="43" t="n">
+        <v>11</v>
       </c>
       <c r="C15" s="43" t="inlineStr">
         <is>
-          <t>Silver10</t>
-        </is>
-      </c>
-      <c r="D15" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver11</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="72">
-      <c r="B16" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B16" s="43" t="n">
+        <v>12</v>
       </c>
       <c r="C16" s="43" t="inlineStr">
         <is>
-          <t>Silver11</t>
-        </is>
-      </c>
-      <c r="D16" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver12</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>220</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>1320</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="72">
-      <c r="B17" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B17" s="43" t="n">
+        <v>13</v>
       </c>
       <c r="C17" s="43" t="inlineStr">
         <is>
-          <t>Silver12</t>
-        </is>
-      </c>
-      <c r="D17" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver13</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>240</v>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>1560</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="72">
-      <c r="B18" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B18" s="43" t="n">
+        <v>14</v>
       </c>
       <c r="C18" s="43" t="inlineStr">
         <is>
-          <t>Silver13</t>
-        </is>
-      </c>
-      <c r="D18" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver14</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>260</v>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>1820</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="72">
-      <c r="B19" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B19" s="43" t="n">
+        <v>15</v>
       </c>
       <c r="C19" s="43" t="inlineStr">
         <is>
-          <t>Silver14</t>
-        </is>
-      </c>
-      <c r="D19" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver15</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>280</v>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="72">
-      <c r="B20" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B20" s="43" t="n">
+        <v>16</v>
       </c>
       <c r="C20" s="43" t="inlineStr">
         <is>
-          <t>Silver15</t>
-        </is>
-      </c>
-      <c r="D20" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver16</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>300</v>
+      </c>
+      <c r="E20" s="43" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="72">
-      <c r="B21" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B21" s="43" t="n">
+        <v>17</v>
       </c>
       <c r="C21" s="43" t="inlineStr">
         <is>
-          <t>Silver16</t>
-        </is>
-      </c>
-      <c r="D21" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Silver17</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>320</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>2720</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="72">
-      <c r="B22" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B22" s="43" t="n">
+        <v>18</v>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
-          <t>Silver17</t>
-        </is>
-      </c>
-      <c r="D22" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold18</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="n">
+        <v>340</v>
+      </c>
+      <c r="E22" s="43" t="n">
+        <v>3060</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="72">
-      <c r="B23" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B23" s="43" t="n">
+        <v>19</v>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>Gold18</t>
-        </is>
-      </c>
-      <c r="D23" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold19</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>370</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>3430</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="72">
-      <c r="B24" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B24" s="43" t="n">
+        <v>20</v>
       </c>
       <c r="C24" s="43" t="inlineStr">
         <is>
-          <t>Gold19</t>
-        </is>
-      </c>
-      <c r="D24" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold20</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="n">
+        <v>400</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>3830</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="72">
-      <c r="B25" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B25" s="43" t="n">
+        <v>21</v>
       </c>
       <c r="C25" s="43" t="inlineStr">
         <is>
-          <t>Gold20</t>
-        </is>
-      </c>
-      <c r="D25" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold21</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>430</v>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>4260</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="72">
-      <c r="B26" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B26" s="43" t="n">
+        <v>22</v>
       </c>
       <c r="C26" s="43" t="inlineStr">
         <is>
-          <t>Gold21</t>
-        </is>
-      </c>
-      <c r="D26" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold22</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="n">
+        <v>460</v>
+      </c>
+      <c r="E26" s="43" t="n">
+        <v>4720</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="72">
-      <c r="B27" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B27" s="43" t="n">
+        <v>23</v>
       </c>
       <c r="C27" s="43" t="inlineStr">
         <is>
-          <t>Gold22</t>
-        </is>
-      </c>
-      <c r="D27" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold23</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>490</v>
+      </c>
+      <c r="E27" s="43" t="n">
+        <v>5210</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="72">
-      <c r="B28" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B28" s="43" t="n">
+        <v>24</v>
       </c>
       <c r="C28" s="43" t="inlineStr">
         <is>
-          <t>Gold23</t>
-        </is>
-      </c>
-      <c r="D28" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Gold24</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>520</v>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>5730</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="72">
-      <c r="B29" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B29" s="43" t="n">
+        <v>25</v>
       </c>
       <c r="C29" s="43" t="inlineStr">
         <is>
-          <t>Gold24</t>
-        </is>
-      </c>
-      <c r="D29" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Platinum25</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>550</v>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>6280</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="72">
-      <c r="B30" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B30" s="43" t="n">
+        <v>26</v>
       </c>
       <c r="C30" s="43" t="inlineStr">
         <is>
-          <t>Platinum25</t>
-        </is>
-      </c>
-      <c r="D30" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Platinum26</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>580</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>6860</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" s="72">
-      <c r="B31" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B31" s="43" t="n">
+        <v>27</v>
       </c>
       <c r="C31" s="43" t="inlineStr">
         <is>
-          <t>Platinum26</t>
-        </is>
-      </c>
-      <c r="D31" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Platinum27</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>610</v>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>7470</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="72">
-      <c r="B32" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B32" s="43" t="n">
+        <v>28</v>
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
-          <t>Platinum27</t>
-        </is>
-      </c>
-      <c r="D32" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Platinum28</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>640</v>
+      </c>
+      <c r="E32" s="43" t="n">
+        <v>8110</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="72">
-      <c r="B33" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B33" s="43" t="n">
+        <v>29</v>
       </c>
       <c r="C33" s="43" t="inlineStr">
         <is>
-          <t>Platinum28</t>
-        </is>
-      </c>
-      <c r="D33" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Platinum29</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>670</v>
+      </c>
+      <c r="E33" s="43" t="n">
+        <v>8780</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="72">
-      <c r="B34" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B34" s="43" t="n">
+        <v>30</v>
       </c>
       <c r="C34" s="43" t="inlineStr">
         <is>
-          <t>Platinum29</t>
-        </is>
-      </c>
-      <c r="D34" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Platinum30</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="n">
+        <v>700</v>
+      </c>
+      <c r="E34" s="43" t="n">
+        <v>9480</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="72">
-      <c r="B35" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B35" s="43" t="n">
+        <v>31</v>
       </c>
       <c r="C35" s="43" t="inlineStr">
         <is>
-          <t>Platinum30</t>
-        </is>
-      </c>
-      <c r="D35" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Diamond31</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>740</v>
+      </c>
+      <c r="E35" s="43" t="n">
+        <v>10220</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="72">
-      <c r="B36" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B36" s="43" t="n">
+        <v>32</v>
       </c>
       <c r="C36" s="43" t="inlineStr">
         <is>
-          <t>Diamond31</t>
-        </is>
-      </c>
-      <c r="D36" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Diamond32</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="n">
+        <v>780</v>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>11000</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="72">
-      <c r="B37" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B37" s="43" t="n">
+        <v>33</v>
       </c>
       <c r="C37" s="43" t="inlineStr">
         <is>
-          <t>Diamond32</t>
-        </is>
-      </c>
-      <c r="D37" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Diamond33</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="n">
+        <v>820</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>11820</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="72">
-      <c r="B38" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B38" s="43" t="n">
+        <v>34</v>
       </c>
       <c r="C38" s="43" t="inlineStr">
         <is>
-          <t>Diamond33</t>
-        </is>
-      </c>
-      <c r="D38" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Diamond34</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="n">
+        <v>860</v>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>12680</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="72">
-      <c r="B39" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B39" s="43" t="n">
+        <v>35</v>
       </c>
       <c r="C39" s="43" t="inlineStr">
         <is>
-          <t>Diamond34</t>
-        </is>
-      </c>
-      <c r="D39" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Diamond35</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="n">
+        <v>900</v>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>13580</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="72">
-      <c r="B40" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B40" s="43" t="n">
+        <v>36</v>
       </c>
       <c r="C40" s="43" t="inlineStr">
         <is>
-          <t>Diamond35</t>
-        </is>
-      </c>
-      <c r="D40" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Ascended Master36</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="n">
+        <v>940</v>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>14520</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="72">
-      <c r="B41" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B41" s="43" t="n">
+        <v>37</v>
       </c>
       <c r="C41" s="43" t="inlineStr">
         <is>
-          <t>Ascended Master36</t>
-        </is>
-      </c>
-      <c r="D41" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Ascended Master37</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="n">
+        <v>980</v>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>15500</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="72">
-      <c r="B42" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B42" s="43" t="n">
+        <v>38</v>
       </c>
       <c r="C42" s="43" t="inlineStr">
         <is>
-          <t>Ascended Master37</t>
-        </is>
-      </c>
-      <c r="D42" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Ascended Master38</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E42" s="43" t="n">
+        <v>16520</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="72">
-      <c r="B43" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B43" s="43" t="n">
+        <v>39</v>
       </c>
       <c r="C43" s="43" t="inlineStr">
         <is>
-          <t>Ascended Master38</t>
-        </is>
-      </c>
-      <c r="D43" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Ascended Master39</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E43" s="43" t="n">
+        <v>17580</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="72">
-      <c r="B44" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B44" s="43" t="n">
+        <v>40</v>
       </c>
       <c r="C44" s="43" t="inlineStr">
         <is>
-          <t>Ascended Master39</t>
-        </is>
-      </c>
-      <c r="D44" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Grandmaster40</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E44" s="43" t="n">
+        <v>18690</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="72">
-      <c r="B45" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B45" s="43" t="n">
+        <v>41</v>
       </c>
       <c r="C45" s="43" t="inlineStr">
         <is>
-          <t>Grandmaster40</t>
-        </is>
-      </c>
-      <c r="D45" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Grandmaster41</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="n">
+        <v>1160</v>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>19850</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="72">
-      <c r="B46" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B46" s="43" t="n">
+        <v>42</v>
       </c>
       <c r="C46" s="43" t="inlineStr">
         <is>
-          <t>Grandmaster41</t>
-        </is>
-      </c>
-      <c r="D46" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Grandmaster42</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>21060</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="72">
-      <c r="B47" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B47" s="43" t="n">
+        <v>43</v>
       </c>
       <c r="C47" s="43" t="inlineStr">
         <is>
-          <t>Grandmaster42</t>
-        </is>
-      </c>
-      <c r="D47" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Challenger43</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>22320</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="72">
-      <c r="B48" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B48" s="43" t="n">
+        <v>44</v>
       </c>
       <c r="C48" s="43" t="inlineStr">
         <is>
-          <t>Challenger43</t>
-        </is>
-      </c>
-      <c r="D48" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E48" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Challenger44</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="n">
+        <v>1310</v>
+      </c>
+      <c r="E48" s="43" t="n">
+        <v>23630</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="72">
-      <c r="B49" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B49" s="43" t="n">
+        <v>45</v>
       </c>
       <c r="C49" s="43" t="inlineStr">
         <is>
-          <t>Challenger44</t>
-        </is>
-      </c>
-      <c r="D49" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" s="43" t="inlineStr">
-        <is>
           <t>Legend45</t>
         </is>
       </c>
-      <c r="D50" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D49" s="43" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E49" s="43" t="n">
+        <v>25000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8049,7 +7361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="B2:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="44" min="1" max="3"/>
@@ -8057,786 +7369,607 @@
     <col width="9" customWidth="1" style="44" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" s="72">
-      <c r="A1" s="104" t="inlineStr">
-        <is>
-          <t>CONFIDENTIAL — Shared for portfolio review purposes only. All game content is the property of its respective studio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" s="72"/>
-    <row r="3" s="72">
-      <c r="B3" s="37" t="inlineStr">
+    <row r="1" s="72"/>
+    <row r="2" s="72">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>Pass Reward</t>
         </is>
       </c>
     </row>
-    <row r="4" s="72"/>
+    <row r="3" s="72"/>
+    <row r="4" s="72">
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
     <row r="5" s="72">
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="E5" s="38" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+      <c r="B5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>Shard</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="6" s="72">
       <c r="B6" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>Shard</t>
-        </is>
-      </c>
-      <c r="E6" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7" s="72">
-      <c r="B7" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B7" s="43" t="n">
+        <v>3</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E7" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> applied Each</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8" s="72">
-      <c r="B8" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B8" s="43" t="n">
+        <v>4</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> applied Each</t>
-        </is>
-      </c>
-      <c r="E8" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9" s="72">
-      <c r="B9" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B9" s="43" t="n">
+        <v>5</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="43" t="inlineStr">
         <is>
+          <t xml:space="preserve">R also </t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="72">
+      <c r="B10" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Experience Fragment</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="72">
+      <c r="B11" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> applied Each</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" s="72">
+      <c r="B12" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> applied </t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" s="72">
+      <c r="B13" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Shard</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" s="72">
+      <c r="B14" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" s="72">
+      <c r="B15" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Experience Fragment</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" s="72">
+      <c r="B16" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> applied Each</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" s="72">
+      <c r="B17" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Shining Modify</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" s="72">
+      <c r="B18" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Shard</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19" s="72">
+      <c r="B19" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SR also </t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="72">
+      <c r="B20" s="43" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>Shard</t>
+        </is>
+      </c>
+      <c r="E20" s="43" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="21" s="72">
+      <c r="B21" s="43" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time's </t>
+        </is>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="72">
+      <c r="B22" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>Experience Fragment</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" s="72">
+      <c r="B23" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> applied </t>
+        </is>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="72">
+      <c r="B24" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>Dia</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" s="72">
+      <c r="B25" s="43" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">during </t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="72">
+      <c r="B26" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> integer 1pieces </t>
+        </is>
+      </c>
+      <c r="E26" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" s="72">
+      <c r="B27" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Experience Fragment</t>
+        </is>
+      </c>
+      <c r="E27" s="43" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" s="72">
+      <c r="B28" s="43" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>Shining Modify</t>
+        </is>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" s="72">
+      <c r="B29" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 's Spirit</t>
+        </is>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" s="72">
+      <c r="B30" s="43" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Experience Fragment</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" s="72">
+      <c r="B31" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>Shard</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="32" s="72">
+      <c r="B32" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="C32" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> integer 1pieces </t>
+        </is>
+      </c>
+      <c r="E32" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" s="72">
+      <c r="B33" s="43" t="n">
+        <v>29</v>
+      </c>
+      <c r="C33" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGrade/Tier Gem </t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" s="72">
+      <c r="B34" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40 </t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" s="72">
+      <c r="B35" s="43" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E9" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" s="72">
-      <c r="B10" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="n">
+      <c r="E35" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" s="72">
+      <c r="B36" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="C36" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>Shining Modify</t>
+        </is>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" s="72">
+      <c r="B37" s="43" t="n">
+        <v>33</v>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> integer 1pieces </t>
+        </is>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" s="72">
+      <c r="B38" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="C38" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UCGrade/Tier Gem </t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" s="72">
+      <c r="B39" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> applied also </t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R also </t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="72">
-      <c r="B11" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>Experience Fragment</t>
-        </is>
-      </c>
-      <c r="E11" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" s="72">
-      <c r="B12" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied Each</t>
-        </is>
-      </c>
-      <c r="E12" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" s="72">
-      <c r="B13" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied </t>
-        </is>
-      </c>
-      <c r="E13" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" s="72">
-      <c r="B14" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="43" t="inlineStr">
-        <is>
-          <t>Shard</t>
-        </is>
-      </c>
-      <c r="E14" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" s="72">
-      <c r="B15" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Dia</t>
-        </is>
-      </c>
-      <c r="E15" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" s="72">
-      <c r="B16" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t>Experience Fragment</t>
-        </is>
-      </c>
-      <c r="E16" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" s="72">
-      <c r="B17" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied Each</t>
-        </is>
-      </c>
-      <c r="E17" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" s="72">
-      <c r="B18" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Shining Modify</t>
-        </is>
-      </c>
-      <c r="E18" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" s="72">
-      <c r="B19" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>Shard</t>
-        </is>
-      </c>
-      <c r="E19" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" s="72">
-      <c r="B20" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SR also </t>
-        </is>
-      </c>
-      <c r="E20" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="72">
-      <c r="B21" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Shard</t>
-        </is>
-      </c>
-      <c r="E21" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" s="72">
-      <c r="B22" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
+    </row>
+    <row r="40" s="72">
+      <c r="B40" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="C40" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Time's </t>
-        </is>
-      </c>
-      <c r="E22" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" s="72">
-      <c r="B23" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="43" t="inlineStr">
-        <is>
-          <t>Experience Fragment</t>
-        </is>
-      </c>
-      <c r="E23" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" s="72">
-      <c r="B24" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C24" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied </t>
-        </is>
-      </c>
-      <c r="E24" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" s="72">
-      <c r="B25" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C25" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="43" t="inlineStr">
-        <is>
-          <t>Dia</t>
-        </is>
-      </c>
-      <c r="E25" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" s="72">
-      <c r="B26" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C26" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">during </t>
-        </is>
-      </c>
-      <c r="E26" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" s="72">
-      <c r="B27" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C27" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> integer 1pieces </t>
-        </is>
-      </c>
-      <c r="E27" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" s="72">
-      <c r="B28" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C28" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Experience Fragment</t>
-        </is>
-      </c>
-      <c r="E28" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" s="72">
-      <c r="B29" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Shining Modify</t>
-        </is>
-      </c>
-      <c r="E29" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" s="72">
-      <c r="B30" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 's Spirit</t>
-        </is>
-      </c>
-      <c r="E30" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" s="72">
-      <c r="B31" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
-        <is>
-          <t>Experience Fragment</t>
-        </is>
-      </c>
-      <c r="E31" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" s="72">
-      <c r="B32" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C32" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Shard</t>
-        </is>
-      </c>
-      <c r="E32" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" s="72">
-      <c r="B33" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C33" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> integer 1pieces </t>
-        </is>
-      </c>
-      <c r="E33" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" s="72">
-      <c r="B34" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CGrade/Tier Gem </t>
-        </is>
-      </c>
-      <c r="E34" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" s="72">
-      <c r="B35" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C35" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" s="72">
-      <c r="B36" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E36" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" s="72">
-      <c r="B37" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C37" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
-        <is>
-          <t>Shining Modify</t>
-        </is>
-      </c>
-      <c r="E37" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" s="72">
-      <c r="B38" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C38" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> integer 1pieces </t>
-        </is>
-      </c>
-      <c r="E38" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" s="72">
-      <c r="B39" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C39" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UCGrade/Tier Gem </t>
-        </is>
-      </c>
-      <c r="E39" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" s="72">
-      <c r="B40" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied also </t>
         </is>
       </c>
       <c r="E40" s="43" t="n">
@@ -8844,221 +7977,150 @@
       </c>
     </row>
     <row r="41" s="72">
-      <c r="B41" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C41" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B41" s="43" t="n">
+        <v>37</v>
+      </c>
+      <c r="C41" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time's </t>
+          <t xml:space="preserve"> applied Each</t>
         </is>
       </c>
       <c r="E41" s="43" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" s="72">
+      <c r="B42" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="C42" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
+          <t>Shining Modify</t>
+        </is>
+      </c>
+      <c r="E42" s="43" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" s="72">
+      <c r="B43" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="C43" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E43" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" s="72">
+      <c r="B44" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C44" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RGrade/Tier Gem </t>
+        </is>
+      </c>
+      <c r="E44" s="43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" s="72">
+      <c r="B45" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C45" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>per's Spirit</t>
+        </is>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" s="72">
+      <c r="B46" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C46" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40 </t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="42" s="72">
-      <c r="B42" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C42" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied Each</t>
-        </is>
-      </c>
-      <c r="E42" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" s="72">
-      <c r="B43" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C43" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D43" s="43" t="inlineStr">
-        <is>
-          <t>Shining Modify</t>
-        </is>
-      </c>
-      <c r="E43" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" s="72">
-      <c r="B44" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C44" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D44" s="43" t="inlineStr">
+    <row r="47" s="72">
+      <c r="B47" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="C47" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>Soul</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" s="72">
+      <c r="B48" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> applied also </t>
+        </is>
+      </c>
+      <c r="E48" s="43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" s="72">
+      <c r="B49" s="43" t="n">
+        <v>45</v>
+      </c>
+      <c r="C49" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E44" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" s="72">
-      <c r="B45" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C45" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RGrade/Tier Gem </t>
-        </is>
-      </c>
-      <c r="E45" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" s="72">
-      <c r="B46" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C46" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>per's Spirit</t>
-        </is>
-      </c>
-      <c r="E46" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" s="72">
-      <c r="B47" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C47" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" s="72">
-      <c r="B48" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C48" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Soul</t>
-        </is>
-      </c>
-      <c r="E48" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" s="72">
-      <c r="B49" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C49" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> applied also </t>
         </is>
       </c>
       <c r="E49" s="43" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" s="107" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="E50" s="43" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -2325,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A2:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="27" min="1" max="1"/>
@@ -2337,7 +2337,6 @@
     <col width="9" customWidth="1" style="27" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22" customHeight="1" s="72">
       <c r="B2" s="91" t="inlineStr">
         <is>
@@ -3471,7 +3470,7 @@
       <c r="D118" s="88" t="n"/>
       <c r="E118" s="16" t="inlineStr">
         <is>
-          <t>Greyscale processing And green V Check</t>
+          <t>Greyed out with green checkmark when completed</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3681,7 @@
       <c r="D159" s="86" t="n"/>
       <c r="E159" s="20" t="inlineStr">
         <is>
-          <t>Corresponding List Greyscale processing, Reward Icon green V Display</t>
+          <t>Completed entries greyed out; reward icon shows green checkmark</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3738,7 @@
       <c r="D164" s="87" t="n"/>
       <c r="E164" s="71" t="inlineStr">
         <is>
-          <t>Claim Available Reward without case Greyscale processing</t>
+          <t>Greyed out when no claimable rewards available</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4149,7 @@
     <row r="233" ht="16.5" customFormat="1" customHeight="1" s="9">
       <c r="C233" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> when) Below and as follows Composition when, Weekly Mission Progressduring state in Monster 100creatures DefeatDid, season Mission Monster 90/100 to Count Done/Applied</t>
+          <t>When composed as below, Weekly Mission remains in progress state</t>
         </is>
       </c>
     </row>

--- a/docs/SeasonPass_DesignDocument.xlsx
+++ b/docs/SeasonPass_DesignDocument.xlsx
@@ -1066,996 +1066,996 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>971550</colOff>
-      <row>252</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1076325</colOff>
-      <row>255</row>
-      <rowOff>238125</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="226" name="그룹 225"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+<ns0:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:ns0="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:ns2="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>971550</ns0:colOff>
+      <ns0:row>252</ns0:row>
+      <ns0:rowOff>190500</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1076325</ns0:colOff>
+      <ns0:row>255</ns0:row>
+      <ns0:rowOff>238125</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="226" name="그룹 225"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2076450" y="55797450"/>
           <a:ext cx="1295400" cy="1314450"/>
           <a:chOff x="454025" y="184150"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="227" name="그림 226" descr="스크린샷, 예술, 대칭, 프레임이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="227" name="그림 226" descr="스크린샷, 예술, 대칭, 프레임이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId1"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="454025" y="184150"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>1019175</colOff>
-      <row>254</row>
-      <rowOff>581026</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1076325</colOff>
-      <row>256</row>
-      <rowOff>219076</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="229" name="그룹 228"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>1019175</ns0:colOff>
+      <ns0:row>254</ns0:row>
+      <ns0:rowOff>581026</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1076325</ns0:colOff>
+      <ns0:row>256</ns0:row>
+      <ns0:rowOff>219076</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="229" name="그룹 228"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2124075" y="56607076"/>
           <a:ext cx="1247775" cy="1333500"/>
           <a:chOff x="2184400" y="184150"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="230" name="그림 229" descr="대칭, 예술, 디자인, 육각형이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="230" name="그림 229" descr="대칭, 예술, 디자인, 육각형이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId2"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="2184400" y="184150"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>981075</colOff>
-      <row>255</row>
-      <rowOff>581025</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1095375</colOff>
-      <row>257</row>
-      <rowOff>171450</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="233" name="그룹 232"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>981075</ns0:colOff>
+      <ns0:row>255</ns0:row>
+      <ns0:rowOff>581025</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1095375</ns0:colOff>
+      <ns0:row>257</ns0:row>
+      <ns0:rowOff>171450</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="233" name="그룹 232"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2085975" y="57454800"/>
           <a:ext cx="1304925" cy="1285875"/>
           <a:chOff x="3914775" y="184150"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="234" name="그림 233" descr="대칭, 예술, 디자인이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="234" name="그림 233" descr="대칭, 예술, 디자인이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId3"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="3914775" y="184150"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>1009650</colOff>
-      <row>256</row>
-      <rowOff>581025</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1019175</colOff>
-      <row>258</row>
-      <rowOff>142875</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="236" name="그룹 235"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>1009650</ns0:colOff>
+      <ns0:row>256</ns0:row>
+      <ns0:rowOff>581025</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1019175</ns0:colOff>
+      <ns0:row>258</ns0:row>
+      <ns0:rowOff>142875</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="236" name="그룹 235"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2114550" y="58302525"/>
           <a:ext cx="1200150" cy="1257300"/>
           <a:chOff x="5773737" y="184150"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="237" name="그림 236" descr="예술, 대칭, 디자인이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="237" name="그림 236" descr="예술, 대칭, 디자인이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId4"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="5773737" y="184150"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>1104900</colOff>
-      <row>257</row>
-      <rowOff>571500</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1133475</colOff>
-      <row>259</row>
-      <rowOff>171450</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="239" name="그룹 238"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>1104900</ns0:colOff>
+      <ns0:row>257</ns0:row>
+      <ns0:rowOff>571500</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1133475</ns0:colOff>
+      <ns0:row>259</ns0:row>
+      <ns0:rowOff>171450</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="239" name="그룹 238"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2209800" y="59140725"/>
           <a:ext cx="1219200" cy="1295400"/>
           <a:chOff x="7678738" y="184150"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="240" name="그림 239" descr="대칭, 예술이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="240" name="그림 239" descr="대칭, 예술이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId5"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="7678738" y="184150"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>1133475</colOff>
-      <row>258</row>
-      <rowOff>561974</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1133476</colOff>
-      <row>260</row>
-      <rowOff>200025</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="242" name="그룹 241"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>1133475</ns0:colOff>
+      <ns0:row>258</ns0:row>
+      <ns0:rowOff>561974</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1133476</ns0:colOff>
+      <ns0:row>260</ns0:row>
+      <ns0:rowOff>200025</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="242" name="그룹 241"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2238375" y="59978924"/>
           <a:ext cx="1190626" cy="1333501"/>
           <a:chOff x="454025" y="2476500"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="243" name="그림 242" descr="예술, 디자인이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="243" name="그림 242" descr="예술, 디자인이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId6"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="454025" y="2476500"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>1133475</colOff>
-      <row>259</row>
-      <rowOff>685800</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1066800</colOff>
-      <row>261</row>
-      <rowOff>76200</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="245" name="그룹 244"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>1133475</ns0:colOff>
+      <ns0:row>259</ns0:row>
+      <ns0:rowOff>685800</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1066800</ns0:colOff>
+      <ns0:row>261</ns0:row>
+      <ns0:rowOff>76200</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="245" name="그룹 244"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2238375" y="60950475"/>
           <a:ext cx="1123950" cy="1085850"/>
           <a:chOff x="2927350" y="2476499"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="246" name="그림 245" descr="예술이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="246" name="그림 245" descr="예술이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId7"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="2927350" y="2476499"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>1114425</colOff>
-      <row>260</row>
-      <rowOff>619125</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1162050</colOff>
-      <row>262</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="248" name="그룹 247"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>3</ns0:col>
+      <ns0:colOff>1114425</ns0:colOff>
+      <ns0:row>260</ns0:row>
+      <ns0:rowOff>619125</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1162050</ns0:colOff>
+      <ns0:row>262</ns0:row>
+      <ns0:rowOff>95250</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="248" name="그룹 247"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2219325" y="61731525"/>
           <a:ext cx="1238250" cy="1171575"/>
           <a:chOff x="5575300" y="2476499"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="249" name="그림 248" descr="예술, 종이접기이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="249" name="그림 248" descr="예술, 종이접기이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId8"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="5575300" y="2476499"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>261</row>
-      <rowOff>695325</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>1066800</colOff>
-      <row>263</row>
-      <rowOff>76200</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="251" name="그룹 250"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>0</ns0:colOff>
+      <ns0:row>261</ns0:row>
+      <ns0:rowOff>695325</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>1066800</ns0:colOff>
+      <ns0:row>263</ns0:row>
+      <ns0:rowOff>76200</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="251" name="그룹 250"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2295525" y="62655450"/>
           <a:ext cx="1066800" cy="1076325"/>
           <a:chOff x="8185150" y="2476499"/>
           <a:chExt cx="1905000" cy="1905000"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="252" name="그림 251" descr="예술이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="252" name="그림 251" descr="예술이(가) 표시된 사진&#10;&#10;자동 생성된 설명"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId9"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="8185150" y="2476499"/>
             <a:ext cx="1905000" cy="1905000"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>152400</colOff>
-      <row>311</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <to>
-      <col>50</col>
-      <colOff>140870</colOff>
-      <row>328</row>
-      <rowOff>113849</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="256" name="그림 255"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>1</ns0:col>
+      <ns0:colOff>152400</ns0:colOff>
+      <ns0:row>311</ns0:row>
+      <ns0:rowOff>66675</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>50</ns0:col>
+      <ns0:colOff>140870</ns0:colOff>
+      <ns0:row>328</ns0:row>
+      <ns0:rowOff>113849</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="256" name="그림 255"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId10"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="352425" y="60321825"/>
           <a:ext cx="16038095" cy="3609524"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>332</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>2085477</colOff>
-      <row>340</row>
-      <rowOff>37886</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="257" name="그림 256"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>0</ns0:colOff>
+      <ns0:row>332</ns0:row>
+      <ns0:rowOff>0</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>2085477</ns0:colOff>
+      <ns0:row>340</ns0:row>
+      <ns0:rowOff>37886</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="257" name="그림 256"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId11"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="400050" y="64655700"/>
           <a:ext cx="3980952" cy="1714286"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>561668</colOff>
-      <row>356</row>
-      <rowOff>123626</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="258" name="그림 257"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>0</ns0:colOff>
+      <ns0:row>349</ns0:row>
+      <ns0:rowOff>0</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>561668</ns0:colOff>
+      <ns0:row>356</ns0:row>
+      <ns0:rowOff>123626</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="258" name="그림 257"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId12"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="400050" y="68218050"/>
           <a:ext cx="2457143" cy="1590476"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>198029</colOff>
-      <row>33</row>
-      <rowOff>54115</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>4276725</colOff>
-      <row>49</row>
-      <rowOff>136761</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="그림 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>1</ns0:col>
+      <ns0:colOff>198029</ns0:colOff>
+      <ns0:row>33</ns0:row>
+      <ns0:rowOff>54115</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>4276725</ns0:colOff>
+      <ns0:row>49</ns0:row>
+      <ns0:rowOff>136761</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="9" name="그림 8"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId13"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="398054" y="6969265"/>
           <a:ext cx="6174196" cy="3435446"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>14369</colOff>
-      <row>12</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>4293280</colOff>
-      <row>28</row>
-      <rowOff>132339</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="그림 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>14369</ns0:colOff>
+      <ns0:row>12</ns0:row>
+      <ns0:rowOff>9525</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>4293280</ns0:colOff>
+      <ns0:row>28</ns0:row>
+      <ns0:rowOff>132339</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="10" name="그림 9"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId14"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="414419" y="2524125"/>
           <a:ext cx="6174386" cy="3475614"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>106194</colOff>
-      <row>53</row>
-      <rowOff>15401</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>123825</colOff>
-      <row>75</row>
-      <rowOff>57150</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="11" name="그룹 10"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>1</ns0:col>
+      <ns0:colOff>106194</ns0:colOff>
+      <ns0:row>53</ns0:row>
+      <ns0:rowOff>15401</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>12</ns0:col>
+      <ns0:colOff>123825</ns0:colOff>
+      <ns0:row>75</ns0:row>
+      <ns0:rowOff>57150</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="11" name="그룹 10"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="306219" y="11121551"/>
           <a:ext cx="8466306" cy="4651849"/>
           <a:chOff x="94118" y="195262"/>
           <a:chExt cx="11968292" cy="6467475"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="12" name="그림 11"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="12" name="그림 11"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId15"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="266700" y="195262"/>
             <a:ext cx="11658600" cy="6467475"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>13841</colOff>
-      <row>167</row>
-      <rowOff>93926</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>138559</colOff>
-      <row>184</row>
-      <rowOff>182298</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="57" name="그룹 56"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>13841</ns0:colOff>
+      <ns0:row>167</ns0:row>
+      <ns0:rowOff>93926</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>5</ns0:col>
+      <ns0:colOff>138559</ns0:colOff>
+      <ns0:row>184</ns0:row>
+      <ns0:rowOff>182298</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="57" name="그룹 56"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="413891" y="35250701"/>
           <a:ext cx="6554093" cy="3650722"/>
           <a:chOff x="290512" y="195262"/>
           <a:chExt cx="11610975" cy="6467475"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="58" name="그림 57"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="58" name="그림 57"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId16"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="290512" y="195262"/>
             <a:ext cx="11610975" cy="6467475"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>28579</colOff>
-      <row>189</row>
-      <rowOff>330140</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>4522913</colOff>
-      <row>189</row>
-      <rowOff>2812304</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="그림 62"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>28579</ns0:colOff>
+      <ns0:row>189</ns0:row>
+      <ns0:rowOff>330140</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>4522913</ns0:colOff>
+      <ns0:row>189</ns0:row>
+      <ns0:rowOff>2812304</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="63" name="그림 62"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId17"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="2324104" y="40097015"/>
           <a:ext cx="4494334" cy="2482164"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>43790</colOff>
-      <row>192</row>
-      <rowOff>59799</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>221448</colOff>
-      <row>209</row>
-      <rowOff>158466</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="128" name="그림 127"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>43790</ns0:colOff>
+      <ns0:row>192</ns0:row>
+      <ns0:rowOff>59799</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>5</ns0:col>
+      <ns0:colOff>221448</ns0:colOff>
+      <ns0:row>209</ns0:row>
+      <ns0:rowOff>158466</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="128" name="그림 127"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId18"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="443840" y="43093749"/>
           <a:ext cx="6607033" cy="3661017"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>15624</colOff>
-      <row>267</row>
-      <rowOff>157117</rowOff>
-    </from>
-    <to>
-      <col>31</col>
-      <colOff>58573</colOff>
-      <row>298</row>
-      <rowOff>146702</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="129" name="그림 128"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>1</ns0:col>
+      <ns0:colOff>15624</ns0:colOff>
+      <ns0:row>267</ns0:row>
+      <ns0:rowOff>157117</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>31</ns0:col>
+      <ns0:colOff>58573</ns0:colOff>
+      <ns0:row>298</ns0:row>
+      <ns0:rowOff>146702</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="129" name="그림 128"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId19"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="215649" y="64650892"/>
           <a:ext cx="12292099" cy="6485635"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>143766</colOff>
-      <row>88</row>
-      <rowOff>49357</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>2638098</colOff>
-      <row>99</row>
-      <rowOff>255443</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="130" name="그룹 129"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>143766</ns0:colOff>
+      <ns0:row>88</ns0:row>
+      <ns0:rowOff>49357</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>4</ns0:col>
+      <ns0:colOff>2638098</ns0:colOff>
+      <ns0:row>99</ns0:row>
+      <ns0:rowOff>255443</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="130" name="그룹 129"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="2439291" y="18489757"/>
           <a:ext cx="2494332" cy="2511136"/>
           <a:chOff x="4638110" y="2047875"/>
           <a:chExt cx="2743765" cy="2762250"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="134" name="그림 133"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="134" name="그림 133"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId20"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="4928244" y="3261441"/>
             <a:ext cx="2335512" cy="593001"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+</ns0:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
